--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1A27E0-D3F1-491E-833D-A2854DC4F08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4424F84-E6ED-4585-AACD-6DA1A4511956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="7965" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5617" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5630" uniqueCount="115">
   <si>
     <t>ID</t>
   </si>
@@ -592,8 +592,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI903" totalsRowShown="0">
-  <autoFilter ref="A1:AI903" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI905" totalsRowShown="0">
+  <autoFilter ref="A1:AI905" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -947,7 +947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI903"/>
+  <dimension ref="A1:AI905"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -79729,7 +79729,7 @@
         <v>0.78194444444444444</v>
       </c>
       <c r="E898" s="2">
-        <f>D898 + 1/24</f>
+        <f t="shared" ref="E898:E904" si="71">D898 + 1/24</f>
         <v>0.82361111111111107</v>
       </c>
       <c r="F898" t="s">
@@ -79825,7 +79825,7 @@
         <v>0.82013888888888886</v>
       </c>
       <c r="E899" s="2">
-        <f>D899 + 1/24</f>
+        <f t="shared" si="71"/>
         <v>0.86180555555555549</v>
       </c>
       <c r="F899" t="s">
@@ -79912,7 +79912,7 @@
         <v>0.85972222222222228</v>
       </c>
       <c r="E900" s="2">
-        <f>D900 + 1/24</f>
+        <f t="shared" si="71"/>
         <v>0.90138888888888891</v>
       </c>
       <c r="F900" t="s">
@@ -80002,7 +80002,7 @@
         <v>0.79791666666666672</v>
       </c>
       <c r="E901" s="2">
-        <f>D901 + 1/24</f>
+        <f t="shared" si="71"/>
         <v>0.83958333333333335</v>
       </c>
       <c r="F901" t="s">
@@ -80083,7 +80083,7 @@
         <v>0.83750000000000002</v>
       </c>
       <c r="E902" s="2">
-        <f>D902 + 1/24</f>
+        <f t="shared" si="71"/>
         <v>0.87916666666666665</v>
       </c>
       <c r="F902" t="s">
@@ -80164,7 +80164,7 @@
         <v>0.75</v>
       </c>
       <c r="E903" s="2">
-        <f>D903 + 1/24</f>
+        <f t="shared" si="71"/>
         <v>0.79166666666666663</v>
       </c>
       <c r="F903" t="s">
@@ -80218,22 +80218,200 @@
       <c r="V903">
         <v>1</v>
       </c>
-      <c r="AC903" s="5">
+      <c r="AC903">
         <f>IF(C903=C902, AC902+1, 1)</f>
         <v>1</v>
       </c>
-      <c r="AD903" s="5">
+      <c r="AD903">
         <f>IF(T903="Loss",AD902+1,0)</f>
         <v>0</v>
       </c>
-      <c r="AE903" s="5">
+      <c r="AE903">
         <f>IF(T903="Win", AE902+1, 0)</f>
         <v>5</v>
       </c>
-      <c r="AF903" s="5"/>
-      <c r="AG903" s="5"/>
-      <c r="AH903" s="5"/>
-      <c r="AI903" s="5"/>
+    </row>
+    <row r="904" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A904">
+        <v>903</v>
+      </c>
+      <c r="B904">
+        <v>1</v>
+      </c>
+      <c r="C904" s="1">
+        <v>45979</v>
+      </c>
+      <c r="D904" s="2">
+        <v>0.83472222222222225</v>
+      </c>
+      <c r="E904" s="2">
+        <f t="shared" si="71"/>
+        <v>0.87638888888888888</v>
+      </c>
+      <c r="F904" t="s">
+        <v>50</v>
+      </c>
+      <c r="G904" t="s">
+        <v>96</v>
+      </c>
+      <c r="H904" t="s">
+        <v>54</v>
+      </c>
+      <c r="I904" t="s">
+        <v>100</v>
+      </c>
+      <c r="J904" t="s">
+        <v>53</v>
+      </c>
+      <c r="K904">
+        <v>9</v>
+      </c>
+      <c r="L904">
+        <v>2</v>
+      </c>
+      <c r="M904">
+        <v>11</v>
+      </c>
+      <c r="N904">
+        <v>10</v>
+      </c>
+      <c r="O904">
+        <v>5</v>
+      </c>
+      <c r="P904">
+        <v>6</v>
+      </c>
+      <c r="Q904">
+        <v>2127</v>
+      </c>
+      <c r="R904">
+        <v>73</v>
+      </c>
+      <c r="S904">
+        <v>52</v>
+      </c>
+      <c r="T904" t="s">
+        <v>63</v>
+      </c>
+      <c r="U904">
+        <v>17856</v>
+      </c>
+      <c r="V904">
+        <v>4</v>
+      </c>
+      <c r="AC904">
+        <f>IF(C904=C903, AC903+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD904">
+        <f>IF(T904="Loss",AD903+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE904">
+        <f>IF(T904="Win", AE903+1, 0)</f>
+        <v>6</v>
+      </c>
+      <c r="AF904">
+        <v>0.17</v>
+      </c>
+      <c r="AG904">
+        <v>43</v>
+      </c>
+      <c r="AH904">
+        <v>69</v>
+      </c>
+      <c r="AI904">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="905" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A905">
+        <v>904</v>
+      </c>
+      <c r="B905">
+        <v>2</v>
+      </c>
+      <c r="C905" s="1">
+        <v>45983</v>
+      </c>
+      <c r="D905" s="2">
+        <v>0.81597222222222221</v>
+      </c>
+      <c r="F905" t="s">
+        <v>59</v>
+      </c>
+      <c r="G905" t="s">
+        <v>97</v>
+      </c>
+      <c r="H905" t="s">
+        <v>54</v>
+      </c>
+      <c r="I905" t="s">
+        <v>61</v>
+      </c>
+      <c r="J905" t="s">
+        <v>57</v>
+      </c>
+      <c r="K905">
+        <v>9</v>
+      </c>
+      <c r="L905">
+        <v>5</v>
+      </c>
+      <c r="M905">
+        <v>5</v>
+      </c>
+      <c r="N905">
+        <v>3</v>
+      </c>
+      <c r="O905">
+        <v>0</v>
+      </c>
+      <c r="P905">
+        <v>0</v>
+      </c>
+      <c r="Q905">
+        <v>1452</v>
+      </c>
+      <c r="R905">
+        <v>103</v>
+      </c>
+      <c r="S905">
+        <v>83</v>
+      </c>
+      <c r="T905" t="s">
+        <v>63</v>
+      </c>
+      <c r="U905" t="s">
+        <v>108</v>
+      </c>
+      <c r="V905">
+        <v>1</v>
+      </c>
+      <c r="AC905" s="5">
+        <f>IF(C905=C904, AC904+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD905" s="5">
+        <f>IF(T905="Loss",AD904+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE905" s="5">
+        <f>IF(T905="Win", AE904+1, 0)</f>
+        <v>7</v>
+      </c>
+      <c r="AF905" s="5">
+        <v>6.28</v>
+      </c>
+      <c r="AG905" s="5">
+        <v>23</v>
+      </c>
+      <c r="AH905" s="5">
+        <v>82</v>
+      </c>
+      <c r="AI905" s="5">
+        <v>93</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4424F84-E6ED-4585-AACD-6DA1A4511956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A6D288-AF62-4B56-BC61-A692B683E5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="7965" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5630" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5636" uniqueCount="115">
   <si>
     <t>ID</t>
   </si>
@@ -539,13 +539,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -592,8 +591,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI905" totalsRowShown="0">
-  <autoFilter ref="A1:AI905" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI906" totalsRowShown="0">
+  <autoFilter ref="A1:AI906" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -947,7 +946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI905"/>
+  <dimension ref="A1:AI906"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -79729,7 +79728,7 @@
         <v>0.78194444444444444</v>
       </c>
       <c r="E898" s="2">
-        <f t="shared" ref="E898:E904" si="71">D898 + 1/24</f>
+        <f t="shared" ref="E898:E903" si="71">D898 + 1/24</f>
         <v>0.82361111111111107</v>
       </c>
       <c r="F898" t="s">
@@ -79967,15 +79966,15 @@
         <v>1</v>
       </c>
       <c r="AC900">
-        <f>IF(C900=C899, AC899+1, 1)</f>
+        <f t="shared" ref="AC900:AC905" si="72">IF(C900=C899, AC899+1, 1)</f>
         <v>1</v>
       </c>
       <c r="AD900">
-        <f>IF(T900="Loss",AD899+1,0)</f>
+        <f t="shared" ref="AD900:AD905" si="73">IF(T900="Loss",AD899+1,0)</f>
         <v>0</v>
       </c>
       <c r="AE900">
-        <f>IF(T900="Win", AE899+1, 0)</f>
+        <f t="shared" ref="AE900:AE905" si="74">IF(T900="Win", AE899+1, 0)</f>
         <v>2</v>
       </c>
       <c r="AF900">
@@ -80057,15 +80056,15 @@
         <v>5</v>
       </c>
       <c r="AC901">
-        <f>IF(C901=C900, AC900+1, 1)</f>
+        <f t="shared" si="72"/>
         <v>1</v>
       </c>
       <c r="AD901">
-        <f>IF(T901="Loss",AD900+1,0)</f>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="AE901">
-        <f>IF(T901="Win", AE900+1, 0)</f>
+        <f t="shared" si="74"/>
         <v>3</v>
       </c>
     </row>
@@ -80138,15 +80137,15 @@
         <v>1</v>
       </c>
       <c r="AC902">
-        <f>IF(C902=C901, AC901+1, 1)</f>
+        <f t="shared" si="72"/>
         <v>1</v>
       </c>
       <c r="AD902">
-        <f>IF(T902="Loss",AD901+1,0)</f>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="AE902">
-        <f>IF(T902="Win", AE901+1, 0)</f>
+        <f t="shared" si="74"/>
         <v>4</v>
       </c>
     </row>
@@ -80219,15 +80218,15 @@
         <v>1</v>
       </c>
       <c r="AC903">
-        <f>IF(C903=C902, AC902+1, 1)</f>
+        <f t="shared" si="72"/>
         <v>1</v>
       </c>
       <c r="AD903">
-        <f>IF(T903="Loss",AD902+1,0)</f>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="AE903">
-        <f>IF(T903="Win", AE902+1, 0)</f>
+        <f t="shared" si="74"/>
         <v>5</v>
       </c>
     </row>
@@ -80245,7 +80244,7 @@
         <v>0.83472222222222225</v>
       </c>
       <c r="E904" s="2">
-        <f t="shared" si="71"/>
+        <f>D904 + 1/24</f>
         <v>0.87638888888888888</v>
       </c>
       <c r="F904" t="s">
@@ -80300,15 +80299,15 @@
         <v>4</v>
       </c>
       <c r="AC904">
-        <f>IF(C904=C903, AC903+1, 1)</f>
+        <f t="shared" si="72"/>
         <v>1</v>
       </c>
       <c r="AD904">
-        <f>IF(T904="Loss",AD903+1,0)</f>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="AE904">
-        <f>IF(T904="Win", AE903+1, 0)</f>
+        <f t="shared" si="74"/>
         <v>6</v>
       </c>
       <c r="AF904">
@@ -80337,6 +80336,10 @@
       <c r="D905" s="2">
         <v>0.81597222222222221</v>
       </c>
+      <c r="E905" s="2">
+        <f>D905 + 1/24</f>
+        <v>0.85763888888888884</v>
+      </c>
       <c r="F905" t="s">
         <v>59</v>
       </c>
@@ -80388,29 +80391,118 @@
       <c r="V905">
         <v>1</v>
       </c>
-      <c r="AC905" s="5">
-        <f>IF(C905=C904, AC904+1, 1)</f>
-        <v>1</v>
-      </c>
-      <c r="AD905" s="5">
-        <f>IF(T905="Loss",AD904+1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE905" s="5">
-        <f>IF(T905="Win", AE904+1, 0)</f>
+      <c r="AC905">
+        <f t="shared" si="72"/>
+        <v>1</v>
+      </c>
+      <c r="AD905">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="AE905">
+        <f t="shared" si="74"/>
         <v>7</v>
       </c>
-      <c r="AF905" s="5">
+      <c r="AF905">
         <v>6.28</v>
       </c>
-      <c r="AG905" s="5">
+      <c r="AG905">
         <v>23</v>
       </c>
-      <c r="AH905" s="5">
+      <c r="AH905">
         <v>82</v>
       </c>
-      <c r="AI905" s="5">
+      <c r="AI905">
         <v>93</v>
+      </c>
+    </row>
+    <row r="906" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A906">
+        <v>905</v>
+      </c>
+      <c r="B906">
+        <v>1</v>
+      </c>
+      <c r="C906" s="1">
+        <v>45986</v>
+      </c>
+      <c r="D906" s="2">
+        <v>0.85069444444444442</v>
+      </c>
+      <c r="F906" t="s">
+        <v>50</v>
+      </c>
+      <c r="G906" t="s">
+        <v>96</v>
+      </c>
+      <c r="H906" t="s">
+        <v>60</v>
+      </c>
+      <c r="I906" t="s">
+        <v>56</v>
+      </c>
+      <c r="J906" t="s">
+        <v>53</v>
+      </c>
+      <c r="K906">
+        <v>9</v>
+      </c>
+      <c r="L906">
+        <v>2</v>
+      </c>
+      <c r="M906">
+        <v>7</v>
+      </c>
+      <c r="N906">
+        <v>9</v>
+      </c>
+      <c r="O906">
+        <v>2</v>
+      </c>
+      <c r="P906">
+        <v>7</v>
+      </c>
+      <c r="Q906">
+        <v>1809</v>
+      </c>
+      <c r="R906">
+        <v>78</v>
+      </c>
+      <c r="S906">
+        <v>50</v>
+      </c>
+      <c r="T906" t="s">
+        <v>63</v>
+      </c>
+      <c r="U906">
+        <v>17921</v>
+      </c>
+      <c r="V906">
+        <v>1</v>
+      </c>
+      <c r="AC906">
+        <f>IF(C906=C905, AC905+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD906">
+        <f>IF(T906="Loss",AD905+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE906">
+        <f>IF(T906="Win", AE905+1, 0)</f>
+        <v>8</v>
+      </c>
+      <c r="AF906">
+        <v>1.69</v>
+      </c>
+      <c r="AG906">
+        <v>37</v>
+      </c>
+      <c r="AH906">
+        <v>59</v>
+      </c>
+      <c r="AI906">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A6D288-AF62-4B56-BC61-A692B683E5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9967D3C-B592-46DF-8727-C178F7CEBF42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="7965" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5636" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5693" uniqueCount="115">
   <si>
     <t>ID</t>
   </si>
@@ -591,8 +591,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI906" totalsRowShown="0">
-  <autoFilter ref="A1:AI906" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI916" totalsRowShown="0">
+  <autoFilter ref="A1:AI916" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -946,7 +946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI906"/>
+  <dimension ref="A1:AI916"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -80429,6 +80429,10 @@
       <c r="D906" s="2">
         <v>0.85069444444444442</v>
       </c>
+      <c r="E906" s="2">
+        <f t="shared" ref="E906" si="75">D906 + 1/24</f>
+        <v>0.89236111111111105</v>
+      </c>
       <c r="F906" t="s">
         <v>50</v>
       </c>
@@ -80481,15 +80485,15 @@
         <v>1</v>
       </c>
       <c r="AC906">
-        <f>IF(C906=C905, AC905+1, 1)</f>
+        <f t="shared" ref="AC906:AC914" si="76">IF(C906=C905, AC905+1, 1)</f>
         <v>1</v>
       </c>
       <c r="AD906">
-        <f>IF(T906="Loss",AD905+1,0)</f>
+        <f t="shared" ref="AD906:AD914" si="77">IF(T906="Loss",AD905+1,0)</f>
         <v>0</v>
       </c>
       <c r="AE906">
-        <f>IF(T906="Win", AE905+1, 0)</f>
+        <f t="shared" ref="AE906:AE914" si="78">IF(T906="Win", AE905+1, 0)</f>
         <v>8</v>
       </c>
       <c r="AF906">
@@ -80503,6 +80507,885 @@
       </c>
       <c r="AI906">
         <v>78</v>
+      </c>
+    </row>
+    <row r="907" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A907">
+        <v>906</v>
+      </c>
+      <c r="B907">
+        <v>1</v>
+      </c>
+      <c r="C907" s="1">
+        <v>45990</v>
+      </c>
+      <c r="D907" s="2">
+        <v>0.8569444444444444</v>
+      </c>
+      <c r="E907" s="2">
+        <f t="shared" ref="E907:E916" si="79">D907 + 1/24</f>
+        <v>0.89861111111111103</v>
+      </c>
+      <c r="F907" t="s">
+        <v>50</v>
+      </c>
+      <c r="G907" t="s">
+        <v>96</v>
+      </c>
+      <c r="H907" t="s">
+        <v>60</v>
+      </c>
+      <c r="I907" t="s">
+        <v>87</v>
+      </c>
+      <c r="J907" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q907">
+        <v>1775</v>
+      </c>
+      <c r="R907">
+        <v>88</v>
+      </c>
+      <c r="S907">
+        <v>46</v>
+      </c>
+      <c r="T907" t="s">
+        <v>63</v>
+      </c>
+      <c r="U907">
+        <v>18294</v>
+      </c>
+      <c r="V907">
+        <v>4</v>
+      </c>
+      <c r="AC907">
+        <f t="shared" si="76"/>
+        <v>1</v>
+      </c>
+      <c r="AD907">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="AE907">
+        <f t="shared" si="78"/>
+        <v>9</v>
+      </c>
+      <c r="AF907">
+        <v>2.84</v>
+      </c>
+      <c r="AG907">
+        <v>20</v>
+      </c>
+      <c r="AH907">
+        <v>83</v>
+      </c>
+      <c r="AI907">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="908" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A908">
+        <v>907</v>
+      </c>
+      <c r="B908">
+        <v>1</v>
+      </c>
+      <c r="C908" s="1">
+        <v>45990</v>
+      </c>
+      <c r="D908" s="2">
+        <v>0.88402777777777775</v>
+      </c>
+      <c r="E908" s="2">
+        <f t="shared" si="79"/>
+        <v>0.92569444444444438</v>
+      </c>
+      <c r="F908" t="s">
+        <v>59</v>
+      </c>
+      <c r="G908" t="s">
+        <v>96</v>
+      </c>
+      <c r="H908" t="s">
+        <v>60</v>
+      </c>
+      <c r="I908" t="s">
+        <v>61</v>
+      </c>
+      <c r="J908" t="s">
+        <v>57</v>
+      </c>
+      <c r="K908">
+        <v>4</v>
+      </c>
+      <c r="L908">
+        <v>3</v>
+      </c>
+      <c r="M908">
+        <v>12</v>
+      </c>
+      <c r="N908">
+        <v>4</v>
+      </c>
+      <c r="O908">
+        <v>0</v>
+      </c>
+      <c r="P908">
+        <v>4</v>
+      </c>
+      <c r="Q908">
+        <v>783</v>
+      </c>
+      <c r="R908">
+        <v>43</v>
+      </c>
+      <c r="S908">
+        <v>37</v>
+      </c>
+      <c r="T908" t="s">
+        <v>58</v>
+      </c>
+      <c r="U908">
+        <v>18668</v>
+      </c>
+      <c r="V908">
+        <v>4</v>
+      </c>
+      <c r="AC908">
+        <f t="shared" si="76"/>
+        <v>2</v>
+      </c>
+      <c r="AD908">
+        <f t="shared" si="77"/>
+        <v>1</v>
+      </c>
+      <c r="AE908">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="AF908">
+        <v>-6.04</v>
+      </c>
+      <c r="AG908">
+        <v>33</v>
+      </c>
+      <c r="AH908">
+        <v>41</v>
+      </c>
+      <c r="AI908">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="909" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A909">
+        <v>908</v>
+      </c>
+      <c r="B909">
+        <v>1</v>
+      </c>
+      <c r="C909" s="1">
+        <v>45990</v>
+      </c>
+      <c r="D909" s="2">
+        <v>0.90902777777777777</v>
+      </c>
+      <c r="E909" s="2">
+        <f t="shared" si="79"/>
+        <v>0.9506944444444444</v>
+      </c>
+      <c r="F909" t="s">
+        <v>50</v>
+      </c>
+      <c r="G909" t="s">
+        <v>96</v>
+      </c>
+      <c r="I909" t="s">
+        <v>87</v>
+      </c>
+      <c r="J909" t="s">
+        <v>53</v>
+      </c>
+      <c r="K909">
+        <v>8</v>
+      </c>
+      <c r="L909">
+        <v>0</v>
+      </c>
+      <c r="M909">
+        <v>8</v>
+      </c>
+      <c r="N909">
+        <v>13</v>
+      </c>
+      <c r="O909">
+        <v>3</v>
+      </c>
+      <c r="P909">
+        <v>6</v>
+      </c>
+      <c r="Q909">
+        <v>2041</v>
+      </c>
+      <c r="R909">
+        <v>92</v>
+      </c>
+      <c r="S909">
+        <v>28</v>
+      </c>
+      <c r="T909" t="s">
+        <v>58</v>
+      </c>
+      <c r="U909">
+        <v>18401</v>
+      </c>
+      <c r="V909">
+        <v>4</v>
+      </c>
+      <c r="AC909">
+        <f t="shared" si="76"/>
+        <v>3</v>
+      </c>
+      <c r="AD909">
+        <f t="shared" si="77"/>
+        <v>2</v>
+      </c>
+      <c r="AE909">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="910" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A910">
+        <v>909</v>
+      </c>
+      <c r="B910">
+        <v>1</v>
+      </c>
+      <c r="C910" s="1">
+        <v>45990</v>
+      </c>
+      <c r="D910" s="2">
+        <v>0.93888888888888888</v>
+      </c>
+      <c r="E910" s="2">
+        <f t="shared" si="79"/>
+        <v>0.98055555555555551</v>
+      </c>
+      <c r="F910" t="s">
+        <v>50</v>
+      </c>
+      <c r="G910" t="s">
+        <v>101</v>
+      </c>
+      <c r="H910" t="s">
+        <v>60</v>
+      </c>
+      <c r="I910" t="s">
+        <v>64</v>
+      </c>
+      <c r="J910" t="s">
+        <v>53</v>
+      </c>
+      <c r="K910">
+        <v>1</v>
+      </c>
+      <c r="L910">
+        <v>3</v>
+      </c>
+      <c r="M910">
+        <v>5</v>
+      </c>
+      <c r="N910">
+        <v>8</v>
+      </c>
+      <c r="O910">
+        <v>5</v>
+      </c>
+      <c r="P910">
+        <v>7</v>
+      </c>
+      <c r="Q910">
+        <v>1313</v>
+      </c>
+      <c r="R910">
+        <v>72</v>
+      </c>
+      <c r="S910">
+        <v>33</v>
+      </c>
+      <c r="T910" t="s">
+        <v>63</v>
+      </c>
+      <c r="U910">
+        <v>18003</v>
+      </c>
+      <c r="V910">
+        <v>1</v>
+      </c>
+      <c r="AC910">
+        <f t="shared" si="76"/>
+        <v>4</v>
+      </c>
+      <c r="AD910">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="AE910">
+        <f t="shared" si="78"/>
+        <v>1</v>
+      </c>
+      <c r="AF910">
+        <v>-2.36</v>
+      </c>
+      <c r="AG910">
+        <v>41</v>
+      </c>
+      <c r="AH910">
+        <v>56</v>
+      </c>
+      <c r="AI910">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="911" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A911">
+        <v>910</v>
+      </c>
+      <c r="B911">
+        <v>1</v>
+      </c>
+      <c r="C911" s="1">
+        <v>45991</v>
+      </c>
+      <c r="D911" s="2">
+        <v>0.77638888888888891</v>
+      </c>
+      <c r="E911" s="2">
+        <f t="shared" si="79"/>
+        <v>0.81805555555555554</v>
+      </c>
+      <c r="F911" t="s">
+        <v>59</v>
+      </c>
+      <c r="G911" t="s">
+        <v>96</v>
+      </c>
+      <c r="H911" t="s">
+        <v>60</v>
+      </c>
+      <c r="I911" t="s">
+        <v>61</v>
+      </c>
+      <c r="J911" t="s">
+        <v>57</v>
+      </c>
+      <c r="K911">
+        <v>5</v>
+      </c>
+      <c r="L911">
+        <v>5</v>
+      </c>
+      <c r="M911">
+        <v>12</v>
+      </c>
+      <c r="N911">
+        <v>7</v>
+      </c>
+      <c r="O911">
+        <v>3</v>
+      </c>
+      <c r="P911">
+        <v>9</v>
+      </c>
+      <c r="Q911">
+        <v>1595</v>
+      </c>
+      <c r="R911">
+        <v>55</v>
+      </c>
+      <c r="S911">
+        <v>8</v>
+      </c>
+      <c r="T911" t="s">
+        <v>63</v>
+      </c>
+      <c r="U911">
+        <v>18263</v>
+      </c>
+      <c r="V911">
+        <v>5</v>
+      </c>
+      <c r="AC911">
+        <f t="shared" si="76"/>
+        <v>1</v>
+      </c>
+      <c r="AD911">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="AE911">
+        <f t="shared" si="78"/>
+        <v>2</v>
+      </c>
+      <c r="AF911">
+        <v>-1.52</v>
+      </c>
+      <c r="AG911">
+        <v>30</v>
+      </c>
+      <c r="AH911">
+        <v>43</v>
+      </c>
+      <c r="AI911">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="912" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A912">
+        <v>911</v>
+      </c>
+      <c r="B912">
+        <v>1</v>
+      </c>
+      <c r="C912" s="1">
+        <v>45991</v>
+      </c>
+      <c r="D912" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E912" s="2">
+        <f t="shared" si="79"/>
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="F912" t="s">
+        <v>50</v>
+      </c>
+      <c r="G912" t="s">
+        <v>96</v>
+      </c>
+      <c r="I912" t="s">
+        <v>87</v>
+      </c>
+      <c r="J912" t="s">
+        <v>53</v>
+      </c>
+      <c r="K912">
+        <v>7</v>
+      </c>
+      <c r="L912">
+        <v>2</v>
+      </c>
+      <c r="M912">
+        <v>12</v>
+      </c>
+      <c r="N912">
+        <v>6</v>
+      </c>
+      <c r="O912">
+        <v>1</v>
+      </c>
+      <c r="P912">
+        <v>11</v>
+      </c>
+      <c r="Q912">
+        <v>1322</v>
+      </c>
+      <c r="R912">
+        <v>45</v>
+      </c>
+      <c r="S912">
+        <v>53</v>
+      </c>
+      <c r="T912" t="s">
+        <v>58</v>
+      </c>
+      <c r="U912">
+        <v>18626</v>
+      </c>
+      <c r="V912">
+        <v>5</v>
+      </c>
+      <c r="AC912">
+        <f t="shared" si="76"/>
+        <v>2</v>
+      </c>
+      <c r="AD912">
+        <f t="shared" si="77"/>
+        <v>1</v>
+      </c>
+      <c r="AE912">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="AF912">
+        <v>-7.54</v>
+      </c>
+      <c r="AG912">
+        <v>42</v>
+      </c>
+      <c r="AH912">
+        <v>48</v>
+      </c>
+      <c r="AI912">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="913" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A913">
+        <v>912</v>
+      </c>
+      <c r="B913">
+        <v>1</v>
+      </c>
+      <c r="C913" s="1">
+        <v>45991</v>
+      </c>
+      <c r="D913" s="2">
+        <v>0.8569444444444444</v>
+      </c>
+      <c r="E913" s="2">
+        <f t="shared" si="79"/>
+        <v>0.89861111111111103</v>
+      </c>
+      <c r="F913" t="s">
+        <v>50</v>
+      </c>
+      <c r="G913" t="s">
+        <v>96</v>
+      </c>
+      <c r="H913" t="s">
+        <v>54</v>
+      </c>
+      <c r="I913" t="s">
+        <v>64</v>
+      </c>
+      <c r="J913" t="s">
+        <v>53</v>
+      </c>
+      <c r="K913">
+        <v>1</v>
+      </c>
+      <c r="L913">
+        <v>0</v>
+      </c>
+      <c r="M913">
+        <v>2</v>
+      </c>
+      <c r="N913">
+        <v>4</v>
+      </c>
+      <c r="O913">
+        <v>5</v>
+      </c>
+      <c r="P913">
+        <v>10</v>
+      </c>
+      <c r="Q913">
+        <v>643</v>
+      </c>
+      <c r="R913">
+        <v>45</v>
+      </c>
+      <c r="S913">
+        <v>60</v>
+      </c>
+      <c r="T913" t="s">
+        <v>58</v>
+      </c>
+      <c r="U913">
+        <v>18357</v>
+      </c>
+      <c r="V913">
+        <v>2</v>
+      </c>
+      <c r="AC913">
+        <f t="shared" si="76"/>
+        <v>3</v>
+      </c>
+      <c r="AD913">
+        <f t="shared" si="77"/>
+        <v>2</v>
+      </c>
+      <c r="AE913">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="914" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A914">
+        <v>913</v>
+      </c>
+      <c r="B914">
+        <v>1</v>
+      </c>
+      <c r="C914" s="1">
+        <v>45991</v>
+      </c>
+      <c r="D914" s="2">
+        <v>0.87430555555555556</v>
+      </c>
+      <c r="E914" s="2">
+        <f t="shared" si="79"/>
+        <v>0.91597222222222219</v>
+      </c>
+      <c r="F914" t="s">
+        <v>59</v>
+      </c>
+      <c r="G914" t="s">
+        <v>96</v>
+      </c>
+      <c r="I914" t="s">
+        <v>52</v>
+      </c>
+      <c r="J914" t="s">
+        <v>57</v>
+      </c>
+      <c r="K914">
+        <v>11</v>
+      </c>
+      <c r="L914">
+        <v>4</v>
+      </c>
+      <c r="M914">
+        <v>9</v>
+      </c>
+      <c r="N914">
+        <v>11</v>
+      </c>
+      <c r="O914">
+        <v>2</v>
+      </c>
+      <c r="P914">
+        <v>8</v>
+      </c>
+      <c r="Q914">
+        <v>2192</v>
+      </c>
+      <c r="R914">
+        <v>99</v>
+      </c>
+      <c r="S914">
+        <v>36</v>
+      </c>
+      <c r="T914" t="s">
+        <v>63</v>
+      </c>
+      <c r="U914">
+        <v>17879</v>
+      </c>
+      <c r="V914">
+        <v>2</v>
+      </c>
+      <c r="AC914">
+        <f t="shared" si="76"/>
+        <v>4</v>
+      </c>
+      <c r="AD914">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="AE914">
+        <f t="shared" si="78"/>
+        <v>1</v>
+      </c>
+      <c r="AF914">
+        <v>2.93</v>
+      </c>
+      <c r="AG914">
+        <v>46</v>
+      </c>
+      <c r="AH914">
+        <v>64</v>
+      </c>
+      <c r="AI914">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="915" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A915">
+        <v>914</v>
+      </c>
+      <c r="B915">
+        <v>1</v>
+      </c>
+      <c r="C915" s="1">
+        <v>45992</v>
+      </c>
+      <c r="D915" s="2">
+        <v>0.9194444444444444</v>
+      </c>
+      <c r="E915" s="2">
+        <f t="shared" si="79"/>
+        <v>0.96111111111111103</v>
+      </c>
+      <c r="F915" t="s">
+        <v>50</v>
+      </c>
+      <c r="G915" t="s">
+        <v>101</v>
+      </c>
+      <c r="H915" t="s">
+        <v>60</v>
+      </c>
+      <c r="I915" t="s">
+        <v>64</v>
+      </c>
+      <c r="J915" t="s">
+        <v>57</v>
+      </c>
+      <c r="K915">
+        <v>1</v>
+      </c>
+      <c r="L915">
+        <v>5</v>
+      </c>
+      <c r="M915">
+        <v>10</v>
+      </c>
+      <c r="N915">
+        <v>4</v>
+      </c>
+      <c r="O915">
+        <v>0</v>
+      </c>
+      <c r="P915">
+        <v>7</v>
+      </c>
+      <c r="Q915">
+        <v>806</v>
+      </c>
+      <c r="R915">
+        <v>40</v>
+      </c>
+      <c r="S915">
+        <v>40</v>
+      </c>
+      <c r="T915" t="s">
+        <v>58</v>
+      </c>
+      <c r="U915">
+        <v>18248</v>
+      </c>
+      <c r="V915">
+        <v>1</v>
+      </c>
+      <c r="AC915">
+        <f>IF(C915=C914, AC914+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD915">
+        <f>IF(T915="Loss",AD914+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE915">
+        <f>IF(T915="Win", AE914+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF915">
+        <v>-5.95</v>
+      </c>
+      <c r="AG915">
+        <v>14</v>
+      </c>
+      <c r="AH915">
+        <v>45</v>
+      </c>
+      <c r="AI915">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="916" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A916">
+        <v>915</v>
+      </c>
+      <c r="B916">
+        <v>1</v>
+      </c>
+      <c r="C916" s="1">
+        <v>45992</v>
+      </c>
+      <c r="D916" s="2">
+        <v>0.9506944444444444</v>
+      </c>
+      <c r="E916" s="2">
+        <f t="shared" si="79"/>
+        <v>0.99236111111111103</v>
+      </c>
+      <c r="F916" t="s">
+        <v>59</v>
+      </c>
+      <c r="G916" t="s">
+        <v>97</v>
+      </c>
+      <c r="H916" t="s">
+        <v>60</v>
+      </c>
+      <c r="I916" t="s">
+        <v>52</v>
+      </c>
+      <c r="J916" t="s">
+        <v>57</v>
+      </c>
+      <c r="K916">
+        <v>6</v>
+      </c>
+      <c r="L916">
+        <v>3</v>
+      </c>
+      <c r="M916">
+        <v>11</v>
+      </c>
+      <c r="N916">
+        <v>10</v>
+      </c>
+      <c r="O916">
+        <v>4</v>
+      </c>
+      <c r="P916">
+        <v>10</v>
+      </c>
+      <c r="Q916">
+        <v>1825</v>
+      </c>
+      <c r="R916">
+        <v>60</v>
+      </c>
+      <c r="S916">
+        <v>37</v>
+      </c>
+      <c r="T916" t="s">
+        <v>63</v>
+      </c>
+      <c r="U916">
+        <v>17856</v>
+      </c>
+      <c r="V916">
+        <v>1</v>
+      </c>
+      <c r="AC916">
+        <f>IF(C916=C915, AC915+1, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AD916">
+        <f>IF(T916="Loss",AD915+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE916">
+        <f>IF(T916="Win", AE915+1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF916">
+        <v>-5.24</v>
+      </c>
+      <c r="AG916">
+        <v>29</v>
+      </c>
+      <c r="AH916">
+        <v>54</v>
+      </c>
+      <c r="AI916">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62895A3E-6E76-4253-A047-9436409A15D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807FA8D5-6DB0-496B-B9BC-5B5388557737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="4020" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6343" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6361" uniqueCount="117">
   <si>
     <t>ID</t>
   </si>
@@ -598,8 +598,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1019" totalsRowShown="0">
-  <autoFilter ref="A1:AI1019" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1022" totalsRowShown="0">
+  <autoFilter ref="A1:AI1022" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -953,7 +953,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1019"/>
+  <dimension ref="A1:AI1022"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -89665,30 +89665,272 @@
       <c r="V1019">
         <v>1</v>
       </c>
-      <c r="AC1019" s="5">
+      <c r="AC1019">
         <f>IF(C1019=C1018, AC1018+1, 1)</f>
         <v>1</v>
       </c>
-      <c r="AD1019" s="5">
+      <c r="AD1019">
         <f>IF(T1019="Loss",AD1018+1,0)</f>
         <v>0</v>
       </c>
-      <c r="AE1019" s="5">
+      <c r="AE1019">
         <f>IF(T1019="Win", AE1018+1, 0)</f>
         <v>2</v>
       </c>
-      <c r="AF1019" s="5">
+      <c r="AF1019">
         <v>7.36</v>
       </c>
-      <c r="AG1019" s="5">
+      <c r="AG1019">
         <v>31</v>
       </c>
-      <c r="AH1019" s="5">
+      <c r="AH1019">
         <v>86</v>
       </c>
-      <c r="AI1019" s="5">
+      <c r="AI1019">
         <v>21</v>
       </c>
+    </row>
+    <row r="1020" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1020">
+        <v>1019</v>
+      </c>
+      <c r="B1020">
+        <v>1</v>
+      </c>
+      <c r="C1020" s="1">
+        <v>46080</v>
+      </c>
+      <c r="D1020" s="2">
+        <v>0.8881944444444444</v>
+      </c>
+      <c r="E1020" s="2">
+        <v>0.8881944444444444</v>
+      </c>
+      <c r="F1020" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1020" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1020" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1020" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1020">
+        <v>6</v>
+      </c>
+      <c r="L1020">
+        <v>5</v>
+      </c>
+      <c r="M1020">
+        <v>10</v>
+      </c>
+      <c r="N1020">
+        <v>8</v>
+      </c>
+      <c r="O1020">
+        <v>2</v>
+      </c>
+      <c r="P1020">
+        <v>9</v>
+      </c>
+      <c r="Q1020">
+        <v>1781</v>
+      </c>
+      <c r="R1020">
+        <v>59</v>
+      </c>
+      <c r="T1020" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1020">
+        <v>18103</v>
+      </c>
+      <c r="V1020">
+        <v>5</v>
+      </c>
+      <c r="AC1020">
+        <f>IF(C1020=C1019, AC1019+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1020">
+        <f>IF(T1020="Loss",AD1019+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1020">
+        <f>IF(T1020="Win", AE1019+1, 0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1021">
+        <v>1020</v>
+      </c>
+      <c r="B1021">
+        <v>1</v>
+      </c>
+      <c r="C1021" s="1">
+        <v>46081</v>
+      </c>
+      <c r="D1021" s="2">
+        <v>0.9375</v>
+      </c>
+      <c r="E1021" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="F1021" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1021" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1021" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1021" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1021" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1021">
+        <v>2</v>
+      </c>
+      <c r="L1021">
+        <v>0</v>
+      </c>
+      <c r="M1021">
+        <v>3</v>
+      </c>
+      <c r="N1021">
+        <v>8</v>
+      </c>
+      <c r="O1021">
+        <v>6</v>
+      </c>
+      <c r="P1021">
+        <v>11</v>
+      </c>
+      <c r="Q1021">
+        <v>1379</v>
+      </c>
+      <c r="R1021">
+        <v>91</v>
+      </c>
+      <c r="S1021">
+        <v>50</v>
+      </c>
+      <c r="T1021" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1021">
+        <v>18457</v>
+      </c>
+      <c r="V1021">
+        <v>4</v>
+      </c>
+      <c r="AC1021" s="5">
+        <f>IF(C1021=C1020, AC1020+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1021" s="5">
+        <f>IF(T1021="Loss",AD1020+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1021" s="5">
+        <f>IF(T1021="Win", AE1020+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF1021" s="5"/>
+      <c r="AG1021" s="5"/>
+      <c r="AH1021" s="5"/>
+      <c r="AI1021" s="5"/>
+    </row>
+    <row r="1022" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1022">
+        <v>1021</v>
+      </c>
+      <c r="B1022">
+        <v>1</v>
+      </c>
+      <c r="C1022" s="1">
+        <v>46081</v>
+      </c>
+      <c r="D1022" s="2">
+        <v>0.9555555555555556</v>
+      </c>
+      <c r="E1022" s="2">
+        <v>0.9555555555555556</v>
+      </c>
+      <c r="F1022" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1022" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1022" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1022" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1022" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1022">
+        <v>7</v>
+      </c>
+      <c r="L1022">
+        <v>2</v>
+      </c>
+      <c r="M1022">
+        <v>9</v>
+      </c>
+      <c r="N1022">
+        <v>5</v>
+      </c>
+      <c r="O1022">
+        <v>3</v>
+      </c>
+      <c r="P1022">
+        <v>7</v>
+      </c>
+      <c r="R1022">
+        <v>66</v>
+      </c>
+      <c r="S1022">
+        <v>16</v>
+      </c>
+      <c r="T1022" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1022">
+        <v>18167</v>
+      </c>
+      <c r="V1022">
+        <v>4</v>
+      </c>
+      <c r="AA1022" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC1022" s="5">
+        <f>IF(C1022=C1021, AC1021+1, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AD1022" s="5">
+        <f>IF(T1022="Loss",AD1021+1,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AE1022" s="5">
+        <f>IF(T1022="Win", AE1021+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF1022" s="5"/>
+      <c r="AG1022" s="5"/>
+      <c r="AH1022" s="5"/>
+      <c r="AI1022" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807FA8D5-6DB0-496B-B9BC-5B5388557737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8994A517-467D-4DD5-8370-D83204DD2B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="4020" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6361" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6367" uniqueCount="117">
   <si>
     <t>ID</t>
   </si>
@@ -598,8 +598,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1022" totalsRowShown="0">
-  <autoFilter ref="A1:AI1022" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1023" totalsRowShown="0">
+  <autoFilter ref="A1:AI1023" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -953,7 +953,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1022"/>
+  <dimension ref="A1:AI1023"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -89831,22 +89831,18 @@
       <c r="V1021">
         <v>4</v>
       </c>
-      <c r="AC1021" s="5">
+      <c r="AC1021">
         <f>IF(C1021=C1020, AC1020+1, 1)</f>
         <v>1</v>
       </c>
-      <c r="AD1021" s="5">
+      <c r="AD1021">
         <f>IF(T1021="Loss",AD1020+1,0)</f>
         <v>1</v>
       </c>
-      <c r="AE1021" s="5">
+      <c r="AE1021">
         <f>IF(T1021="Win", AE1020+1, 0)</f>
         <v>0</v>
       </c>
-      <c r="AF1021" s="5"/>
-      <c r="AG1021" s="5"/>
-      <c r="AH1021" s="5"/>
-      <c r="AI1021" s="5"/>
     </row>
     <row r="1022" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1022">
@@ -89915,22 +89911,107 @@
       <c r="AA1022" t="s">
         <v>113</v>
       </c>
-      <c r="AC1022" s="5">
+      <c r="AC1022">
         <f>IF(C1022=C1021, AC1021+1, 1)</f>
         <v>2</v>
       </c>
-      <c r="AD1022" s="5">
+      <c r="AD1022">
         <f>IF(T1022="Loss",AD1021+1,0)</f>
         <v>2</v>
       </c>
-      <c r="AE1022" s="5">
+      <c r="AE1022">
         <f>IF(T1022="Win", AE1021+1, 0)</f>
         <v>0</v>
       </c>
-      <c r="AF1022" s="5"/>
-      <c r="AG1022" s="5"/>
-      <c r="AH1022" s="5"/>
-      <c r="AI1022" s="5"/>
+    </row>
+    <row r="1023" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1023">
+        <v>1022</v>
+      </c>
+      <c r="B1023">
+        <v>1</v>
+      </c>
+      <c r="C1023" s="1">
+        <v>46087</v>
+      </c>
+      <c r="D1023" s="2">
+        <v>0.96944444444444444</v>
+      </c>
+      <c r="E1023" s="2">
+        <v>0.96944444444444444</v>
+      </c>
+      <c r="F1023" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1023" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1023" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1023" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1023" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1023">
+        <v>10</v>
+      </c>
+      <c r="L1023">
+        <v>3</v>
+      </c>
+      <c r="M1023">
+        <v>8</v>
+      </c>
+      <c r="N1023">
+        <v>7</v>
+      </c>
+      <c r="O1023">
+        <v>2</v>
+      </c>
+      <c r="P1023">
+        <v>5</v>
+      </c>
+      <c r="Q1023">
+        <v>1691</v>
+      </c>
+      <c r="R1023">
+        <v>84</v>
+      </c>
+      <c r="T1023" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1023">
+        <v>17844</v>
+      </c>
+      <c r="V1023">
+        <v>1</v>
+      </c>
+      <c r="AC1023" s="5">
+        <f>IF(C1023=C1022, AC1022+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1023" s="5">
+        <f>IF(T1023="Loss",AD1022+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1023" s="5">
+        <f>IF(T1023="Win", AE1022+1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF1023" s="5">
+        <v>2.87</v>
+      </c>
+      <c r="AG1023" s="5">
+        <v>43</v>
+      </c>
+      <c r="AH1023" s="5">
+        <v>61</v>
+      </c>
+      <c r="AI1023" s="5">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8994A517-467D-4DD5-8370-D83204DD2B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A8146E-8212-4343-853C-9BF4CE67C8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6367" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6375" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -511,6 +511,9 @@
   <si>
     <t>Season Four. -Train +Anubis</t>
   </si>
+  <si>
+    <t>BC-&gt;S</t>
+  </si>
 </sst>
 </file>
 
@@ -598,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1023" totalsRowShown="0">
-  <autoFilter ref="A1:AI1023" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1024" totalsRowShown="0">
+  <autoFilter ref="A1:AI1024" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -953,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1023"/>
+  <dimension ref="A1:AI1024"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -89589,15 +89592,15 @@
         <v>1</v>
       </c>
       <c r="AC1018">
-        <f>IF(C1018=C1017, AC1017+1, 1)</f>
+        <f t="shared" ref="AC1018:AC1023" si="120">IF(C1018=C1017, AC1017+1, 1)</f>
         <v>1</v>
       </c>
       <c r="AD1018">
-        <f>IF(T1018="Loss",AD1017+1,0)</f>
+        <f t="shared" ref="AD1018:AD1023" si="121">IF(T1018="Loss",AD1017+1,0)</f>
         <v>0</v>
       </c>
       <c r="AE1018">
-        <f>IF(T1018="Win", AE1017+1, 0)</f>
+        <f t="shared" ref="AE1018:AE1023" si="122">IF(T1018="Win", AE1017+1, 0)</f>
         <v>1</v>
       </c>
     </row>
@@ -89666,15 +89669,15 @@
         <v>1</v>
       </c>
       <c r="AC1019">
-        <f>IF(C1019=C1018, AC1018+1, 1)</f>
+        <f t="shared" si="120"/>
         <v>1</v>
       </c>
       <c r="AD1019">
-        <f>IF(T1019="Loss",AD1018+1,0)</f>
+        <f t="shared" si="121"/>
         <v>0</v>
       </c>
       <c r="AE1019">
-        <f>IF(T1019="Win", AE1018+1, 0)</f>
+        <f t="shared" si="122"/>
         <v>2</v>
       </c>
       <c r="AF1019">
@@ -89752,15 +89755,15 @@
         <v>5</v>
       </c>
       <c r="AC1020">
-        <f>IF(C1020=C1019, AC1019+1, 1)</f>
+        <f t="shared" si="120"/>
         <v>1</v>
       </c>
       <c r="AD1020">
-        <f>IF(T1020="Loss",AD1019+1,0)</f>
+        <f t="shared" si="121"/>
         <v>0</v>
       </c>
       <c r="AE1020">
-        <f>IF(T1020="Win", AE1019+1, 0)</f>
+        <f t="shared" si="122"/>
         <v>3</v>
       </c>
     </row>
@@ -89832,15 +89835,15 @@
         <v>4</v>
       </c>
       <c r="AC1021">
-        <f>IF(C1021=C1020, AC1020+1, 1)</f>
+        <f t="shared" si="120"/>
         <v>1</v>
       </c>
       <c r="AD1021">
-        <f>IF(T1021="Loss",AD1020+1,0)</f>
+        <f t="shared" si="121"/>
         <v>1</v>
       </c>
       <c r="AE1021">
-        <f>IF(T1021="Win", AE1020+1, 0)</f>
+        <f t="shared" si="122"/>
         <v>0</v>
       </c>
     </row>
@@ -89912,15 +89915,15 @@
         <v>113</v>
       </c>
       <c r="AC1022">
-        <f>IF(C1022=C1021, AC1021+1, 1)</f>
+        <f t="shared" si="120"/>
         <v>2</v>
       </c>
       <c r="AD1022">
-        <f>IF(T1022="Loss",AD1021+1,0)</f>
+        <f t="shared" si="121"/>
         <v>2</v>
       </c>
       <c r="AE1022">
-        <f>IF(T1022="Win", AE1021+1, 0)</f>
+        <f t="shared" si="122"/>
         <v>0</v>
       </c>
     </row>
@@ -89988,30 +89991,108 @@
       <c r="V1023">
         <v>1</v>
       </c>
-      <c r="AC1023" s="5">
-        <f>IF(C1023=C1022, AC1022+1, 1)</f>
-        <v>1</v>
-      </c>
-      <c r="AD1023" s="5">
-        <f>IF(T1023="Loss",AD1022+1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE1023" s="5">
-        <f>IF(T1023="Win", AE1022+1, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="AF1023" s="5">
+      <c r="AC1023">
+        <f t="shared" si="120"/>
+        <v>1</v>
+      </c>
+      <c r="AD1023">
+        <f t="shared" si="121"/>
+        <v>0</v>
+      </c>
+      <c r="AE1023">
+        <f t="shared" si="122"/>
+        <v>1</v>
+      </c>
+      <c r="AF1023">
         <v>2.87</v>
       </c>
-      <c r="AG1023" s="5">
+      <c r="AG1023">
         <v>43</v>
       </c>
-      <c r="AH1023" s="5">
+      <c r="AH1023">
         <v>61</v>
       </c>
-      <c r="AI1023" s="5">
+      <c r="AI1023">
         <v>74</v>
       </c>
+    </row>
+    <row r="1024" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1024">
+        <v>1023</v>
+      </c>
+      <c r="B1024">
+        <v>2</v>
+      </c>
+      <c r="C1024" s="1">
+        <v>46094</v>
+      </c>
+      <c r="D1024" s="2">
+        <v>0.98750000000000004</v>
+      </c>
+      <c r="E1024" s="2">
+        <v>0.98750000000000004</v>
+      </c>
+      <c r="F1024" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1024" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1024" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1024" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1024" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1024">
+        <v>7</v>
+      </c>
+      <c r="L1024">
+        <v>2</v>
+      </c>
+      <c r="M1024">
+        <v>11</v>
+      </c>
+      <c r="N1024">
+        <v>5</v>
+      </c>
+      <c r="O1024">
+        <v>1</v>
+      </c>
+      <c r="P1024">
+        <v>2</v>
+      </c>
+      <c r="T1024" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1024" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1024">
+        <v>2</v>
+      </c>
+      <c r="AA1024" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC1024" s="5">
+        <f>IF(C1024=C1023, AC1023+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1024" s="5">
+        <f>IF(T1024="Loss",AD1023+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1024" s="5">
+        <f>IF(T1024="Win", AE1023+1, 0)</f>
+        <v>2</v>
+      </c>
+      <c r="AF1024" s="5"/>
+      <c r="AG1024" s="5"/>
+      <c r="AH1024" s="5"/>
+      <c r="AI1024" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A8146E-8212-4343-853C-9BF4CE67C8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAA1813-166F-4324-BEA0-D7346910DF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="4020" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6375" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6425" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -601,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1024" totalsRowShown="0">
-  <autoFilter ref="A1:AI1024" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1033" totalsRowShown="0">
+  <autoFilter ref="A1:AI1033" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -956,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1024"/>
+  <dimension ref="A1:AI1033"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -90077,22 +90077,662 @@
       <c r="AA1024" t="s">
         <v>117</v>
       </c>
-      <c r="AC1024" s="5">
-        <f>IF(C1024=C1023, AC1023+1, 1)</f>
-        <v>1</v>
-      </c>
-      <c r="AD1024" s="5">
-        <f>IF(T1024="Loss",AD1023+1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE1024" s="5">
-        <f>IF(T1024="Win", AE1023+1, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="AF1024" s="5"/>
-      <c r="AG1024" s="5"/>
-      <c r="AH1024" s="5"/>
-      <c r="AI1024" s="5"/>
+      <c r="AC1024">
+        <f t="shared" ref="AC1024:AC1029" si="123">IF(C1024=C1023, AC1023+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1024">
+        <f t="shared" ref="AD1024:AD1029" si="124">IF(T1024="Loss",AD1023+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1024">
+        <f t="shared" ref="AE1024:AE1029" si="125">IF(T1024="Win", AE1023+1, 0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1025">
+        <v>1024</v>
+      </c>
+      <c r="B1025">
+        <v>2</v>
+      </c>
+      <c r="C1025" s="1">
+        <v>46098</v>
+      </c>
+      <c r="D1025" s="2">
+        <v>0.89861111111111114</v>
+      </c>
+      <c r="E1025" s="2">
+        <v>0.89861111111111114</v>
+      </c>
+      <c r="F1025" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1025" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1025" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1025" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1025" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1025">
+        <v>0</v>
+      </c>
+      <c r="L1025">
+        <v>0</v>
+      </c>
+      <c r="M1025">
+        <v>6</v>
+      </c>
+      <c r="N1025">
+        <v>4</v>
+      </c>
+      <c r="O1025">
+        <v>2</v>
+      </c>
+      <c r="P1025">
+        <v>11</v>
+      </c>
+      <c r="Q1025">
+        <v>761</v>
+      </c>
+      <c r="R1025">
+        <v>42</v>
+      </c>
+      <c r="S1025">
+        <v>0</v>
+      </c>
+      <c r="T1025" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1025" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1025">
+        <v>2</v>
+      </c>
+      <c r="AC1025">
+        <f t="shared" si="123"/>
+        <v>1</v>
+      </c>
+      <c r="AD1025">
+        <f t="shared" si="124"/>
+        <v>1</v>
+      </c>
+      <c r="AE1025">
+        <f t="shared" si="125"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1026">
+        <v>1025</v>
+      </c>
+      <c r="B1026">
+        <v>2</v>
+      </c>
+      <c r="C1026" s="1">
+        <v>46098</v>
+      </c>
+      <c r="D1026" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E1026" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F1026" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1026" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1026" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1026" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1026">
+        <v>7</v>
+      </c>
+      <c r="L1026">
+        <v>2</v>
+      </c>
+      <c r="M1026">
+        <v>12</v>
+      </c>
+      <c r="N1026">
+        <v>1</v>
+      </c>
+      <c r="O1026">
+        <v>5</v>
+      </c>
+      <c r="P1026">
+        <v>7</v>
+      </c>
+      <c r="Q1026">
+        <v>1179</v>
+      </c>
+      <c r="R1026">
+        <v>65</v>
+      </c>
+      <c r="S1026">
+        <v>62</v>
+      </c>
+      <c r="T1026" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1026" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1026">
+        <v>2</v>
+      </c>
+      <c r="AC1026">
+        <f t="shared" si="123"/>
+        <v>2</v>
+      </c>
+      <c r="AD1026">
+        <f t="shared" si="124"/>
+        <v>2</v>
+      </c>
+      <c r="AE1026">
+        <f t="shared" si="125"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1027">
+        <v>1026</v>
+      </c>
+      <c r="B1027">
+        <v>2</v>
+      </c>
+      <c r="C1027" s="1">
+        <v>46098</v>
+      </c>
+      <c r="D1027" s="2">
+        <v>0.93611111111111112</v>
+      </c>
+      <c r="E1027" s="2">
+        <v>0.93611111111111112</v>
+      </c>
+      <c r="G1027" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1027" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1027" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1027">
+        <v>8</v>
+      </c>
+      <c r="L1027">
+        <v>7</v>
+      </c>
+      <c r="M1027">
+        <v>9</v>
+      </c>
+      <c r="N1027">
+        <v>12</v>
+      </c>
+      <c r="O1027">
+        <v>0</v>
+      </c>
+      <c r="P1027">
+        <v>8</v>
+      </c>
+      <c r="Q1027">
+        <v>2001</v>
+      </c>
+      <c r="R1027">
+        <v>83</v>
+      </c>
+      <c r="S1027">
+        <v>40</v>
+      </c>
+      <c r="T1027" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1027" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1027">
+        <v>2</v>
+      </c>
+      <c r="AC1027">
+        <f t="shared" si="123"/>
+        <v>3</v>
+      </c>
+      <c r="AD1027">
+        <f t="shared" si="124"/>
+        <v>3</v>
+      </c>
+      <c r="AE1027">
+        <f t="shared" si="125"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1028">
+        <v>1027</v>
+      </c>
+      <c r="B1028">
+        <v>2</v>
+      </c>
+      <c r="C1028" s="1">
+        <v>46101</v>
+      </c>
+      <c r="D1028" s="2">
+        <v>0.92291666666666672</v>
+      </c>
+      <c r="E1028" s="2">
+        <v>0.92291666666666672</v>
+      </c>
+      <c r="F1028" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1028" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1028" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1028" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1028" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1028">
+        <v>11</v>
+      </c>
+      <c r="L1028">
+        <v>2</v>
+      </c>
+      <c r="M1028">
+        <v>12</v>
+      </c>
+      <c r="N1028">
+        <v>8</v>
+      </c>
+      <c r="O1028">
+        <v>3</v>
+      </c>
+      <c r="P1028">
+        <v>8</v>
+      </c>
+      <c r="Q1028">
+        <v>1835</v>
+      </c>
+      <c r="R1028">
+        <v>76</v>
+      </c>
+      <c r="S1028">
+        <v>21</v>
+      </c>
+      <c r="T1028" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1028" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1028">
+        <v>2</v>
+      </c>
+      <c r="AC1028">
+        <f t="shared" si="123"/>
+        <v>1</v>
+      </c>
+      <c r="AD1028">
+        <f t="shared" si="124"/>
+        <v>0</v>
+      </c>
+      <c r="AE1028">
+        <f t="shared" si="125"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1029">
+        <v>1028</v>
+      </c>
+      <c r="B1029">
+        <v>2</v>
+      </c>
+      <c r="C1029" s="1">
+        <v>46101</v>
+      </c>
+      <c r="D1029" s="2">
+        <v>0.96111111111111114</v>
+      </c>
+      <c r="E1029" s="2">
+        <v>0.96111111111111114</v>
+      </c>
+      <c r="F1029" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1029" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1029" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1029" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1029" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1029">
+        <v>12</v>
+      </c>
+      <c r="L1029">
+        <v>1</v>
+      </c>
+      <c r="M1029">
+        <v>10</v>
+      </c>
+      <c r="N1029">
+        <v>10</v>
+      </c>
+      <c r="O1029">
+        <v>5</v>
+      </c>
+      <c r="P1029">
+        <v>4</v>
+      </c>
+      <c r="Q1029">
+        <v>2462</v>
+      </c>
+      <c r="R1029">
+        <v>117</v>
+      </c>
+      <c r="T1029" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1029" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1029">
+        <v>2</v>
+      </c>
+      <c r="AC1029">
+        <f t="shared" si="123"/>
+        <v>2</v>
+      </c>
+      <c r="AD1029">
+        <f t="shared" si="124"/>
+        <v>0</v>
+      </c>
+      <c r="AE1029">
+        <f t="shared" si="125"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1030">
+        <v>1029</v>
+      </c>
+      <c r="B1030">
+        <v>2</v>
+      </c>
+      <c r="C1030" s="1">
+        <v>46102</v>
+      </c>
+      <c r="D1030" s="2">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="E1030" s="2">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="F1030" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1030" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1030" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1030" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1030" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1030">
+        <v>3</v>
+      </c>
+      <c r="L1030">
+        <v>3</v>
+      </c>
+      <c r="M1030">
+        <v>3</v>
+      </c>
+      <c r="N1030">
+        <v>5</v>
+      </c>
+      <c r="O1030">
+        <v>9</v>
+      </c>
+      <c r="P1030">
+        <v>9</v>
+      </c>
+      <c r="Q1030">
+        <v>1317</v>
+      </c>
+      <c r="R1030">
+        <v>82</v>
+      </c>
+      <c r="S1030">
+        <v>25</v>
+      </c>
+      <c r="T1030" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1030" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1030">
+        <v>2</v>
+      </c>
+      <c r="AC1030">
+        <f>IF(C1030=C1029, AC1029+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1030">
+        <f>IF(T1030="Loss",AD1029+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1030">
+        <f>IF(T1030="Win", AE1029+1, 0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1031">
+        <v>1030</v>
+      </c>
+      <c r="B1031">
+        <v>2</v>
+      </c>
+      <c r="C1031" s="1">
+        <v>46102</v>
+      </c>
+      <c r="D1031" s="2">
+        <v>0.8881944444444444</v>
+      </c>
+      <c r="E1031" s="2">
+        <v>0.8881944444444444</v>
+      </c>
+      <c r="F1031" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1031" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1031" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1031" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1031" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1031">
+        <v>6</v>
+      </c>
+      <c r="L1031">
+        <v>0</v>
+      </c>
+      <c r="M1031">
+        <v>6</v>
+      </c>
+      <c r="N1031">
+        <v>12</v>
+      </c>
+      <c r="O1031">
+        <v>5</v>
+      </c>
+      <c r="P1031">
+        <v>8</v>
+      </c>
+      <c r="Q1031">
+        <v>1729</v>
+      </c>
+      <c r="R1031">
+        <v>78</v>
+      </c>
+      <c r="S1031">
+        <v>16</v>
+      </c>
+      <c r="T1031" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1031">
+        <v>10663</v>
+      </c>
+      <c r="V1031">
+        <v>2</v>
+      </c>
+      <c r="AC1031">
+        <f>IF(C1031=C1030, AC1030+1, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AD1031">
+        <f>IF(T1031="Loss",AD1030+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1031">
+        <f>IF(T1031="Win", AE1030+1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1032">
+        <v>1031</v>
+      </c>
+      <c r="B1032">
+        <v>2</v>
+      </c>
+      <c r="C1032" s="1">
+        <v>46102</v>
+      </c>
+      <c r="D1032" s="2">
+        <v>0.9145833333333333</v>
+      </c>
+      <c r="E1032" s="2">
+        <v>0.9145833333333333</v>
+      </c>
+      <c r="F1032" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1032" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1032" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1032" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1032">
+        <v>10</v>
+      </c>
+      <c r="L1032">
+        <v>5</v>
+      </c>
+      <c r="M1032">
+        <v>10</v>
+      </c>
+      <c r="N1032">
+        <v>3</v>
+      </c>
+      <c r="O1032">
+        <v>3</v>
+      </c>
+      <c r="P1032">
+        <v>5</v>
+      </c>
+      <c r="Q1032">
+        <v>1866</v>
+      </c>
+      <c r="R1032">
+        <v>109</v>
+      </c>
+      <c r="S1032">
+        <v>53</v>
+      </c>
+      <c r="T1032" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1032">
+        <v>10540</v>
+      </c>
+      <c r="V1032">
+        <v>2</v>
+      </c>
+      <c r="AC1032">
+        <f>IF(C1032=C1031, AC1031+1, 1)</f>
+        <v>3</v>
+      </c>
+      <c r="AD1032">
+        <f>IF(T1032="Loss",AD1031+1,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AE1032">
+        <f>IF(T1032="Win", AE1031+1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="C1033" s="1"/>
+      <c r="AC1033" s="5">
+        <f>IF(C1033=C1032, AC1032+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1033" s="5">
+        <f>IF(T1033="Loss",AD1032+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1033" s="5">
+        <f>IF(T1033="Win", AE1032+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF1033" s="5"/>
+      <c r="AG1033" s="5"/>
+      <c r="AH1033" s="5"/>
+      <c r="AI1033" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAA1813-166F-4324-BEA0-D7346910DF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9E05EC-A47B-4D83-9A7C-27D09AC28C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="4020" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6425" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6466" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -601,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1033" totalsRowShown="0">
-  <autoFilter ref="A1:AI1033" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1039" totalsRowShown="0">
+  <autoFilter ref="A1:AI1039" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -956,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1033"/>
+  <dimension ref="A1:AI1039"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -90546,15 +90546,15 @@
         <v>2</v>
       </c>
       <c r="AC1030">
-        <f>IF(C1030=C1029, AC1029+1, 1)</f>
+        <f t="shared" ref="AC1030:AC1035" si="126">IF(C1030=C1029, AC1029+1, 1)</f>
         <v>1</v>
       </c>
       <c r="AD1030">
-        <f>IF(T1030="Loss",AD1029+1,0)</f>
+        <f t="shared" ref="AD1030:AD1035" si="127">IF(T1030="Loss",AD1029+1,0)</f>
         <v>0</v>
       </c>
       <c r="AE1030">
-        <f>IF(T1030="Win", AE1029+1, 0)</f>
+        <f t="shared" ref="AE1030:AE1035" si="128">IF(T1030="Win", AE1029+1, 0)</f>
         <v>3</v>
       </c>
     </row>
@@ -90626,15 +90626,15 @@
         <v>2</v>
       </c>
       <c r="AC1031">
-        <f>IF(C1031=C1030, AC1030+1, 1)</f>
+        <f t="shared" si="126"/>
         <v>2</v>
       </c>
       <c r="AD1031">
-        <f>IF(T1031="Loss",AD1030+1,0)</f>
+        <f t="shared" si="127"/>
         <v>1</v>
       </c>
       <c r="AE1031">
-        <f>IF(T1031="Win", AE1030+1, 0)</f>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
     </row>
@@ -90703,36 +90703,538 @@
         <v>2</v>
       </c>
       <c r="AC1032">
-        <f>IF(C1032=C1031, AC1031+1, 1)</f>
+        <f t="shared" si="126"/>
         <v>3</v>
       </c>
       <c r="AD1032">
-        <f>IF(T1032="Loss",AD1031+1,0)</f>
+        <f t="shared" si="127"/>
         <v>2</v>
       </c>
       <c r="AE1032">
-        <f>IF(T1032="Win", AE1031+1, 0)</f>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
     </row>
     <row r="1033" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="C1033" s="1"/>
-      <c r="AC1033" s="5">
-        <f>IF(C1033=C1032, AC1032+1, 1)</f>
-        <v>1</v>
-      </c>
-      <c r="AD1033" s="5">
-        <f>IF(T1033="Loss",AD1032+1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE1033" s="5">
-        <f>IF(T1033="Win", AE1032+1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF1033" s="5"/>
-      <c r="AG1033" s="5"/>
-      <c r="AH1033" s="5"/>
-      <c r="AI1033" s="5"/>
+      <c r="A1033">
+        <v>1032</v>
+      </c>
+      <c r="B1033">
+        <v>2</v>
+      </c>
+      <c r="C1033" s="1">
+        <v>46105</v>
+      </c>
+      <c r="D1033" s="2">
+        <v>0.85069444444444442</v>
+      </c>
+      <c r="E1033" s="2">
+        <v>0.85069444444444442</v>
+      </c>
+      <c r="F1033" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1033" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1033" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1033" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1033" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1033">
+        <v>2</v>
+      </c>
+      <c r="L1033">
+        <v>1</v>
+      </c>
+      <c r="M1033">
+        <v>1</v>
+      </c>
+      <c r="N1033">
+        <v>11</v>
+      </c>
+      <c r="O1033">
+        <v>2</v>
+      </c>
+      <c r="P1033">
+        <v>4</v>
+      </c>
+      <c r="Q1033">
+        <v>1232</v>
+      </c>
+      <c r="R1033">
+        <v>88</v>
+      </c>
+      <c r="S1033">
+        <v>38</v>
+      </c>
+      <c r="T1033" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1033">
+        <v>10430</v>
+      </c>
+      <c r="V1033">
+        <v>2</v>
+      </c>
+      <c r="AC1033">
+        <f t="shared" si="126"/>
+        <v>1</v>
+      </c>
+      <c r="AD1033">
+        <f t="shared" si="127"/>
+        <v>0</v>
+      </c>
+      <c r="AE1033">
+        <f t="shared" si="128"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1034">
+        <v>1033</v>
+      </c>
+      <c r="B1034">
+        <v>2</v>
+      </c>
+      <c r="C1034" s="1">
+        <v>46105</v>
+      </c>
+      <c r="D1034" s="2">
+        <v>0.86944444444444446</v>
+      </c>
+      <c r="E1034" s="2">
+        <v>0.86944444444444446</v>
+      </c>
+      <c r="F1034" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1034" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1034" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1034" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1034" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1034">
+        <v>8</v>
+      </c>
+      <c r="L1034">
+        <v>3</v>
+      </c>
+      <c r="M1034">
+        <v>10</v>
+      </c>
+      <c r="N1034">
+        <v>12</v>
+      </c>
+      <c r="O1034">
+        <v>1</v>
+      </c>
+      <c r="P1034">
+        <v>8</v>
+      </c>
+      <c r="Q1034">
+        <v>2308</v>
+      </c>
+      <c r="R1034">
+        <v>96</v>
+      </c>
+      <c r="S1034">
+        <v>35</v>
+      </c>
+      <c r="T1034" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1034">
+        <v>10852</v>
+      </c>
+      <c r="V1034">
+        <v>2</v>
+      </c>
+      <c r="AC1034">
+        <f t="shared" si="126"/>
+        <v>2</v>
+      </c>
+      <c r="AD1034">
+        <f t="shared" si="127"/>
+        <v>0</v>
+      </c>
+      <c r="AE1034">
+        <f t="shared" si="128"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1035">
+        <v>1034</v>
+      </c>
+      <c r="B1035">
+        <v>2</v>
+      </c>
+      <c r="C1035" s="1">
+        <v>46105</v>
+      </c>
+      <c r="D1035" s="2">
+        <v>0.90138888888888891</v>
+      </c>
+      <c r="E1035" s="2">
+        <v>0.90138888888888891</v>
+      </c>
+      <c r="F1035" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1035" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1035" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1035" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1035" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q1035">
+        <v>3860</v>
+      </c>
+      <c r="R1035">
+        <v>128</v>
+      </c>
+      <c r="S1035">
+        <v>56</v>
+      </c>
+      <c r="T1035" t="s">
+        <v>65</v>
+      </c>
+      <c r="U1035">
+        <v>11278</v>
+      </c>
+      <c r="V1035">
+        <v>2</v>
+      </c>
+      <c r="AC1035">
+        <f t="shared" si="126"/>
+        <v>3</v>
+      </c>
+      <c r="AD1035">
+        <f t="shared" si="127"/>
+        <v>0</v>
+      </c>
+      <c r="AE1035">
+        <f t="shared" si="128"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1036">
+        <v>1035</v>
+      </c>
+      <c r="B1036">
+        <v>2</v>
+      </c>
+      <c r="C1036" s="1">
+        <v>46107</v>
+      </c>
+      <c r="D1036" s="2">
+        <v>0.82916666666666672</v>
+      </c>
+      <c r="E1036" s="2">
+        <v>0.82916666666666672</v>
+      </c>
+      <c r="F1036" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1036" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1036" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1036" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1036">
+        <v>4</v>
+      </c>
+      <c r="L1036">
+        <v>1</v>
+      </c>
+      <c r="M1036">
+        <v>9</v>
+      </c>
+      <c r="N1036">
+        <v>11</v>
+      </c>
+      <c r="O1036">
+        <v>6</v>
+      </c>
+      <c r="P1036">
+        <v>9</v>
+      </c>
+      <c r="Q1036">
+        <v>1753</v>
+      </c>
+      <c r="R1036">
+        <v>79</v>
+      </c>
+      <c r="S1036">
+        <v>33</v>
+      </c>
+      <c r="T1036" t="s">
+        <v>58</v>
+      </c>
+      <c r="V1036">
+        <v>2</v>
+      </c>
+      <c r="AC1036">
+        <f>IF(C1036=C1035, AC1035+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1036">
+        <f>IF(T1036="Loss",AD1035+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1036">
+        <f>IF(T1036="Win", AE1035+1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1037">
+        <v>1036</v>
+      </c>
+      <c r="B1037">
+        <v>2</v>
+      </c>
+      <c r="C1037" s="1">
+        <v>46109</v>
+      </c>
+      <c r="D1037" s="2">
+        <v>0.8569444444444444</v>
+      </c>
+      <c r="E1037" s="2">
+        <v>0.8569444444444444</v>
+      </c>
+      <c r="F1037" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1037" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1037" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1037" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1037" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1037">
+        <v>11</v>
+      </c>
+      <c r="L1037">
+        <v>2</v>
+      </c>
+      <c r="M1037">
+        <v>9</v>
+      </c>
+      <c r="N1037">
+        <v>10</v>
+      </c>
+      <c r="O1037">
+        <v>3</v>
+      </c>
+      <c r="P1037">
+        <v>9</v>
+      </c>
+      <c r="Q1037">
+        <v>2068</v>
+      </c>
+      <c r="R1037">
+        <v>89</v>
+      </c>
+      <c r="S1037">
+        <v>28</v>
+      </c>
+      <c r="T1037" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1037">
+        <v>11230</v>
+      </c>
+      <c r="V1037">
+        <v>2</v>
+      </c>
+      <c r="AC1037" s="5">
+        <f>IF(C1037=C1036, AC1036+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1037" s="5">
+        <f>IF(T1037="Loss",AD1036+1,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AE1037" s="5">
+        <f>IF(T1037="Win", AE1036+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF1037" s="5"/>
+      <c r="AG1037" s="5"/>
+      <c r="AH1037" s="5"/>
+      <c r="AI1037" s="5"/>
+    </row>
+    <row r="1038" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1038">
+        <v>1037</v>
+      </c>
+      <c r="B1038">
+        <v>2</v>
+      </c>
+      <c r="C1038" s="1">
+        <v>46109</v>
+      </c>
+      <c r="D1038" s="2">
+        <v>0.88402777777777775</v>
+      </c>
+      <c r="E1038" s="2">
+        <v>0.88402777777777775</v>
+      </c>
+      <c r="F1038" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1038" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1038" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1038" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1038" t="s">
+        <v>53</v>
+      </c>
+      <c r="T1038" t="s">
+        <v>65</v>
+      </c>
+      <c r="U1038">
+        <v>11124</v>
+      </c>
+      <c r="V1038">
+        <v>2</v>
+      </c>
+      <c r="AC1038" s="5">
+        <f>IF(C1038=C1037, AC1037+1, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AD1038" s="5">
+        <f>IF(T1038="Loss",AD1037+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1038" s="5">
+        <f>IF(T1038="Win", AE1037+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF1038" s="5"/>
+      <c r="AG1038" s="5"/>
+      <c r="AH1038" s="5"/>
+      <c r="AI1038" s="5"/>
+    </row>
+    <row r="1039" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1039">
+        <v>1038</v>
+      </c>
+      <c r="B1039">
+        <v>2</v>
+      </c>
+      <c r="C1039" s="1">
+        <v>46109</v>
+      </c>
+      <c r="D1039" s="2">
+        <v>0.92291666666666672</v>
+      </c>
+      <c r="E1039" s="2">
+        <v>0.92291666666666672</v>
+      </c>
+      <c r="F1039" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1039" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1039" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1039" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1039" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1039">
+        <v>13</v>
+      </c>
+      <c r="L1039">
+        <v>2</v>
+      </c>
+      <c r="M1039">
+        <v>11</v>
+      </c>
+      <c r="N1039">
+        <v>7</v>
+      </c>
+      <c r="O1039">
+        <v>1</v>
+      </c>
+      <c r="P1039">
+        <v>5</v>
+      </c>
+      <c r="Q1039">
+        <v>1908</v>
+      </c>
+      <c r="R1039">
+        <v>106</v>
+      </c>
+      <c r="S1039">
+        <v>40</v>
+      </c>
+      <c r="T1039" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1039">
+        <v>11071</v>
+      </c>
+      <c r="V1039">
+        <v>2</v>
+      </c>
+      <c r="AC1039" s="5">
+        <f>IF(C1039=C1038, AC1038+1, 1)</f>
+        <v>3</v>
+      </c>
+      <c r="AD1039" s="5">
+        <f>IF(T1039="Loss",AD1038+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1039" s="5">
+        <f>IF(T1039="Win", AE1038+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF1039" s="5"/>
+      <c r="AG1039" s="5"/>
+      <c r="AH1039" s="5"/>
+      <c r="AI1039" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9E05EC-A47B-4D83-9A7C-27D09AC28C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85619A57-A9FF-47C2-A69C-3CA9AD7A7409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="4020" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6466" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6498" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -601,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1039" totalsRowShown="0">
-  <autoFilter ref="A1:AI1039" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1044" totalsRowShown="0">
+  <autoFilter ref="A1:AI1044" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -956,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1039"/>
+  <dimension ref="A1:AI1044"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -90090,7 +90090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1025" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1025">
         <v>1024</v>
       </c>
@@ -90170,7 +90170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1026" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1026">
         <v>1025</v>
       </c>
@@ -90247,7 +90247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1027" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1027">
         <v>1026</v>
       </c>
@@ -90321,7 +90321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1028" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1028">
         <v>1027</v>
       </c>
@@ -90401,7 +90401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1029" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1029">
         <v>1028</v>
       </c>
@@ -90478,7 +90478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1030" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1030">
         <v>1029</v>
       </c>
@@ -90558,7 +90558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1031" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1031">
         <v>1030</v>
       </c>
@@ -90638,7 +90638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1032" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1032">
         <v>1031</v>
       </c>
@@ -90715,7 +90715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1033" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1033">
         <v>1032</v>
       </c>
@@ -90795,7 +90795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1034" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1034">
         <v>1033</v>
       </c>
@@ -90875,7 +90875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1035" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1035">
         <v>1034</v>
       </c>
@@ -90937,7 +90937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1036" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1036">
         <v>1035</v>
       </c>
@@ -90999,19 +90999,19 @@
         <v>2</v>
       </c>
       <c r="AC1036">
-        <f>IF(C1036=C1035, AC1035+1, 1)</f>
+        <f t="shared" ref="AC1036:AC1041" si="129">IF(C1036=C1035, AC1035+1, 1)</f>
         <v>1</v>
       </c>
       <c r="AD1036">
-        <f>IF(T1036="Loss",AD1035+1,0)</f>
+        <f t="shared" ref="AD1036:AD1041" si="130">IF(T1036="Loss",AD1035+1,0)</f>
         <v>1</v>
       </c>
       <c r="AE1036">
-        <f>IF(T1036="Win", AE1035+1, 0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1037" spans="1:35" x14ac:dyDescent="0.25">
+        <f t="shared" ref="AE1036:AE1041" si="131">IF(T1036="Win", AE1035+1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1037">
         <v>1036</v>
       </c>
@@ -91078,24 +91078,20 @@
       <c r="V1037">
         <v>2</v>
       </c>
-      <c r="AC1037" s="5">
-        <f>IF(C1037=C1036, AC1036+1, 1)</f>
-        <v>1</v>
-      </c>
-      <c r="AD1037" s="5">
-        <f>IF(T1037="Loss",AD1036+1,0)</f>
-        <v>2</v>
-      </c>
-      <c r="AE1037" s="5">
-        <f>IF(T1037="Win", AE1036+1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF1037" s="5"/>
-      <c r="AG1037" s="5"/>
-      <c r="AH1037" s="5"/>
-      <c r="AI1037" s="5"/>
-    </row>
-    <row r="1038" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AC1037">
+        <f t="shared" si="129"/>
+        <v>1</v>
+      </c>
+      <c r="AD1037">
+        <f t="shared" si="130"/>
+        <v>2</v>
+      </c>
+      <c r="AE1037">
+        <f t="shared" si="131"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1038">
         <v>1037</v>
       </c>
@@ -91135,24 +91131,20 @@
       <c r="V1038">
         <v>2</v>
       </c>
-      <c r="AC1038" s="5">
-        <f>IF(C1038=C1037, AC1037+1, 1)</f>
-        <v>2</v>
-      </c>
-      <c r="AD1038" s="5">
-        <f>IF(T1038="Loss",AD1037+1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE1038" s="5">
-        <f>IF(T1038="Win", AE1037+1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF1038" s="5"/>
-      <c r="AG1038" s="5"/>
-      <c r="AH1038" s="5"/>
-      <c r="AI1038" s="5"/>
-    </row>
-    <row r="1039" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AC1038">
+        <f t="shared" si="129"/>
+        <v>2</v>
+      </c>
+      <c r="AD1038">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="AE1038">
+        <f t="shared" si="131"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1039">
         <v>1038</v>
       </c>
@@ -91219,22 +91211,423 @@
       <c r="V1039">
         <v>2</v>
       </c>
-      <c r="AC1039" s="5">
-        <f>IF(C1039=C1038, AC1038+1, 1)</f>
-        <v>3</v>
-      </c>
-      <c r="AD1039" s="5">
-        <f>IF(T1039="Loss",AD1038+1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AE1039" s="5">
-        <f>IF(T1039="Win", AE1038+1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF1039" s="5"/>
-      <c r="AG1039" s="5"/>
-      <c r="AH1039" s="5"/>
-      <c r="AI1039" s="5"/>
+      <c r="AC1039">
+        <f t="shared" si="129"/>
+        <v>3</v>
+      </c>
+      <c r="AD1039">
+        <f t="shared" si="130"/>
+        <v>1</v>
+      </c>
+      <c r="AE1039">
+        <f t="shared" si="131"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1040">
+        <v>1039</v>
+      </c>
+      <c r="B1040">
+        <v>1</v>
+      </c>
+      <c r="C1040" s="1">
+        <v>46112</v>
+      </c>
+      <c r="D1040" s="2">
+        <v>0.94930555555555551</v>
+      </c>
+      <c r="E1040" s="2">
+        <v>0.94930555555555551</v>
+      </c>
+      <c r="F1040" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1040" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1040" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1040" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1040" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1040">
+        <v>10</v>
+      </c>
+      <c r="L1040">
+        <v>4</v>
+      </c>
+      <c r="M1040">
+        <v>9</v>
+      </c>
+      <c r="N1040">
+        <v>9</v>
+      </c>
+      <c r="O1040">
+        <v>0</v>
+      </c>
+      <c r="P1040">
+        <v>7</v>
+      </c>
+      <c r="Q1040">
+        <v>1915</v>
+      </c>
+      <c r="R1040">
+        <v>83</v>
+      </c>
+      <c r="S1040">
+        <v>42</v>
+      </c>
+      <c r="T1040" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1040" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1040">
+        <v>2</v>
+      </c>
+      <c r="AC1040">
+        <f t="shared" si="129"/>
+        <v>1</v>
+      </c>
+      <c r="AD1040">
+        <f t="shared" si="130"/>
+        <v>2</v>
+      </c>
+      <c r="AE1040">
+        <f t="shared" si="131"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1041">
+        <v>1040</v>
+      </c>
+      <c r="B1041">
+        <v>1</v>
+      </c>
+      <c r="C1041" s="1">
+        <v>46113</v>
+      </c>
+      <c r="D1041" s="2">
+        <v>0.95902777777777781</v>
+      </c>
+      <c r="E1041" s="2">
+        <v>0.95902777777777781</v>
+      </c>
+      <c r="F1041" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1041" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1041" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1041" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1041" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1041">
+        <v>9</v>
+      </c>
+      <c r="L1041">
+        <v>4</v>
+      </c>
+      <c r="M1041">
+        <v>10</v>
+      </c>
+      <c r="N1041">
+        <v>10</v>
+      </c>
+      <c r="O1041">
+        <v>2</v>
+      </c>
+      <c r="P1041">
+        <v>7</v>
+      </c>
+      <c r="R1041">
+        <v>81</v>
+      </c>
+      <c r="S1041">
+        <v>36</v>
+      </c>
+      <c r="T1041" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1041" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1041">
+        <v>2</v>
+      </c>
+      <c r="AC1041">
+        <f t="shared" si="129"/>
+        <v>1</v>
+      </c>
+      <c r="AD1041">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="AE1041">
+        <f t="shared" si="131"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1042">
+        <v>1041</v>
+      </c>
+      <c r="B1042">
+        <v>2</v>
+      </c>
+      <c r="C1042" s="1">
+        <v>46115</v>
+      </c>
+      <c r="D1042" s="2">
+        <v>0.98263888888888884</v>
+      </c>
+      <c r="E1042" s="2">
+        <v>0.98263888888888884</v>
+      </c>
+      <c r="F1042" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1042" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1042" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1042" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1042" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1042">
+        <v>4</v>
+      </c>
+      <c r="L1042">
+        <v>2</v>
+      </c>
+      <c r="M1042">
+        <v>4</v>
+      </c>
+      <c r="N1042">
+        <v>9</v>
+      </c>
+      <c r="O1042">
+        <v>4</v>
+      </c>
+      <c r="P1042">
+        <v>10</v>
+      </c>
+      <c r="Q1042">
+        <v>1823</v>
+      </c>
+      <c r="R1042">
+        <v>113</v>
+      </c>
+      <c r="S1042">
+        <v>46</v>
+      </c>
+      <c r="T1042" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1042">
+        <v>10768</v>
+      </c>
+      <c r="V1042">
+        <v>2</v>
+      </c>
+      <c r="AC1042">
+        <f>IF(C1042=C1041, AC1041+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1042">
+        <f>IF(T1042="Loss",AD1041+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1042">
+        <f>IF(T1042="Win", AE1041+1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1043">
+        <v>1042</v>
+      </c>
+      <c r="B1043">
+        <v>2</v>
+      </c>
+      <c r="C1043" s="1">
+        <v>46117</v>
+      </c>
+      <c r="D1043" s="2">
+        <v>0.88402777777777775</v>
+      </c>
+      <c r="E1043" s="2">
+        <v>0.88402777777777775</v>
+      </c>
+      <c r="F1043" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1043" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1043" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1043" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1043" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1043">
+        <v>11</v>
+      </c>
+      <c r="L1043">
+        <v>1</v>
+      </c>
+      <c r="M1043">
+        <v>11</v>
+      </c>
+      <c r="N1043">
+        <v>5</v>
+      </c>
+      <c r="O1043">
+        <v>2</v>
+      </c>
+      <c r="P1043">
+        <v>4</v>
+      </c>
+      <c r="Q1043">
+        <v>1862</v>
+      </c>
+      <c r="R1043">
+        <v>103</v>
+      </c>
+      <c r="S1043">
+        <v>12</v>
+      </c>
+      <c r="T1043" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1043">
+        <v>10390</v>
+      </c>
+      <c r="V1043">
+        <v>2</v>
+      </c>
+      <c r="AC1043" s="5">
+        <f>IF(C1043=C1042, AC1042+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1043" s="5">
+        <f>IF(T1043="Loss",AD1042+1,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AE1043" s="5">
+        <f>IF(T1043="Win", AE1042+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF1043" s="5"/>
+      <c r="AG1043" s="5"/>
+      <c r="AH1043" s="5"/>
+      <c r="AI1043" s="5"/>
+    </row>
+    <row r="1044" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1044">
+        <v>1043</v>
+      </c>
+      <c r="B1044">
+        <v>2</v>
+      </c>
+      <c r="C1044" s="1">
+        <v>46117</v>
+      </c>
+      <c r="D1044" s="2">
+        <v>0.90833333333333333</v>
+      </c>
+      <c r="E1044" s="2">
+        <v>0.90833333333333333</v>
+      </c>
+      <c r="F1044" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1044" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1044" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1044" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1044" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1044">
+        <v>9</v>
+      </c>
+      <c r="L1044">
+        <v>2</v>
+      </c>
+      <c r="M1044">
+        <v>7</v>
+      </c>
+      <c r="N1044">
+        <v>11</v>
+      </c>
+      <c r="O1044">
+        <v>7</v>
+      </c>
+      <c r="P1044">
+        <v>7</v>
+      </c>
+      <c r="Q1044">
+        <v>2107</v>
+      </c>
+      <c r="R1044">
+        <v>91</v>
+      </c>
+      <c r="S1044">
+        <v>45</v>
+      </c>
+      <c r="T1044" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1044">
+        <v>10022</v>
+      </c>
+      <c r="V1044">
+        <v>2</v>
+      </c>
+      <c r="AC1044" s="5">
+        <f>IF(C1044=C1043, AC1043+1, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AD1044" s="5">
+        <f>IF(T1044="Loss",AD1043+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1044" s="5">
+        <f>IF(T1044="Win", AE1043+1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF1044" s="5"/>
+      <c r="AG1044" s="5"/>
+      <c r="AH1044" s="5"/>
+      <c r="AI1044" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85619A57-A9FF-47C2-A69C-3CA9AD7A7409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C08A97-5A31-4D82-9B7D-2AAD14246974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="4020" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6498" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6551" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -601,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1044" totalsRowShown="0">
-  <autoFilter ref="A1:AI1044" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1053" totalsRowShown="0">
+  <autoFilter ref="A1:AI1053" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -956,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1044"/>
+  <dimension ref="A1:AI1053"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -91449,15 +91449,15 @@
         <v>2</v>
       </c>
       <c r="AC1042">
-        <f>IF(C1042=C1041, AC1041+1, 1)</f>
+        <f t="shared" ref="AC1042:AC1049" si="132">IF(C1042=C1041, AC1041+1, 1)</f>
         <v>1</v>
       </c>
       <c r="AD1042">
-        <f>IF(T1042="Loss",AD1041+1,0)</f>
+        <f t="shared" ref="AD1042:AD1049" si="133">IF(T1042="Loss",AD1041+1,0)</f>
         <v>1</v>
       </c>
       <c r="AE1042">
-        <f>IF(T1042="Win", AE1041+1, 0)</f>
+        <f t="shared" ref="AE1042:AE1049" si="134">IF(T1042="Win", AE1041+1, 0)</f>
         <v>0</v>
       </c>
     </row>
@@ -91528,22 +91528,18 @@
       <c r="V1043">
         <v>2</v>
       </c>
-      <c r="AC1043" s="5">
-        <f>IF(C1043=C1042, AC1042+1, 1)</f>
-        <v>1</v>
-      </c>
-      <c r="AD1043" s="5">
-        <f>IF(T1043="Loss",AD1042+1,0)</f>
-        <v>2</v>
-      </c>
-      <c r="AE1043" s="5">
-        <f>IF(T1043="Win", AE1042+1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF1043" s="5"/>
-      <c r="AG1043" s="5"/>
-      <c r="AH1043" s="5"/>
-      <c r="AI1043" s="5"/>
+      <c r="AC1043">
+        <f t="shared" si="132"/>
+        <v>1</v>
+      </c>
+      <c r="AD1043">
+        <f t="shared" si="133"/>
+        <v>2</v>
+      </c>
+      <c r="AE1043">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="1044" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1044">
@@ -91612,22 +91608,727 @@
       <c r="V1044">
         <v>2</v>
       </c>
-      <c r="AC1044" s="5">
-        <f>IF(C1044=C1043, AC1043+1, 1)</f>
-        <v>2</v>
-      </c>
-      <c r="AD1044" s="5">
-        <f>IF(T1044="Loss",AD1043+1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE1044" s="5">
-        <f>IF(T1044="Win", AE1043+1, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="AF1044" s="5"/>
-      <c r="AG1044" s="5"/>
-      <c r="AH1044" s="5"/>
-      <c r="AI1044" s="5"/>
+      <c r="AC1044">
+        <f t="shared" si="132"/>
+        <v>2</v>
+      </c>
+      <c r="AD1044">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="AE1044">
+        <f t="shared" si="134"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1045">
+        <v>1044</v>
+      </c>
+      <c r="B1045">
+        <v>1</v>
+      </c>
+      <c r="C1045" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D1045" s="2">
+        <v>0.92152777777777772</v>
+      </c>
+      <c r="E1045" s="2">
+        <v>0.92152777777777772</v>
+      </c>
+      <c r="F1045" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1045" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1045" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1045" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1045">
+        <v>9</v>
+      </c>
+      <c r="L1045">
+        <v>2</v>
+      </c>
+      <c r="M1045">
+        <v>8</v>
+      </c>
+      <c r="N1045">
+        <v>2</v>
+      </c>
+      <c r="O1045">
+        <v>4</v>
+      </c>
+      <c r="P1045">
+        <v>2</v>
+      </c>
+      <c r="Q1045">
+        <v>1226</v>
+      </c>
+      <c r="R1045">
+        <v>76</v>
+      </c>
+      <c r="T1045" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1045">
+        <v>17527</v>
+      </c>
+      <c r="V1045">
+        <v>2</v>
+      </c>
+      <c r="AC1045">
+        <f t="shared" si="132"/>
+        <v>1</v>
+      </c>
+      <c r="AD1045">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="AE1045">
+        <f t="shared" si="134"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1046">
+        <v>1045</v>
+      </c>
+      <c r="B1046">
+        <v>1</v>
+      </c>
+      <c r="C1046" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D1046" s="2">
+        <v>0.94166666666666665</v>
+      </c>
+      <c r="E1046" s="2">
+        <v>0.94166666666666665</v>
+      </c>
+      <c r="F1046" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1046" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1046" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1046" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1046" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1046">
+        <v>7</v>
+      </c>
+      <c r="L1046">
+        <v>1</v>
+      </c>
+      <c r="M1046">
+        <v>4</v>
+      </c>
+      <c r="N1046">
+        <v>9</v>
+      </c>
+      <c r="O1046">
+        <v>3</v>
+      </c>
+      <c r="P1046">
+        <v>6</v>
+      </c>
+      <c r="Q1046">
+        <v>1175</v>
+      </c>
+      <c r="R1046">
+        <v>58</v>
+      </c>
+      <c r="S1046">
+        <v>18</v>
+      </c>
+      <c r="T1046" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1046">
+        <v>17916</v>
+      </c>
+      <c r="V1046">
+        <v>2</v>
+      </c>
+      <c r="AC1046">
+        <f t="shared" si="132"/>
+        <v>2</v>
+      </c>
+      <c r="AD1046">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="AE1046">
+        <f t="shared" si="134"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1047">
+        <v>1046</v>
+      </c>
+      <c r="B1047">
+        <v>2</v>
+      </c>
+      <c r="C1047" s="1">
+        <v>46123</v>
+      </c>
+      <c r="D1047" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E1047" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="F1047" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1047" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1047" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1047" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q1047">
+        <v>938</v>
+      </c>
+      <c r="R1047">
+        <v>55</v>
+      </c>
+      <c r="S1047">
+        <v>0</v>
+      </c>
+      <c r="T1047" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1047">
+        <v>10373</v>
+      </c>
+      <c r="V1047">
+        <v>2</v>
+      </c>
+      <c r="AC1047">
+        <f t="shared" si="132"/>
+        <v>1</v>
+      </c>
+      <c r="AD1047">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="AE1047">
+        <f t="shared" si="134"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1048">
+        <v>1047</v>
+      </c>
+      <c r="B1048">
+        <v>2</v>
+      </c>
+      <c r="C1048" s="1">
+        <v>46123</v>
+      </c>
+      <c r="D1048" s="2">
+        <v>0.8354166666666667</v>
+      </c>
+      <c r="E1048" s="2">
+        <v>0.8354166666666667</v>
+      </c>
+      <c r="F1048" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1048" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1048" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1048" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1048" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1048">
+        <v>7</v>
+      </c>
+      <c r="L1048">
+        <v>3</v>
+      </c>
+      <c r="M1048">
+        <v>11</v>
+      </c>
+      <c r="N1048">
+        <v>3</v>
+      </c>
+      <c r="O1048">
+        <v>1</v>
+      </c>
+      <c r="P1048">
+        <v>5</v>
+      </c>
+      <c r="Q1048">
+        <v>1129</v>
+      </c>
+      <c r="R1048">
+        <v>59</v>
+      </c>
+      <c r="S1048">
+        <v>10</v>
+      </c>
+      <c r="T1048" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1048">
+        <v>10745</v>
+      </c>
+      <c r="V1048">
+        <v>2</v>
+      </c>
+      <c r="AC1048">
+        <f t="shared" si="132"/>
+        <v>2</v>
+      </c>
+      <c r="AD1048">
+        <f t="shared" si="133"/>
+        <v>1</v>
+      </c>
+      <c r="AE1048">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1049">
+        <v>1048</v>
+      </c>
+      <c r="B1049">
+        <v>2</v>
+      </c>
+      <c r="C1049" s="1">
+        <v>46123</v>
+      </c>
+      <c r="D1049" s="2">
+        <v>0.85833333333333328</v>
+      </c>
+      <c r="E1049" s="2">
+        <v>0.85833333333333328</v>
+      </c>
+      <c r="F1049" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1049" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1049" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1049" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1049" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1049">
+        <v>13</v>
+      </c>
+      <c r="L1049">
+        <v>3</v>
+      </c>
+      <c r="M1049">
+        <v>6</v>
+      </c>
+      <c r="N1049">
+        <v>8</v>
+      </c>
+      <c r="O1049">
+        <v>3</v>
+      </c>
+      <c r="P1049">
+        <v>4</v>
+      </c>
+      <c r="Q1049">
+        <v>2140</v>
+      </c>
+      <c r="R1049">
+        <v>112</v>
+      </c>
+      <c r="S1049">
+        <v>38</v>
+      </c>
+      <c r="T1049" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1049">
+        <v>10449</v>
+      </c>
+      <c r="V1049">
+        <v>2</v>
+      </c>
+      <c r="AC1049">
+        <f t="shared" si="132"/>
+        <v>3</v>
+      </c>
+      <c r="AD1049">
+        <f t="shared" si="133"/>
+        <v>0</v>
+      </c>
+      <c r="AE1049">
+        <f t="shared" si="134"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1050">
+        <v>1049</v>
+      </c>
+      <c r="B1050">
+        <v>1</v>
+      </c>
+      <c r="C1050" s="1">
+        <v>46124</v>
+      </c>
+      <c r="D1050" s="2">
+        <v>0.90972222222222221</v>
+      </c>
+      <c r="E1050" s="2">
+        <v>0.90972222222222221</v>
+      </c>
+      <c r="F1050" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1050" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1050" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1050" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1050" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1050">
+        <v>11</v>
+      </c>
+      <c r="L1050">
+        <v>6</v>
+      </c>
+      <c r="M1050">
+        <v>10</v>
+      </c>
+      <c r="N1050">
+        <v>6</v>
+      </c>
+      <c r="O1050">
+        <v>4</v>
+      </c>
+      <c r="P1050">
+        <v>6</v>
+      </c>
+      <c r="Q1050">
+        <v>2019</v>
+      </c>
+      <c r="R1050">
+        <v>96</v>
+      </c>
+      <c r="S1050">
+        <v>52</v>
+      </c>
+      <c r="T1050" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1050">
+        <v>18317</v>
+      </c>
+      <c r="V1050">
+        <v>2</v>
+      </c>
+      <c r="AC1050">
+        <f>IF(C1050=C1049, AC1049+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1050">
+        <f>IF(T1050="Loss",AD1049+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1050">
+        <f>IF(T1050="Win", AE1049+1, 0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1051">
+        <v>1050</v>
+      </c>
+      <c r="B1051">
+        <v>1</v>
+      </c>
+      <c r="C1051" s="1">
+        <v>46124</v>
+      </c>
+      <c r="D1051" s="2">
+        <v>0.9375</v>
+      </c>
+      <c r="E1051" s="2">
+        <v>0.9375</v>
+      </c>
+      <c r="F1051" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1051" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1051" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1051" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1051" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1051">
+        <v>2</v>
+      </c>
+      <c r="L1051">
+        <v>4</v>
+      </c>
+      <c r="M1051">
+        <v>6</v>
+      </c>
+      <c r="N1051">
+        <v>10</v>
+      </c>
+      <c r="O1051">
+        <v>5</v>
+      </c>
+      <c r="P1051">
+        <v>9</v>
+      </c>
+      <c r="Q1051">
+        <v>1937</v>
+      </c>
+      <c r="R1051">
+        <v>107</v>
+      </c>
+      <c r="S1051">
+        <v>33</v>
+      </c>
+      <c r="T1051" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1051">
+        <v>18733</v>
+      </c>
+      <c r="V1051">
+        <v>2</v>
+      </c>
+      <c r="AC1051">
+        <f>IF(C1051=C1050, AC1050+1, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AD1051">
+        <f>IF(T1051="Loss",AD1050+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1051">
+        <f>IF(T1051="Win", AE1050+1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1052">
+        <v>1051</v>
+      </c>
+      <c r="B1052">
+        <v>1</v>
+      </c>
+      <c r="C1052" s="1">
+        <v>46125</v>
+      </c>
+      <c r="D1052" s="2">
+        <v>0.91249999999999998</v>
+      </c>
+      <c r="E1052" s="2">
+        <v>0.91249999999999998</v>
+      </c>
+      <c r="F1052" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1052" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1052" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1052" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1052" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1052">
+        <v>4</v>
+      </c>
+      <c r="L1052">
+        <v>1</v>
+      </c>
+      <c r="M1052">
+        <v>3</v>
+      </c>
+      <c r="N1052">
+        <v>6</v>
+      </c>
+      <c r="O1052">
+        <v>4</v>
+      </c>
+      <c r="P1052">
+        <v>11</v>
+      </c>
+      <c r="Q1052">
+        <v>1429</v>
+      </c>
+      <c r="R1052">
+        <v>89</v>
+      </c>
+      <c r="S1052">
+        <v>60</v>
+      </c>
+      <c r="T1052" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1052">
+        <v>18615</v>
+      </c>
+      <c r="V1052">
+        <v>1</v>
+      </c>
+      <c r="AA1052" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC1052" s="5">
+        <f>IF(C1052=C1051, AC1051+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1052" s="5">
+        <f>IF(T1052="Loss",AD1051+1,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AE1052" s="5">
+        <f>IF(T1052="Win", AE1051+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF1052" s="5">
+        <v>-1.4</v>
+      </c>
+      <c r="AG1052" s="5">
+        <v>35</v>
+      </c>
+      <c r="AH1052" s="5">
+        <v>37</v>
+      </c>
+      <c r="AI1052" s="5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1053">
+        <v>1052</v>
+      </c>
+      <c r="B1053">
+        <v>1</v>
+      </c>
+      <c r="C1053" s="1">
+        <v>46125</v>
+      </c>
+      <c r="D1053" s="2">
+        <v>0.93541666666666667</v>
+      </c>
+      <c r="E1053" s="2">
+        <v>0.93541666666666667</v>
+      </c>
+      <c r="F1053" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1053" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1053" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1053" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1053" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1053">
+        <v>9</v>
+      </c>
+      <c r="L1053">
+        <v>1</v>
+      </c>
+      <c r="M1053">
+        <v>9</v>
+      </c>
+      <c r="N1053">
+        <v>9</v>
+      </c>
+      <c r="O1053">
+        <v>3</v>
+      </c>
+      <c r="P1053">
+        <v>8</v>
+      </c>
+      <c r="R1053">
+        <v>82</v>
+      </c>
+      <c r="S1053">
+        <v>11</v>
+      </c>
+      <c r="T1053" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1053">
+        <v>18493</v>
+      </c>
+      <c r="V1053">
+        <v>1</v>
+      </c>
+      <c r="AC1053" s="5">
+        <f>IF(C1053=C1052, AC1052+1, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AD1053" s="5">
+        <f>IF(T1053="Loss",AD1052+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1053" s="5">
+        <f>IF(T1053="Win", AE1052+1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF1053" s="5"/>
+      <c r="AG1053" s="5"/>
+      <c r="AH1053" s="5"/>
+      <c r="AI1053" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C08A97-5A31-4D82-9B7D-2AAD14246974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0E22C2-5E78-4203-BD13-0D61B6127BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="4020" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6551" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -548,13 +548,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -601,8 +600,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1053" totalsRowShown="0">
-  <autoFilter ref="A1:AI1053" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1061" totalsRowShown="0">
+  <autoFilter ref="A1:AI1061" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -956,7 +955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1053"/>
+  <dimension ref="A1:AI1061"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -92062,15 +92061,15 @@
         <v>2</v>
       </c>
       <c r="AC1050">
-        <f>IF(C1050=C1049, AC1049+1, 1)</f>
+        <f t="shared" ref="AC1050:AC1056" si="135">IF(C1050=C1049, AC1049+1, 1)</f>
         <v>1</v>
       </c>
       <c r="AD1050">
-        <f>IF(T1050="Loss",AD1049+1,0)</f>
+        <f t="shared" ref="AD1050:AD1056" si="136">IF(T1050="Loss",AD1049+1,0)</f>
         <v>0</v>
       </c>
       <c r="AE1050">
-        <f>IF(T1050="Win", AE1049+1, 0)</f>
+        <f t="shared" ref="AE1050:AE1056" si="137">IF(T1050="Win", AE1049+1, 0)</f>
         <v>2</v>
       </c>
     </row>
@@ -92142,15 +92141,15 @@
         <v>2</v>
       </c>
       <c r="AC1051">
-        <f>IF(C1051=C1050, AC1050+1, 1)</f>
+        <f t="shared" si="135"/>
         <v>2</v>
       </c>
       <c r="AD1051">
-        <f>IF(T1051="Loss",AD1050+1,0)</f>
+        <f t="shared" si="136"/>
         <v>1</v>
       </c>
       <c r="AE1051">
-        <f>IF(T1051="Win", AE1050+1, 0)</f>
+        <f t="shared" si="137"/>
         <v>0</v>
       </c>
     </row>
@@ -92224,28 +92223,28 @@
       <c r="AA1052" t="s">
         <v>40</v>
       </c>
-      <c r="AC1052" s="5">
-        <f>IF(C1052=C1051, AC1051+1, 1)</f>
-        <v>1</v>
-      </c>
-      <c r="AD1052" s="5">
-        <f>IF(T1052="Loss",AD1051+1,0)</f>
-        <v>2</v>
-      </c>
-      <c r="AE1052" s="5">
-        <f>IF(T1052="Win", AE1051+1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF1052" s="5">
+      <c r="AC1052">
+        <f t="shared" si="135"/>
+        <v>1</v>
+      </c>
+      <c r="AD1052">
+        <f t="shared" si="136"/>
+        <v>2</v>
+      </c>
+      <c r="AE1052">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+      <c r="AF1052">
         <v>-1.4</v>
       </c>
-      <c r="AG1052" s="5">
+      <c r="AG1052">
         <v>35</v>
       </c>
-      <c r="AH1052" s="5">
+      <c r="AH1052">
         <v>37</v>
       </c>
-      <c r="AI1052" s="5">
+      <c r="AI1052">
         <v>54</v>
       </c>
     </row>
@@ -92313,22 +92312,661 @@
       <c r="V1053">
         <v>1</v>
       </c>
-      <c r="AC1053" s="5">
-        <f>IF(C1053=C1052, AC1052+1, 1)</f>
-        <v>2</v>
-      </c>
-      <c r="AD1053" s="5">
-        <f>IF(T1053="Loss",AD1052+1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE1053" s="5">
-        <f>IF(T1053="Win", AE1052+1, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="AF1053" s="5"/>
-      <c r="AG1053" s="5"/>
-      <c r="AH1053" s="5"/>
-      <c r="AI1053" s="5"/>
+      <c r="AC1053">
+        <f t="shared" si="135"/>
+        <v>2</v>
+      </c>
+      <c r="AD1053">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="AE1053">
+        <f t="shared" si="137"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1054">
+        <v>1053</v>
+      </c>
+      <c r="B1054">
+        <v>2</v>
+      </c>
+      <c r="C1054" s="1">
+        <v>46127</v>
+      </c>
+      <c r="D1054" s="2">
+        <v>0.89444444444444449</v>
+      </c>
+      <c r="E1054" s="2">
+        <v>0.89444444444444449</v>
+      </c>
+      <c r="F1054" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1054" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1054" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1054" t="s">
+        <v>87</v>
+      </c>
+      <c r="K1054">
+        <v>11</v>
+      </c>
+      <c r="L1054">
+        <v>5</v>
+      </c>
+      <c r="M1054">
+        <v>10</v>
+      </c>
+      <c r="N1054">
+        <v>5</v>
+      </c>
+      <c r="O1054">
+        <v>1</v>
+      </c>
+      <c r="P1054">
+        <v>6</v>
+      </c>
+      <c r="Q1054">
+        <v>2048</v>
+      </c>
+      <c r="R1054">
+        <v>107</v>
+      </c>
+      <c r="S1054">
+        <v>37</v>
+      </c>
+      <c r="T1054" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1054">
+        <v>10805</v>
+      </c>
+      <c r="V1054">
+        <v>2</v>
+      </c>
+      <c r="AC1054">
+        <f t="shared" si="135"/>
+        <v>1</v>
+      </c>
+      <c r="AD1054">
+        <f t="shared" si="136"/>
+        <v>1</v>
+      </c>
+      <c r="AE1054">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1055">
+        <v>1054</v>
+      </c>
+      <c r="B1055">
+        <v>2</v>
+      </c>
+      <c r="C1055" s="1">
+        <v>46128</v>
+      </c>
+      <c r="D1055" s="2">
+        <v>0.90902777777777777</v>
+      </c>
+      <c r="E1055" s="2">
+        <v>0.90902777777777777</v>
+      </c>
+      <c r="F1055" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1055" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1055" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1055" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1055" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1055">
+        <v>13</v>
+      </c>
+      <c r="L1055">
+        <v>1</v>
+      </c>
+      <c r="M1055">
+        <v>10</v>
+      </c>
+      <c r="N1055">
+        <v>6</v>
+      </c>
+      <c r="O1055">
+        <v>3</v>
+      </c>
+      <c r="P1055">
+        <v>5</v>
+      </c>
+      <c r="Q1055">
+        <v>1991</v>
+      </c>
+      <c r="R1055">
+        <v>94</v>
+      </c>
+      <c r="S1055">
+        <v>42</v>
+      </c>
+      <c r="T1055" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1055">
+        <v>10453</v>
+      </c>
+      <c r="V1055">
+        <v>2</v>
+      </c>
+      <c r="AC1055">
+        <f t="shared" si="135"/>
+        <v>1</v>
+      </c>
+      <c r="AD1055">
+        <f t="shared" si="136"/>
+        <v>2</v>
+      </c>
+      <c r="AE1055">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1056">
+        <v>1055</v>
+      </c>
+      <c r="B1056">
+        <v>2</v>
+      </c>
+      <c r="C1056" s="1">
+        <v>46128</v>
+      </c>
+      <c r="D1056" s="2">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="E1056" s="2">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="F1056" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1056" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1056" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1056" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1056" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1056">
+        <v>6</v>
+      </c>
+      <c r="L1056">
+        <v>5</v>
+      </c>
+      <c r="M1056">
+        <v>8</v>
+      </c>
+      <c r="N1056">
+        <v>9</v>
+      </c>
+      <c r="O1056">
+        <v>2</v>
+      </c>
+      <c r="P1056">
+        <v>8</v>
+      </c>
+      <c r="Q1056">
+        <v>1807</v>
+      </c>
+      <c r="R1056">
+        <v>82</v>
+      </c>
+      <c r="S1056">
+        <v>26</v>
+      </c>
+      <c r="T1056" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1056">
+        <v>10127</v>
+      </c>
+      <c r="V1056">
+        <v>2</v>
+      </c>
+      <c r="AC1056">
+        <f t="shared" si="135"/>
+        <v>2</v>
+      </c>
+      <c r="AD1056">
+        <f t="shared" si="136"/>
+        <v>3</v>
+      </c>
+      <c r="AE1056">
+        <f t="shared" si="137"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1057">
+        <v>1056</v>
+      </c>
+      <c r="B1057">
+        <v>1</v>
+      </c>
+      <c r="C1057" s="1">
+        <v>46131</v>
+      </c>
+      <c r="D1057" s="2">
+        <v>0.87152777777777779</v>
+      </c>
+      <c r="E1057" s="2">
+        <v>0.87152777777777779</v>
+      </c>
+      <c r="F1057" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1057" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1057" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1057" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1057" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1057">
+        <v>7</v>
+      </c>
+      <c r="L1057">
+        <v>4</v>
+      </c>
+      <c r="M1057">
+        <v>6</v>
+      </c>
+      <c r="N1057">
+        <v>9</v>
+      </c>
+      <c r="O1057">
+        <v>1</v>
+      </c>
+      <c r="P1057">
+        <v>6</v>
+      </c>
+      <c r="Q1057">
+        <v>1609</v>
+      </c>
+      <c r="R1057">
+        <v>80</v>
+      </c>
+      <c r="S1057">
+        <v>43</v>
+      </c>
+      <c r="T1057" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1057">
+        <v>18865</v>
+      </c>
+      <c r="V1057">
+        <v>1</v>
+      </c>
+      <c r="AC1057">
+        <f>IF(C1057=C1056, AC1056+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1057">
+        <f>IF(T1057="Loss",AD1056+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1057">
+        <f>IF(T1057="Win", AE1056+1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF1057">
+        <v>4.09</v>
+      </c>
+      <c r="AG1057">
+        <v>36</v>
+      </c>
+      <c r="AH1057">
+        <v>54</v>
+      </c>
+      <c r="AI1057">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1058">
+        <v>1057</v>
+      </c>
+      <c r="B1058">
+        <v>1</v>
+      </c>
+      <c r="C1058" s="1">
+        <v>46131</v>
+      </c>
+      <c r="D1058" s="2">
+        <v>0.91597222222222219</v>
+      </c>
+      <c r="E1058" s="2">
+        <v>0.91597222222222219</v>
+      </c>
+      <c r="F1058" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1058" t="s">
+        <v>101</v>
+      </c>
+      <c r="I1058" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1058" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1058">
+        <v>4</v>
+      </c>
+      <c r="L1058">
+        <v>8</v>
+      </c>
+      <c r="M1058">
+        <v>9</v>
+      </c>
+      <c r="N1058">
+        <v>11</v>
+      </c>
+      <c r="O1058">
+        <v>3</v>
+      </c>
+      <c r="P1058">
+        <v>9</v>
+      </c>
+      <c r="Q1058">
+        <v>1926</v>
+      </c>
+      <c r="R1058">
+        <v>80</v>
+      </c>
+      <c r="S1058">
+        <v>20</v>
+      </c>
+      <c r="T1058" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1058">
+        <v>19203</v>
+      </c>
+      <c r="V1058">
+        <v>1</v>
+      </c>
+      <c r="AC1058">
+        <f>IF(C1058=C1057, AC1057+1, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AD1058">
+        <f>IF(T1058="Loss",AD1057+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1058">
+        <f>IF(T1058="Win", AE1057+1, 0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1059">
+        <v>1058</v>
+      </c>
+      <c r="B1059">
+        <v>2</v>
+      </c>
+      <c r="C1059" s="1">
+        <v>46131</v>
+      </c>
+      <c r="D1059" s="2">
+        <v>0.9458333333333333</v>
+      </c>
+      <c r="E1059" s="2">
+        <v>0.9458333333333333</v>
+      </c>
+      <c r="F1059" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1059" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1059" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1059" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1059">
+        <v>18</v>
+      </c>
+      <c r="L1059">
+        <v>2</v>
+      </c>
+      <c r="M1059">
+        <v>9</v>
+      </c>
+      <c r="N1059">
+        <v>14</v>
+      </c>
+      <c r="O1059">
+        <v>4</v>
+      </c>
+      <c r="P1059">
+        <v>8</v>
+      </c>
+      <c r="Q1059">
+        <v>2934</v>
+      </c>
+      <c r="R1059">
+        <v>97</v>
+      </c>
+      <c r="S1059">
+        <v>25</v>
+      </c>
+      <c r="T1059" t="s">
+        <v>65</v>
+      </c>
+      <c r="U1059">
+        <v>10000</v>
+      </c>
+      <c r="V1059">
+        <v>2</v>
+      </c>
+      <c r="AC1059">
+        <f>IF(C1059=C1058, AC1058+1, 1)</f>
+        <v>3</v>
+      </c>
+      <c r="AD1059">
+        <f>IF(T1059="Loss",AD1058+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1059">
+        <f>IF(T1059="Win", AE1058+1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1060">
+        <v>1059</v>
+      </c>
+      <c r="B1060">
+        <v>2</v>
+      </c>
+      <c r="C1060" s="1">
+        <v>46131</v>
+      </c>
+      <c r="D1060" s="2">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="E1060" s="2">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="F1060" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1060" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1060" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1060" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1060" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1060">
+        <v>4</v>
+      </c>
+      <c r="L1060">
+        <v>3</v>
+      </c>
+      <c r="M1060">
+        <v>2</v>
+      </c>
+      <c r="N1060">
+        <v>11</v>
+      </c>
+      <c r="O1060">
+        <v>7</v>
+      </c>
+      <c r="P1060">
+        <v>9</v>
+      </c>
+      <c r="Q1060">
+        <v>1675</v>
+      </c>
+      <c r="R1060">
+        <v>98</v>
+      </c>
+      <c r="S1060">
+        <v>26</v>
+      </c>
+      <c r="T1060" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1060">
+        <v>10000</v>
+      </c>
+      <c r="V1060">
+        <v>2</v>
+      </c>
+      <c r="AC1060">
+        <f>IF(C1060=C1059, AC1059+1, 1)</f>
+        <v>4</v>
+      </c>
+      <c r="AD1060">
+        <f>IF(T1060="Loss",AD1059+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1060">
+        <f>IF(T1060="Win", AE1059+1, 0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1061">
+        <v>1060</v>
+      </c>
+      <c r="B1061">
+        <v>1</v>
+      </c>
+      <c r="C1061" s="1">
+        <v>46132</v>
+      </c>
+      <c r="D1061" s="2">
+        <v>0.89097222222222228</v>
+      </c>
+      <c r="E1061" s="2">
+        <v>0.89097222222222228</v>
+      </c>
+      <c r="F1061" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1061" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1061" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1061" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1061">
+        <v>4</v>
+      </c>
+      <c r="L1061">
+        <v>3</v>
+      </c>
+      <c r="M1061">
+        <v>3</v>
+      </c>
+      <c r="N1061">
+        <v>4</v>
+      </c>
+      <c r="O1061">
+        <v>1</v>
+      </c>
+      <c r="P1061">
+        <v>10</v>
+      </c>
+      <c r="Q1061">
+        <v>824</v>
+      </c>
+      <c r="R1061">
+        <v>41</v>
+      </c>
+      <c r="S1061">
+        <v>25</v>
+      </c>
+      <c r="T1061" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1061">
+        <v>19497</v>
+      </c>
+      <c r="V1061">
+        <v>5</v>
+      </c>
+      <c r="AA1061" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC1061">
+        <f>IF(C1061=C1060, AC1060+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1061">
+        <f>IF(T1061="Loss",AD1060+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1061">
+        <f>IF(T1061="Win", AE1060+1, 0)</f>
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0E22C2-5E78-4203-BD13-0D61B6127BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04461189-47F3-41F4-898D-4F8C742F69B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="4020" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6616" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -548,12 +548,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -600,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1061" totalsRowShown="0">
-  <autoFilter ref="A1:AI1061" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1064" totalsRowShown="0">
+  <autoFilter ref="A1:AI1064" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -955,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1061"/>
+  <dimension ref="A1:AI1064"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -92630,15 +92631,15 @@
         <v>1</v>
       </c>
       <c r="AC1057">
-        <f>IF(C1057=C1056, AC1056+1, 1)</f>
+        <f t="shared" ref="AC1057:AC1062" si="138">IF(C1057=C1056, AC1056+1, 1)</f>
         <v>1</v>
       </c>
       <c r="AD1057">
-        <f>IF(T1057="Loss",AD1056+1,0)</f>
+        <f t="shared" ref="AD1057:AD1062" si="139">IF(T1057="Loss",AD1056+1,0)</f>
         <v>0</v>
       </c>
       <c r="AE1057">
-        <f>IF(T1057="Win", AE1056+1, 0)</f>
+        <f t="shared" ref="AE1057:AE1062" si="140">IF(T1057="Win", AE1056+1, 0)</f>
         <v>1</v>
       </c>
       <c r="AF1057">
@@ -92719,15 +92720,15 @@
         <v>1</v>
       </c>
       <c r="AC1058">
-        <f>IF(C1058=C1057, AC1057+1, 1)</f>
+        <f t="shared" si="138"/>
         <v>2</v>
       </c>
       <c r="AD1058">
-        <f>IF(T1058="Loss",AD1057+1,0)</f>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="AE1058">
-        <f>IF(T1058="Win", AE1057+1, 0)</f>
+        <f t="shared" si="140"/>
         <v>2</v>
       </c>
     </row>
@@ -92796,15 +92797,15 @@
         <v>2</v>
       </c>
       <c r="AC1059">
-        <f>IF(C1059=C1058, AC1058+1, 1)</f>
+        <f t="shared" si="138"/>
         <v>3</v>
       </c>
       <c r="AD1059">
-        <f>IF(T1059="Loss",AD1058+1,0)</f>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="AE1059">
-        <f>IF(T1059="Win", AE1058+1, 0)</f>
+        <f t="shared" si="140"/>
         <v>0</v>
       </c>
     </row>
@@ -92876,15 +92877,15 @@
         <v>2</v>
       </c>
       <c r="AC1060">
-        <f>IF(C1060=C1059, AC1059+1, 1)</f>
+        <f t="shared" si="138"/>
         <v>4</v>
       </c>
       <c r="AD1060">
-        <f>IF(T1060="Loss",AD1059+1,0)</f>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="AE1060">
-        <f>IF(T1060="Win", AE1059+1, 0)</f>
+        <f t="shared" si="140"/>
         <v>1</v>
       </c>
     </row>
@@ -92953,20 +92954,282 @@
         <v>5</v>
       </c>
       <c r="AA1061" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="AC1061">
-        <f>IF(C1061=C1060, AC1060+1, 1)</f>
+        <f t="shared" si="138"/>
         <v>1</v>
       </c>
       <c r="AD1061">
-        <f>IF(T1061="Loss",AD1060+1,0)</f>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="AE1061">
-        <f>IF(T1061="Win", AE1060+1, 0)</f>
-        <v>2</v>
-      </c>
+        <f t="shared" si="140"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1062">
+        <v>1061</v>
+      </c>
+      <c r="B1062">
+        <v>1</v>
+      </c>
+      <c r="C1062" s="1">
+        <v>46136</v>
+      </c>
+      <c r="D1062" s="2">
+        <v>0.98888888888888893</v>
+      </c>
+      <c r="E1062" s="2">
+        <v>0.98888888888888893</v>
+      </c>
+      <c r="F1062" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1062" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1062" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1062" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1062" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1062">
+        <v>8</v>
+      </c>
+      <c r="L1062">
+        <v>2</v>
+      </c>
+      <c r="M1062">
+        <v>9</v>
+      </c>
+      <c r="N1062">
+        <v>8</v>
+      </c>
+      <c r="O1062">
+        <v>5</v>
+      </c>
+      <c r="P1062">
+        <v>8</v>
+      </c>
+      <c r="Q1062">
+        <v>1537</v>
+      </c>
+      <c r="R1062">
+        <v>64</v>
+      </c>
+      <c r="S1062">
+        <v>31</v>
+      </c>
+      <c r="T1062" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1062">
+        <v>19859</v>
+      </c>
+      <c r="V1062">
+        <v>2</v>
+      </c>
+      <c r="AA1062" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC1062">
+        <f t="shared" si="138"/>
+        <v>1</v>
+      </c>
+      <c r="AD1062">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+      <c r="AE1062">
+        <f t="shared" si="140"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1063">
+        <v>1062</v>
+      </c>
+      <c r="B1063">
+        <v>1</v>
+      </c>
+      <c r="C1063" s="1">
+        <v>46138</v>
+      </c>
+      <c r="D1063" s="2">
+        <v>0.9291666666666667</v>
+      </c>
+      <c r="E1063" s="2">
+        <v>0.9291666666666667</v>
+      </c>
+      <c r="F1063" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1063" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1063" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1063" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1063" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1063">
+        <v>2</v>
+      </c>
+      <c r="L1063">
+        <v>2</v>
+      </c>
+      <c r="M1063">
+        <v>4</v>
+      </c>
+      <c r="N1063">
+        <v>10</v>
+      </c>
+      <c r="O1063">
+        <v>5</v>
+      </c>
+      <c r="P1063">
+        <v>6</v>
+      </c>
+      <c r="Q1063">
+        <v>1373</v>
+      </c>
+      <c r="R1063">
+        <v>85</v>
+      </c>
+      <c r="S1063">
+        <v>25</v>
+      </c>
+      <c r="T1063" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1063">
+        <v>19999</v>
+      </c>
+      <c r="V1063">
+        <v>1</v>
+      </c>
+      <c r="AC1063">
+        <f>IF(C1063=C1062, AC1062+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1063">
+        <f>IF(T1063="Loss",AD1062+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1063">
+        <f>IF(T1063="Win", AE1062+1, 0)</f>
+        <v>4</v>
+      </c>
+      <c r="AF1063">
+        <v>6.58</v>
+      </c>
+      <c r="AG1063">
+        <v>42</v>
+      </c>
+      <c r="AH1063">
+        <v>84</v>
+      </c>
+      <c r="AI1063">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1064">
+        <v>1063</v>
+      </c>
+      <c r="B1064">
+        <v>1</v>
+      </c>
+      <c r="C1064" s="1">
+        <v>46139</v>
+      </c>
+      <c r="D1064" s="2">
+        <v>0.97013888888888888</v>
+      </c>
+      <c r="E1064" s="2">
+        <v>0.97013888888888888</v>
+      </c>
+      <c r="F1064" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1064" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1064" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1064" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1064" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1064">
+        <v>16</v>
+      </c>
+      <c r="L1064">
+        <v>1</v>
+      </c>
+      <c r="M1064">
+        <v>10</v>
+      </c>
+      <c r="N1064">
+        <v>13</v>
+      </c>
+      <c r="O1064">
+        <v>4</v>
+      </c>
+      <c r="P1064">
+        <v>8</v>
+      </c>
+      <c r="Q1064">
+        <v>2633</v>
+      </c>
+      <c r="R1064">
+        <v>90</v>
+      </c>
+      <c r="S1064">
+        <v>38</v>
+      </c>
+      <c r="T1064" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1064">
+        <v>20115</v>
+      </c>
+      <c r="V1064">
+        <v>2</v>
+      </c>
+      <c r="AA1064" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC1064" s="5">
+        <f>IF(C1064=C1063, AC1063+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1064" s="5">
+        <f>IF(T1064="Loss",AD1063+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1064" s="5">
+        <f>IF(T1064="Win", AE1063+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF1064" s="5"/>
+      <c r="AG1064" s="5"/>
+      <c r="AH1064" s="5"/>
+      <c r="AI1064" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04461189-47F3-41F4-898D-4F8C742F69B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53831097-A322-4AC6-963F-0DE525A40A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="4020" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6616" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6710" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -601,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1064" totalsRowShown="0">
-  <autoFilter ref="A1:AI1064" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1081" totalsRowShown="0">
+  <autoFilter ref="A1:AI1081" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -956,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1064"/>
+  <dimension ref="A1:AI1081"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -93120,15 +93120,15 @@
         <v>1</v>
       </c>
       <c r="AC1063">
-        <f>IF(C1063=C1062, AC1062+1, 1)</f>
+        <f t="shared" ref="AC1063:AC1069" si="141">IF(C1063=C1062, AC1062+1, 1)</f>
         <v>1</v>
       </c>
       <c r="AD1063">
-        <f>IF(T1063="Loss",AD1062+1,0)</f>
+        <f t="shared" ref="AD1063:AD1069" si="142">IF(T1063="Loss",AD1062+1,0)</f>
         <v>0</v>
       </c>
       <c r="AE1063">
-        <f>IF(T1063="Win", AE1062+1, 0)</f>
+        <f t="shared" ref="AE1063:AE1069" si="143">IF(T1063="Win", AE1062+1, 0)</f>
         <v>4</v>
       </c>
       <c r="AF1063">
@@ -93214,22 +93214,1326 @@
       <c r="AA1064" t="s">
         <v>40</v>
       </c>
-      <c r="AC1064" s="5">
-        <f>IF(C1064=C1063, AC1063+1, 1)</f>
-        <v>1</v>
-      </c>
-      <c r="AD1064" s="5">
-        <f>IF(T1064="Loss",AD1063+1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AE1064" s="5">
-        <f>IF(T1064="Win", AE1063+1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF1064" s="5"/>
-      <c r="AG1064" s="5"/>
-      <c r="AH1064" s="5"/>
-      <c r="AI1064" s="5"/>
+      <c r="AC1064">
+        <f t="shared" si="141"/>
+        <v>1</v>
+      </c>
+      <c r="AD1064">
+        <f t="shared" si="142"/>
+        <v>1</v>
+      </c>
+      <c r="AE1064">
+        <f t="shared" si="143"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1065">
+        <v>1064</v>
+      </c>
+      <c r="B1065">
+        <v>1</v>
+      </c>
+      <c r="C1065" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D1065" s="2">
+        <v>0.87569444444444444</v>
+      </c>
+      <c r="E1065" s="2">
+        <v>0.87569444444444444</v>
+      </c>
+      <c r="F1065" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1065" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1065" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1065" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1065" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1065">
+        <v>5</v>
+      </c>
+      <c r="L1065">
+        <v>0</v>
+      </c>
+      <c r="M1065">
+        <v>7</v>
+      </c>
+      <c r="N1065">
+        <v>7</v>
+      </c>
+      <c r="O1065">
+        <v>0</v>
+      </c>
+      <c r="P1065">
+        <v>11</v>
+      </c>
+      <c r="Q1065">
+        <v>1187</v>
+      </c>
+      <c r="R1065">
+        <v>62</v>
+      </c>
+      <c r="S1065">
+        <v>50</v>
+      </c>
+      <c r="T1065" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1065">
+        <v>20008</v>
+      </c>
+      <c r="V1065">
+        <v>1</v>
+      </c>
+      <c r="AC1065">
+        <f t="shared" si="141"/>
+        <v>1</v>
+      </c>
+      <c r="AD1065">
+        <f t="shared" si="142"/>
+        <v>2</v>
+      </c>
+      <c r="AE1065">
+        <f t="shared" si="143"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1066">
+        <v>1065</v>
+      </c>
+      <c r="B1066">
+        <v>1</v>
+      </c>
+      <c r="C1066" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D1066" s="2">
+        <v>0.90486111111111112</v>
+      </c>
+      <c r="E1066" s="2">
+        <v>0.90486111111111112</v>
+      </c>
+      <c r="F1066" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1066" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1066" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1066" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1066" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1066">
+        <v>7</v>
+      </c>
+      <c r="L1066">
+        <v>4</v>
+      </c>
+      <c r="M1066">
+        <v>10</v>
+      </c>
+      <c r="T1066" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1066">
+        <v>20000</v>
+      </c>
+      <c r="V1066">
+        <v>1</v>
+      </c>
+      <c r="AC1066">
+        <f t="shared" si="141"/>
+        <v>2</v>
+      </c>
+      <c r="AD1066">
+        <f t="shared" si="142"/>
+        <v>3</v>
+      </c>
+      <c r="AE1066">
+        <f t="shared" si="143"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1067">
+        <v>1066</v>
+      </c>
+      <c r="B1067">
+        <v>2</v>
+      </c>
+      <c r="C1067" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D1067" s="2">
+        <v>0.93194444444444446</v>
+      </c>
+      <c r="E1067" s="2">
+        <v>0.93194444444444446</v>
+      </c>
+      <c r="F1067" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1067" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1067" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1067" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1067" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1067">
+        <v>12</v>
+      </c>
+      <c r="L1067">
+        <v>4</v>
+      </c>
+      <c r="M1067">
+        <v>9</v>
+      </c>
+      <c r="N1067">
+        <v>13</v>
+      </c>
+      <c r="O1067">
+        <v>3</v>
+      </c>
+      <c r="P1067">
+        <v>6</v>
+      </c>
+      <c r="Q1067">
+        <v>2405</v>
+      </c>
+      <c r="R1067">
+        <v>100</v>
+      </c>
+      <c r="S1067">
+        <v>16</v>
+      </c>
+      <c r="T1067" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1067">
+        <v>10156</v>
+      </c>
+      <c r="V1067">
+        <v>2</v>
+      </c>
+      <c r="AC1067">
+        <f t="shared" si="141"/>
+        <v>3</v>
+      </c>
+      <c r="AD1067">
+        <f t="shared" si="142"/>
+        <v>0</v>
+      </c>
+      <c r="AE1067">
+        <f t="shared" si="143"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1068">
+        <v>1067</v>
+      </c>
+      <c r="B1068">
+        <v>2</v>
+      </c>
+      <c r="C1068" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D1068" s="2">
+        <v>0.9604166666666667</v>
+      </c>
+      <c r="E1068" s="2">
+        <v>0.9604166666666667</v>
+      </c>
+      <c r="F1068" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1068" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1068" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1068" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1068">
+        <v>1</v>
+      </c>
+      <c r="L1068">
+        <v>1</v>
+      </c>
+      <c r="M1068">
+        <v>4</v>
+      </c>
+      <c r="N1068">
+        <v>8</v>
+      </c>
+      <c r="O1068">
+        <v>1</v>
+      </c>
+      <c r="P1068">
+        <v>10</v>
+      </c>
+      <c r="Q1068">
+        <v>1248</v>
+      </c>
+      <c r="R1068">
+        <v>78</v>
+      </c>
+      <c r="S1068">
+        <v>44</v>
+      </c>
+      <c r="T1068" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1068">
+        <v>10509</v>
+      </c>
+      <c r="V1068">
+        <v>2</v>
+      </c>
+      <c r="AC1068">
+        <f t="shared" si="141"/>
+        <v>4</v>
+      </c>
+      <c r="AD1068">
+        <f t="shared" si="142"/>
+        <v>1</v>
+      </c>
+      <c r="AE1068">
+        <f t="shared" si="143"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1069">
+        <v>1068</v>
+      </c>
+      <c r="B1069">
+        <v>1</v>
+      </c>
+      <c r="C1069" s="1">
+        <v>46142</v>
+      </c>
+      <c r="D1069" s="2">
+        <v>1.3194444444444444E-2</v>
+      </c>
+      <c r="E1069" s="2">
+        <v>1.3194444444444444E-2</v>
+      </c>
+      <c r="F1069" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1069" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1069" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1069" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1069">
+        <v>11</v>
+      </c>
+      <c r="L1069">
+        <v>7</v>
+      </c>
+      <c r="M1069">
+        <v>10</v>
+      </c>
+      <c r="N1069">
+        <v>10</v>
+      </c>
+      <c r="O1069">
+        <v>4</v>
+      </c>
+      <c r="P1069">
+        <v>8</v>
+      </c>
+      <c r="Q1069">
+        <v>1902</v>
+      </c>
+      <c r="R1069">
+        <v>65</v>
+      </c>
+      <c r="T1069" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1069">
+        <v>19887</v>
+      </c>
+      <c r="V1069">
+        <v>2</v>
+      </c>
+      <c r="AC1069">
+        <f t="shared" si="141"/>
+        <v>1</v>
+      </c>
+      <c r="AD1069">
+        <f t="shared" si="142"/>
+        <v>0</v>
+      </c>
+      <c r="AE1069">
+        <f t="shared" si="143"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1070">
+        <v>1069</v>
+      </c>
+      <c r="B1070">
+        <v>1</v>
+      </c>
+      <c r="C1070" s="1">
+        <v>46143</v>
+      </c>
+      <c r="D1070" s="2">
+        <v>0.89166666666666672</v>
+      </c>
+      <c r="E1070" s="2">
+        <v>0.89166666666666672</v>
+      </c>
+      <c r="F1070" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1070" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1070" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1070" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1070" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1070">
+        <v>10</v>
+      </c>
+      <c r="L1070">
+        <v>1</v>
+      </c>
+      <c r="M1070">
+        <v>9</v>
+      </c>
+      <c r="N1070">
+        <v>8</v>
+      </c>
+      <c r="O1070">
+        <v>3</v>
+      </c>
+      <c r="P1070">
+        <v>6</v>
+      </c>
+      <c r="Q1070">
+        <v>1839</v>
+      </c>
+      <c r="R1070">
+        <v>76</v>
+      </c>
+      <c r="S1070">
+        <v>22</v>
+      </c>
+      <c r="T1070" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1070">
+        <v>19999</v>
+      </c>
+      <c r="V1070">
+        <v>1</v>
+      </c>
+      <c r="AC1070">
+        <f t="shared" ref="AC1070:AC1075" si="144">IF(C1070=C1069, AC1069+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1070">
+        <f t="shared" ref="AD1070:AD1075" si="145">IF(T1070="Loss",AD1069+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1070">
+        <f t="shared" ref="AE1070:AE1075" si="146">IF(T1070="Win", AE1069+1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1071">
+        <v>1070</v>
+      </c>
+      <c r="B1071">
+        <v>1</v>
+      </c>
+      <c r="C1071" s="1">
+        <v>46145</v>
+      </c>
+      <c r="D1071" s="2">
+        <v>0.79722222222222228</v>
+      </c>
+      <c r="E1071" s="2">
+        <v>0.79722222222222228</v>
+      </c>
+      <c r="F1071" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1071" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1071" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1071" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1071" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1071">
+        <v>4</v>
+      </c>
+      <c r="L1071">
+        <v>3</v>
+      </c>
+      <c r="M1071">
+        <v>7</v>
+      </c>
+      <c r="N1071">
+        <v>7</v>
+      </c>
+      <c r="O1071">
+        <v>8</v>
+      </c>
+      <c r="P1071">
+        <v>12</v>
+      </c>
+      <c r="Q1071">
+        <v>1705</v>
+      </c>
+      <c r="R1071">
+        <v>77</v>
+      </c>
+      <c r="S1071">
+        <v>9</v>
+      </c>
+      <c r="T1071" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1071">
+        <v>19435</v>
+      </c>
+      <c r="V1071">
+        <v>1</v>
+      </c>
+      <c r="AC1071">
+        <f t="shared" si="144"/>
+        <v>1</v>
+      </c>
+      <c r="AD1071">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="AE1071">
+        <f t="shared" si="146"/>
+        <v>1</v>
+      </c>
+      <c r="AF1071">
+        <v>-4.59</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1072">
+        <v>1071</v>
+      </c>
+      <c r="B1072">
+        <v>1</v>
+      </c>
+      <c r="C1072" s="1">
+        <v>46145</v>
+      </c>
+      <c r="D1072" s="2">
+        <v>0.82916666666666672</v>
+      </c>
+      <c r="E1072" s="2">
+        <v>0.82916666666666672</v>
+      </c>
+      <c r="F1072" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1072" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1072" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1072" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1072">
+        <v>8</v>
+      </c>
+      <c r="L1072">
+        <v>1</v>
+      </c>
+      <c r="M1072">
+        <v>10</v>
+      </c>
+      <c r="N1072">
+        <v>10</v>
+      </c>
+      <c r="O1072">
+        <v>5</v>
+      </c>
+      <c r="P1072">
+        <v>6</v>
+      </c>
+      <c r="Q1072">
+        <v>1804</v>
+      </c>
+      <c r="R1072">
+        <v>82</v>
+      </c>
+      <c r="S1072">
+        <v>38</v>
+      </c>
+      <c r="T1072" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1072">
+        <v>19619</v>
+      </c>
+      <c r="V1072">
+        <v>1</v>
+      </c>
+      <c r="AC1072">
+        <f t="shared" si="144"/>
+        <v>2</v>
+      </c>
+      <c r="AD1072">
+        <f t="shared" si="145"/>
+        <v>1</v>
+      </c>
+      <c r="AE1072">
+        <f t="shared" si="146"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1073">
+        <v>1072</v>
+      </c>
+      <c r="B1073">
+        <v>2</v>
+      </c>
+      <c r="C1073" s="1">
+        <v>46145</v>
+      </c>
+      <c r="D1073" s="2">
+        <v>0.88263888888888886</v>
+      </c>
+      <c r="E1073" s="2">
+        <v>0.88263888888888886</v>
+      </c>
+      <c r="F1073" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1073" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1073" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1073" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1073">
+        <v>6</v>
+      </c>
+      <c r="L1073">
+        <v>5</v>
+      </c>
+      <c r="M1073">
+        <v>4</v>
+      </c>
+      <c r="N1073">
+        <v>17</v>
+      </c>
+      <c r="O1073">
+        <v>3</v>
+      </c>
+      <c r="P1073">
+        <v>7</v>
+      </c>
+      <c r="Q1073">
+        <v>2487</v>
+      </c>
+      <c r="R1073">
+        <v>146</v>
+      </c>
+      <c r="S1073">
+        <v>21</v>
+      </c>
+      <c r="T1073" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1073">
+        <v>10182</v>
+      </c>
+      <c r="V1073">
+        <v>2</v>
+      </c>
+      <c r="AC1073">
+        <f t="shared" si="144"/>
+        <v>3</v>
+      </c>
+      <c r="AD1073">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="AE1073">
+        <f t="shared" si="146"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1074">
+        <v>1073</v>
+      </c>
+      <c r="B1074">
+        <v>2</v>
+      </c>
+      <c r="C1074" s="1">
+        <v>46145</v>
+      </c>
+      <c r="D1074" s="2">
+        <v>0.90555555555555556</v>
+      </c>
+      <c r="E1074" s="2">
+        <v>0.90555555555555556</v>
+      </c>
+      <c r="F1074" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1074" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1074" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1074" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1074" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1074">
+        <v>11</v>
+      </c>
+      <c r="L1074">
+        <v>1</v>
+      </c>
+      <c r="M1074">
+        <v>4</v>
+      </c>
+      <c r="N1074">
+        <v>11</v>
+      </c>
+      <c r="O1074">
+        <v>4</v>
+      </c>
+      <c r="P1074">
+        <v>4</v>
+      </c>
+      <c r="Q1074">
+        <v>2029</v>
+      </c>
+      <c r="R1074">
+        <v>106</v>
+      </c>
+      <c r="S1074">
+        <v>13</v>
+      </c>
+      <c r="T1074" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1074">
+        <v>10546</v>
+      </c>
+      <c r="V1074">
+        <v>2</v>
+      </c>
+      <c r="AC1074">
+        <f t="shared" si="144"/>
+        <v>4</v>
+      </c>
+      <c r="AD1074">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="AE1074">
+        <f t="shared" si="146"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1075">
+        <v>1074</v>
+      </c>
+      <c r="B1075">
+        <v>2</v>
+      </c>
+      <c r="C1075" s="1">
+        <v>46145</v>
+      </c>
+      <c r="D1075" s="2">
+        <v>0.92847222222222225</v>
+      </c>
+      <c r="E1075" s="2">
+        <v>0.92847222222222225</v>
+      </c>
+      <c r="F1075" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1075" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1075" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1075" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1075">
+        <v>15</v>
+      </c>
+      <c r="L1075">
+        <v>4</v>
+      </c>
+      <c r="M1075">
+        <v>9</v>
+      </c>
+      <c r="N1075">
+        <v>9</v>
+      </c>
+      <c r="O1075">
+        <v>2</v>
+      </c>
+      <c r="P1075">
+        <v>6</v>
+      </c>
+      <c r="Q1075">
+        <v>2676</v>
+      </c>
+      <c r="R1075">
+        <v>133</v>
+      </c>
+      <c r="S1075">
+        <v>20</v>
+      </c>
+      <c r="T1075" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1075">
+        <v>10896</v>
+      </c>
+      <c r="V1075">
+        <v>2</v>
+      </c>
+      <c r="AC1075">
+        <f t="shared" si="144"/>
+        <v>5</v>
+      </c>
+      <c r="AD1075">
+        <f t="shared" si="145"/>
+        <v>1</v>
+      </c>
+      <c r="AE1075">
+        <f t="shared" si="146"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1076">
+        <v>1075</v>
+      </c>
+      <c r="B1076">
+        <v>2</v>
+      </c>
+      <c r="C1076" s="1">
+        <v>46145</v>
+      </c>
+      <c r="D1076" s="2">
+        <v>0.96666666666666667</v>
+      </c>
+      <c r="E1076" s="2">
+        <v>0.96666666666666667</v>
+      </c>
+      <c r="F1076" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1076" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1076" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1076" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1076">
+        <v>7</v>
+      </c>
+      <c r="L1076">
+        <v>3</v>
+      </c>
+      <c r="M1076">
+        <v>7</v>
+      </c>
+      <c r="N1076">
+        <v>11</v>
+      </c>
+      <c r="O1076">
+        <v>2</v>
+      </c>
+      <c r="P1076">
+        <v>5</v>
+      </c>
+      <c r="Q1076">
+        <v>1885</v>
+      </c>
+      <c r="R1076">
+        <v>81</v>
+      </c>
+      <c r="S1076">
+        <v>16</v>
+      </c>
+      <c r="T1076" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1076">
+        <v>10686</v>
+      </c>
+      <c r="V1076">
+        <v>5</v>
+      </c>
+      <c r="AC1076">
+        <f>IF(C1076=C1075, AC1075+1, 1)</f>
+        <v>6</v>
+      </c>
+      <c r="AD1076">
+        <f>IF(T1076="Loss",AD1075+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1076">
+        <f>IF(T1076="Win", AE1075+1, 0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1077">
+        <v>1076</v>
+      </c>
+      <c r="B1077">
+        <v>2</v>
+      </c>
+      <c r="C1077" s="1">
+        <v>46146</v>
+      </c>
+      <c r="D1077" s="2">
+        <v>1.8749999999999999E-2</v>
+      </c>
+      <c r="E1077" s="2">
+        <v>1.8749999999999999E-2</v>
+      </c>
+      <c r="F1077" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1077" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1077" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1077" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1077" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1077">
+        <v>9</v>
+      </c>
+      <c r="L1077">
+        <v>3</v>
+      </c>
+      <c r="M1077">
+        <v>10</v>
+      </c>
+      <c r="N1077">
+        <v>7</v>
+      </c>
+      <c r="O1077">
+        <v>6</v>
+      </c>
+      <c r="P1077">
+        <v>8</v>
+      </c>
+      <c r="Q1077">
+        <v>2468</v>
+      </c>
+      <c r="R1077">
+        <v>102</v>
+      </c>
+      <c r="S1077">
+        <v>27</v>
+      </c>
+      <c r="T1077" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1077">
+        <v>11053</v>
+      </c>
+      <c r="V1077">
+        <v>5</v>
+      </c>
+      <c r="AC1077">
+        <f>IF(C1077=C1076, AC1076+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1077">
+        <f>IF(T1077="Loss",AD1076+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1077">
+        <f>IF(T1077="Win", AE1076+1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1078">
+        <v>1077</v>
+      </c>
+      <c r="B1078">
+        <v>2</v>
+      </c>
+      <c r="C1078" s="1">
+        <v>46146</v>
+      </c>
+      <c r="D1078" s="2">
+        <v>0.78888888888888886</v>
+      </c>
+      <c r="E1078" s="2">
+        <v>0.78888888888888886</v>
+      </c>
+      <c r="F1078" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1078" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1078" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1078" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1078" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1078">
+        <v>15</v>
+      </c>
+      <c r="L1078">
+        <v>3</v>
+      </c>
+      <c r="M1078">
+        <v>12</v>
+      </c>
+      <c r="N1078">
+        <v>16</v>
+      </c>
+      <c r="O1078">
+        <v>5</v>
+      </c>
+      <c r="P1078">
+        <v>8</v>
+      </c>
+      <c r="Q1078">
+        <v>2164</v>
+      </c>
+      <c r="R1078">
+        <v>105</v>
+      </c>
+      <c r="S1078">
+        <v>25</v>
+      </c>
+      <c r="T1078" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1078">
+        <v>10762</v>
+      </c>
+      <c r="V1078">
+        <v>2</v>
+      </c>
+      <c r="AC1078">
+        <f>IF(C1078=C1077, AC1077+1, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AD1078">
+        <f>IF(T1078="Loss",AD1077+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1078">
+        <f>IF(T1078="Win", AE1077+1, 0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1079">
+        <v>1078</v>
+      </c>
+      <c r="B1079">
+        <v>2</v>
+      </c>
+      <c r="C1079" s="1">
+        <v>46146</v>
+      </c>
+      <c r="D1079" s="2">
+        <v>0.82222222222222219</v>
+      </c>
+      <c r="E1079" s="2">
+        <v>0.82222222222222219</v>
+      </c>
+      <c r="F1079" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1079" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1079" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1079" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q1079">
+        <v>1313</v>
+      </c>
+      <c r="R1079">
+        <v>82</v>
+      </c>
+      <c r="S1079">
+        <v>33</v>
+      </c>
+      <c r="T1079" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1079">
+        <v>10712</v>
+      </c>
+      <c r="V1079">
+        <v>2</v>
+      </c>
+      <c r="AC1079">
+        <f>IF(C1079=C1078, AC1078+1, 1)</f>
+        <v>3</v>
+      </c>
+      <c r="AD1079">
+        <f>IF(T1079="Loss",AD1078+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1079">
+        <f>IF(T1079="Win", AE1078+1, 0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1080">
+        <v>1079</v>
+      </c>
+      <c r="B1080">
+        <v>2</v>
+      </c>
+      <c r="C1080" s="1">
+        <v>46146</v>
+      </c>
+      <c r="D1080" s="2">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="E1080" s="2">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="F1080" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1080" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1080" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1080" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1080" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1080">
+        <v>6</v>
+      </c>
+      <c r="L1080">
+        <v>5</v>
+      </c>
+      <c r="M1080">
+        <v>8</v>
+      </c>
+      <c r="N1080">
+        <v>6</v>
+      </c>
+      <c r="O1080">
+        <v>1</v>
+      </c>
+      <c r="P1080">
+        <v>3</v>
+      </c>
+      <c r="Q1080">
+        <v>1585</v>
+      </c>
+      <c r="R1080">
+        <v>83</v>
+      </c>
+      <c r="S1080">
+        <v>33</v>
+      </c>
+      <c r="T1080" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1080">
+        <v>11018</v>
+      </c>
+      <c r="V1080">
+        <v>2</v>
+      </c>
+      <c r="AC1080" s="5">
+        <f>IF(C1080=C1079, AC1079+1, 1)</f>
+        <v>4</v>
+      </c>
+      <c r="AD1080" s="5">
+        <f>IF(T1080="Loss",AD1079+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1080" s="5">
+        <f>IF(T1080="Win", AE1079+1, 0)</f>
+        <v>3</v>
+      </c>
+      <c r="AF1080" s="5"/>
+      <c r="AG1080" s="5"/>
+      <c r="AH1080" s="5"/>
+      <c r="AI1080" s="5"/>
+    </row>
+    <row r="1081" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1081">
+        <v>1080</v>
+      </c>
+      <c r="B1081">
+        <v>2</v>
+      </c>
+      <c r="C1081" s="1">
+        <v>46146</v>
+      </c>
+      <c r="D1081" s="2">
+        <v>0.97430555555555554</v>
+      </c>
+      <c r="E1081" s="2">
+        <v>0.97430555555555554</v>
+      </c>
+      <c r="F1081" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1081" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1081" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1081" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1081">
+        <v>8</v>
+      </c>
+      <c r="L1081">
+        <v>3</v>
+      </c>
+      <c r="M1081">
+        <v>2</v>
+      </c>
+      <c r="N1081">
+        <v>15</v>
+      </c>
+      <c r="O1081">
+        <v>6</v>
+      </c>
+      <c r="P1081">
+        <v>3</v>
+      </c>
+      <c r="Q1081">
+        <v>2208</v>
+      </c>
+      <c r="R1081">
+        <v>129</v>
+      </c>
+      <c r="S1081">
+        <v>36</v>
+      </c>
+      <c r="T1081" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1081">
+        <v>11373</v>
+      </c>
+      <c r="V1081">
+        <v>2</v>
+      </c>
+      <c r="AC1081" s="5">
+        <f>IF(C1081=C1080, AC1080+1, 1)</f>
+        <v>5</v>
+      </c>
+      <c r="AD1081" s="5">
+        <f>IF(T1081="Loss",AD1080+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1081" s="5">
+        <f>IF(T1081="Win", AE1080+1, 0)</f>
+        <v>4</v>
+      </c>
+      <c r="AF1081" s="5"/>
+      <c r="AG1081" s="5"/>
+      <c r="AH1081" s="5"/>
+      <c r="AI1081" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53831097-A322-4AC6-963F-0DE525A40A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D06002-49B4-46DC-AA9B-0AF5C79C540D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="4020" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6710" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6802" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -601,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1081" totalsRowShown="0">
-  <autoFilter ref="A1:AI1081" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1097" totalsRowShown="0">
+  <autoFilter ref="A1:AI1097" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -956,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1081"/>
+  <dimension ref="A1:AI1097"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -93840,7 +93840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1073" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1073" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1073">
         <v>1072</v>
       </c>
@@ -93917,7 +93917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1074" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1074" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1074">
         <v>1073</v>
       </c>
@@ -93997,7 +93997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1075" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1075" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1075">
         <v>1074</v>
       </c>
@@ -94074,7 +94074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1076" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1076" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1076">
         <v>1075</v>
       </c>
@@ -94139,19 +94139,19 @@
         <v>5</v>
       </c>
       <c r="AC1076">
-        <f>IF(C1076=C1075, AC1075+1, 1)</f>
+        <f t="shared" ref="AC1076:AC1081" si="147">IF(C1076=C1075, AC1075+1, 1)</f>
         <v>6</v>
       </c>
       <c r="AD1076">
-        <f>IF(T1076="Loss",AD1075+1,0)</f>
+        <f t="shared" ref="AD1076:AD1081" si="148">IF(T1076="Loss",AD1075+1,0)</f>
         <v>0</v>
       </c>
       <c r="AE1076">
-        <f>IF(T1076="Win", AE1075+1, 0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1077" spans="1:35" x14ac:dyDescent="0.25">
+        <f t="shared" ref="AE1076:AE1081" si="149">IF(T1076="Win", AE1075+1, 0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1077">
         <v>1076</v>
       </c>
@@ -94219,19 +94219,19 @@
         <v>5</v>
       </c>
       <c r="AC1077">
-        <f>IF(C1077=C1076, AC1076+1, 1)</f>
+        <f t="shared" si="147"/>
         <v>1</v>
       </c>
       <c r="AD1077">
-        <f>IF(T1077="Loss",AD1076+1,0)</f>
+        <f t="shared" si="148"/>
         <v>1</v>
       </c>
       <c r="AE1077">
-        <f>IF(T1077="Win", AE1076+1, 0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1078" spans="1:35" x14ac:dyDescent="0.25">
+        <f t="shared" si="149"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1078">
         <v>1077</v>
       </c>
@@ -94299,19 +94299,19 @@
         <v>2</v>
       </c>
       <c r="AC1078">
-        <f>IF(C1078=C1077, AC1077+1, 1)</f>
+        <f t="shared" si="147"/>
         <v>2</v>
       </c>
       <c r="AD1078">
-        <f>IF(T1078="Loss",AD1077+1,0)</f>
+        <f t="shared" si="148"/>
         <v>0</v>
       </c>
       <c r="AE1078">
-        <f>IF(T1078="Win", AE1077+1, 0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1079" spans="1:35" x14ac:dyDescent="0.25">
+        <f t="shared" si="149"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1079">
         <v>1078</v>
       </c>
@@ -94358,19 +94358,19 @@
         <v>2</v>
       </c>
       <c r="AC1079">
-        <f>IF(C1079=C1078, AC1078+1, 1)</f>
+        <f t="shared" si="147"/>
         <v>3</v>
       </c>
       <c r="AD1079">
-        <f>IF(T1079="Loss",AD1078+1,0)</f>
+        <f t="shared" si="148"/>
         <v>0</v>
       </c>
       <c r="AE1079">
-        <f>IF(T1079="Win", AE1078+1, 0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1080" spans="1:35" x14ac:dyDescent="0.25">
+        <f t="shared" si="149"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1080">
         <v>1079</v>
       </c>
@@ -94437,24 +94437,20 @@
       <c r="V1080">
         <v>2</v>
       </c>
-      <c r="AC1080" s="5">
-        <f>IF(C1080=C1079, AC1079+1, 1)</f>
+      <c r="AC1080">
+        <f t="shared" si="147"/>
         <v>4</v>
       </c>
-      <c r="AD1080" s="5">
-        <f>IF(T1080="Loss",AD1079+1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE1080" s="5">
-        <f>IF(T1080="Win", AE1079+1, 0)</f>
-        <v>3</v>
-      </c>
-      <c r="AF1080" s="5"/>
-      <c r="AG1080" s="5"/>
-      <c r="AH1080" s="5"/>
-      <c r="AI1080" s="5"/>
-    </row>
-    <row r="1081" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AD1080">
+        <f t="shared" si="148"/>
+        <v>0</v>
+      </c>
+      <c r="AE1080">
+        <f t="shared" si="149"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1081">
         <v>1080</v>
       </c>
@@ -94518,22 +94514,1249 @@
       <c r="V1081">
         <v>2</v>
       </c>
-      <c r="AC1081" s="5">
-        <f>IF(C1081=C1080, AC1080+1, 1)</f>
+      <c r="AC1081">
+        <f t="shared" si="147"/>
         <v>5</v>
       </c>
-      <c r="AD1081" s="5">
-        <f>IF(T1081="Loss",AD1080+1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE1081" s="5">
-        <f>IF(T1081="Win", AE1080+1, 0)</f>
+      <c r="AD1081">
+        <f t="shared" si="148"/>
+        <v>0</v>
+      </c>
+      <c r="AE1081">
+        <f t="shared" si="149"/>
         <v>4</v>
       </c>
-      <c r="AF1081" s="5"/>
-      <c r="AG1081" s="5"/>
-      <c r="AH1081" s="5"/>
-      <c r="AI1081" s="5"/>
+    </row>
+    <row r="1082" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1082">
+        <v>1081</v>
+      </c>
+      <c r="B1082">
+        <v>1</v>
+      </c>
+      <c r="C1082" s="1">
+        <v>46147</v>
+      </c>
+      <c r="D1082" s="2">
+        <v>0.99097222222222225</v>
+      </c>
+      <c r="E1082" s="2">
+        <v>0.99097222222222225</v>
+      </c>
+      <c r="F1082" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1082" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1082" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1082" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1082" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1082">
+        <v>9</v>
+      </c>
+      <c r="L1082">
+        <v>1</v>
+      </c>
+      <c r="M1082">
+        <v>6</v>
+      </c>
+      <c r="N1082">
+        <v>5</v>
+      </c>
+      <c r="O1082">
+        <v>3</v>
+      </c>
+      <c r="P1082">
+        <v>7</v>
+      </c>
+      <c r="Q1082">
+        <v>1205</v>
+      </c>
+      <c r="R1082">
+        <v>54</v>
+      </c>
+      <c r="S1082">
+        <v>28</v>
+      </c>
+      <c r="T1082" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1082">
+        <v>19260</v>
+      </c>
+      <c r="V1082">
+        <v>1</v>
+      </c>
+      <c r="AC1082">
+        <f t="shared" ref="AC1082:AC1087" si="150">IF(C1082=C1081, AC1081+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1082">
+        <f t="shared" ref="AD1082:AD1087" si="151">IF(T1082="Loss",AD1081+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1082">
+        <f t="shared" ref="AE1082:AE1087" si="152">IF(T1082="Win", AE1081+1, 0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1083">
+        <v>1082</v>
+      </c>
+      <c r="B1083">
+        <v>1</v>
+      </c>
+      <c r="C1083" s="1">
+        <v>46148</v>
+      </c>
+      <c r="D1083" s="2">
+        <v>0.82430555555555551</v>
+      </c>
+      <c r="E1083" s="2">
+        <v>0.82430555555555551</v>
+      </c>
+      <c r="F1083" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1083" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1083" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1083" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1083" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1083">
+        <v>9</v>
+      </c>
+      <c r="L1083">
+        <v>3</v>
+      </c>
+      <c r="M1083">
+        <v>8</v>
+      </c>
+      <c r="N1083">
+        <v>4</v>
+      </c>
+      <c r="O1083">
+        <v>1</v>
+      </c>
+      <c r="P1083">
+        <v>6</v>
+      </c>
+      <c r="R1083">
+        <v>63</v>
+      </c>
+      <c r="S1083">
+        <v>30</v>
+      </c>
+      <c r="T1083" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1083">
+        <v>19597</v>
+      </c>
+      <c r="V1083">
+        <v>1</v>
+      </c>
+      <c r="AC1083">
+        <f t="shared" si="150"/>
+        <v>1</v>
+      </c>
+      <c r="AD1083">
+        <f t="shared" si="151"/>
+        <v>1</v>
+      </c>
+      <c r="AE1083">
+        <f t="shared" si="152"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1084">
+        <v>1083</v>
+      </c>
+      <c r="B1084">
+        <v>1</v>
+      </c>
+      <c r="C1084" s="1">
+        <v>46148</v>
+      </c>
+      <c r="D1084" s="2">
+        <v>0.91805555555555551</v>
+      </c>
+      <c r="E1084" s="2">
+        <v>0.91805555555555551</v>
+      </c>
+      <c r="F1084" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1084" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1084" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1084" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1084" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1084">
+        <v>6</v>
+      </c>
+      <c r="L1084">
+        <v>1</v>
+      </c>
+      <c r="M1084">
+        <v>6</v>
+      </c>
+      <c r="N1084">
+        <v>3</v>
+      </c>
+      <c r="O1084">
+        <v>1</v>
+      </c>
+      <c r="P1084">
+        <v>9</v>
+      </c>
+      <c r="Q1084">
+        <v>1362</v>
+      </c>
+      <c r="R1084">
+        <v>68</v>
+      </c>
+      <c r="S1084">
+        <v>55</v>
+      </c>
+      <c r="T1084" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1084">
+        <v>19182</v>
+      </c>
+      <c r="V1084">
+        <v>1</v>
+      </c>
+      <c r="AC1084">
+        <f t="shared" si="150"/>
+        <v>2</v>
+      </c>
+      <c r="AD1084">
+        <f t="shared" si="151"/>
+        <v>2</v>
+      </c>
+      <c r="AE1084">
+        <f t="shared" si="152"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1085">
+        <v>1084</v>
+      </c>
+      <c r="B1085">
+        <v>1</v>
+      </c>
+      <c r="C1085" s="1">
+        <v>46148</v>
+      </c>
+      <c r="D1085" s="2">
+        <v>0.94652777777777775</v>
+      </c>
+      <c r="E1085" s="2">
+        <v>0.94652777777777775</v>
+      </c>
+      <c r="F1085" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1085" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1085" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1085" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1085" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1085">
+        <v>7</v>
+      </c>
+      <c r="L1085">
+        <v>3</v>
+      </c>
+      <c r="M1085">
+        <v>8</v>
+      </c>
+      <c r="N1085">
+        <v>4</v>
+      </c>
+      <c r="O1085">
+        <v>1</v>
+      </c>
+      <c r="P1085">
+        <v>3</v>
+      </c>
+      <c r="Q1085">
+        <v>1060</v>
+      </c>
+      <c r="R1085">
+        <v>58</v>
+      </c>
+      <c r="S1085">
+        <v>36</v>
+      </c>
+      <c r="T1085" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1085">
+        <v>18879</v>
+      </c>
+      <c r="V1085">
+        <v>1</v>
+      </c>
+      <c r="AC1085">
+        <f t="shared" si="150"/>
+        <v>3</v>
+      </c>
+      <c r="AD1085">
+        <f t="shared" si="151"/>
+        <v>3</v>
+      </c>
+      <c r="AE1085">
+        <f t="shared" si="152"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1086">
+        <v>1085</v>
+      </c>
+      <c r="B1086">
+        <v>1</v>
+      </c>
+      <c r="C1086" s="1">
+        <v>46149</v>
+      </c>
+      <c r="D1086" s="2">
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="E1086" s="2">
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="F1086" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1086" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1086" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1086" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1086" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1086">
+        <v>2</v>
+      </c>
+      <c r="L1086">
+        <v>3</v>
+      </c>
+      <c r="M1086">
+        <v>6</v>
+      </c>
+      <c r="N1086">
+        <v>11</v>
+      </c>
+      <c r="O1086">
+        <v>3</v>
+      </c>
+      <c r="P1086">
+        <v>7</v>
+      </c>
+      <c r="Q1086">
+        <v>1433</v>
+      </c>
+      <c r="R1086">
+        <v>68</v>
+      </c>
+      <c r="T1086" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1086">
+        <v>18503</v>
+      </c>
+      <c r="V1086">
+        <v>1</v>
+      </c>
+      <c r="AC1086">
+        <f t="shared" si="150"/>
+        <v>1</v>
+      </c>
+      <c r="AD1086">
+        <f t="shared" si="151"/>
+        <v>4</v>
+      </c>
+      <c r="AE1086">
+        <f t="shared" si="152"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1087">
+        <v>1086</v>
+      </c>
+      <c r="B1087">
+        <v>2</v>
+      </c>
+      <c r="C1087" s="1">
+        <v>46149</v>
+      </c>
+      <c r="D1087" s="2">
+        <v>0.81180555555555556</v>
+      </c>
+      <c r="E1087" s="2">
+        <v>0.81180555555555556</v>
+      </c>
+      <c r="F1087" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1087" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1087" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1087" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1087" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q1087">
+        <v>3309</v>
+      </c>
+      <c r="R1087">
+        <v>110</v>
+      </c>
+      <c r="S1087">
+        <v>14</v>
+      </c>
+      <c r="T1087" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1087">
+        <v>11744</v>
+      </c>
+      <c r="V1087">
+        <v>2</v>
+      </c>
+      <c r="AC1087">
+        <f t="shared" si="150"/>
+        <v>2</v>
+      </c>
+      <c r="AD1087">
+        <f t="shared" si="151"/>
+        <v>5</v>
+      </c>
+      <c r="AE1087">
+        <f t="shared" si="152"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1088">
+        <v>1087</v>
+      </c>
+      <c r="B1088">
+        <v>1</v>
+      </c>
+      <c r="C1088" s="1">
+        <v>46149</v>
+      </c>
+      <c r="D1088" s="2">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="E1088" s="2">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="F1088" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1088" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1088" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1088" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1088" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1088">
+        <v>6</v>
+      </c>
+      <c r="L1088">
+        <v>4</v>
+      </c>
+      <c r="M1088">
+        <v>14</v>
+      </c>
+      <c r="N1088">
+        <v>5</v>
+      </c>
+      <c r="O1088">
+        <v>2</v>
+      </c>
+      <c r="P1088">
+        <v>8</v>
+      </c>
+      <c r="Q1088">
+        <v>1108</v>
+      </c>
+      <c r="R1088">
+        <v>38</v>
+      </c>
+      <c r="S1088">
+        <v>45</v>
+      </c>
+      <c r="T1088" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1088">
+        <v>18076</v>
+      </c>
+      <c r="V1088">
+        <v>1</v>
+      </c>
+      <c r="AC1088">
+        <f t="shared" ref="AC1088:AC1094" si="153">IF(C1088=C1087, AC1087+1, 1)</f>
+        <v>3</v>
+      </c>
+      <c r="AD1088">
+        <f t="shared" ref="AD1088:AD1094" si="154">IF(T1088="Loss",AD1087+1,0)</f>
+        <v>6</v>
+      </c>
+      <c r="AE1088">
+        <f t="shared" ref="AE1088:AE1094" si="155">IF(T1088="Win", AE1087+1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1089">
+        <v>1088</v>
+      </c>
+      <c r="B1089">
+        <v>1</v>
+      </c>
+      <c r="C1089" s="1">
+        <v>46149</v>
+      </c>
+      <c r="D1089" s="2">
+        <v>0.98472222222222228</v>
+      </c>
+      <c r="E1089" s="2">
+        <v>0.98472222222222228</v>
+      </c>
+      <c r="F1089" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1089" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1089" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1089" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1089">
+        <v>4</v>
+      </c>
+      <c r="L1089">
+        <v>0</v>
+      </c>
+      <c r="M1089">
+        <v>9</v>
+      </c>
+      <c r="N1089">
+        <v>5</v>
+      </c>
+      <c r="O1089">
+        <v>2</v>
+      </c>
+      <c r="P1089">
+        <v>8</v>
+      </c>
+      <c r="Q1089">
+        <v>1178</v>
+      </c>
+      <c r="R1089">
+        <v>56</v>
+      </c>
+      <c r="S1089">
+        <v>33</v>
+      </c>
+      <c r="T1089" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1089">
+        <v>17700</v>
+      </c>
+      <c r="V1089">
+        <v>3</v>
+      </c>
+      <c r="AC1089">
+        <f t="shared" si="153"/>
+        <v>4</v>
+      </c>
+      <c r="AD1089">
+        <f t="shared" si="154"/>
+        <v>7</v>
+      </c>
+      <c r="AE1089">
+        <f t="shared" si="155"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1090">
+        <v>1089</v>
+      </c>
+      <c r="B1090">
+        <v>1</v>
+      </c>
+      <c r="C1090" s="1">
+        <v>46150</v>
+      </c>
+      <c r="D1090" s="2">
+        <v>1.3194444444444444E-2</v>
+      </c>
+      <c r="E1090" s="2">
+        <v>1.3194444444444444E-2</v>
+      </c>
+      <c r="F1090" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1090" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1090" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1090" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1090" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1090">
+        <v>11</v>
+      </c>
+      <c r="L1090">
+        <v>2</v>
+      </c>
+      <c r="M1090">
+        <v>7</v>
+      </c>
+      <c r="N1090">
+        <v>5</v>
+      </c>
+      <c r="O1090">
+        <v>2</v>
+      </c>
+      <c r="P1090">
+        <v>3</v>
+      </c>
+      <c r="Q1090">
+        <v>1722</v>
+      </c>
+      <c r="R1090">
+        <v>101</v>
+      </c>
+      <c r="S1090">
+        <v>6</v>
+      </c>
+      <c r="T1090" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1090">
+        <v>17383</v>
+      </c>
+      <c r="V1090">
+        <v>4</v>
+      </c>
+      <c r="AC1090">
+        <f t="shared" si="153"/>
+        <v>1</v>
+      </c>
+      <c r="AD1090">
+        <f t="shared" si="154"/>
+        <v>0</v>
+      </c>
+      <c r="AE1090">
+        <f t="shared" si="155"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1091">
+        <v>1090</v>
+      </c>
+      <c r="B1091">
+        <v>1</v>
+      </c>
+      <c r="C1091" s="1">
+        <v>46150</v>
+      </c>
+      <c r="D1091" s="2">
+        <v>0.86111111111111116</v>
+      </c>
+      <c r="E1091" s="2">
+        <v>0.86111111111111116</v>
+      </c>
+      <c r="F1091" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1091" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1091" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1091" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1091" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1091">
+        <v>0</v>
+      </c>
+      <c r="L1091">
+        <v>1</v>
+      </c>
+      <c r="M1091">
+        <v>4</v>
+      </c>
+      <c r="N1091">
+        <v>0</v>
+      </c>
+      <c r="O1091">
+        <v>1</v>
+      </c>
+      <c r="P1091">
+        <v>8</v>
+      </c>
+      <c r="Q1091">
+        <v>261</v>
+      </c>
+      <c r="R1091">
+        <v>16</v>
+      </c>
+      <c r="S1091">
+        <v>0</v>
+      </c>
+      <c r="T1091" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1091">
+        <v>17570</v>
+      </c>
+      <c r="V1091">
+        <v>5</v>
+      </c>
+      <c r="AC1091">
+        <f t="shared" si="153"/>
+        <v>2</v>
+      </c>
+      <c r="AD1091">
+        <f t="shared" si="154"/>
+        <v>1</v>
+      </c>
+      <c r="AE1091">
+        <f t="shared" si="155"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1092">
+        <v>1091</v>
+      </c>
+      <c r="B1092">
+        <v>1</v>
+      </c>
+      <c r="C1092" s="1">
+        <v>46150</v>
+      </c>
+      <c r="D1092" s="2">
+        <v>0.8833333333333333</v>
+      </c>
+      <c r="E1092" s="2">
+        <v>0.8833333333333333</v>
+      </c>
+      <c r="F1092" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1092" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1092" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1092" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1092" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1092">
+        <v>8</v>
+      </c>
+      <c r="L1092">
+        <v>1</v>
+      </c>
+      <c r="M1092">
+        <v>9</v>
+      </c>
+      <c r="N1092">
+        <v>7</v>
+      </c>
+      <c r="O1092">
+        <v>3</v>
+      </c>
+      <c r="P1092">
+        <v>8</v>
+      </c>
+      <c r="Q1092">
+        <v>1770</v>
+      </c>
+      <c r="R1092">
+        <v>73</v>
+      </c>
+      <c r="S1092">
+        <v>26</v>
+      </c>
+      <c r="T1092" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1092">
+        <v>17437</v>
+      </c>
+      <c r="V1092">
+        <v>5</v>
+      </c>
+      <c r="AC1092">
+        <f t="shared" si="153"/>
+        <v>3</v>
+      </c>
+      <c r="AD1092">
+        <f t="shared" si="154"/>
+        <v>2</v>
+      </c>
+      <c r="AE1092">
+        <f t="shared" si="155"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1093">
+        <v>1092</v>
+      </c>
+      <c r="B1093">
+        <v>1</v>
+      </c>
+      <c r="C1093" s="1">
+        <v>46150</v>
+      </c>
+      <c r="D1093" s="2">
+        <v>0.9145833333333333</v>
+      </c>
+      <c r="E1093" s="2">
+        <v>0.9145833333333333</v>
+      </c>
+      <c r="F1093" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1093" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1093" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1093" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1093">
+        <v>3</v>
+      </c>
+      <c r="L1093">
+        <v>1</v>
+      </c>
+      <c r="M1093">
+        <v>8</v>
+      </c>
+      <c r="N1093">
+        <v>1</v>
+      </c>
+      <c r="O1093">
+        <v>0</v>
+      </c>
+      <c r="P1093">
+        <v>7</v>
+      </c>
+      <c r="Q1093">
+        <v>668</v>
+      </c>
+      <c r="R1093">
+        <v>35</v>
+      </c>
+      <c r="S1093">
+        <v>50</v>
+      </c>
+      <c r="T1093" t="s">
+        <v>58</v>
+      </c>
+      <c r="V1093">
+        <v>5</v>
+      </c>
+      <c r="AC1093">
+        <f t="shared" si="153"/>
+        <v>4</v>
+      </c>
+      <c r="AD1093">
+        <f t="shared" si="154"/>
+        <v>3</v>
+      </c>
+      <c r="AE1093">
+        <f t="shared" si="155"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1094">
+        <v>1093</v>
+      </c>
+      <c r="B1094">
+        <v>1</v>
+      </c>
+      <c r="C1094" s="1">
+        <v>46150</v>
+      </c>
+      <c r="D1094" s="2">
+        <v>0.94027777777777777</v>
+      </c>
+      <c r="E1094" s="2">
+        <v>0.94027777777777777</v>
+      </c>
+      <c r="F1094" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1094" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1094" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1094" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1094" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1094">
+        <v>2</v>
+      </c>
+      <c r="L1094">
+        <v>4</v>
+      </c>
+      <c r="M1094">
+        <v>10</v>
+      </c>
+      <c r="N1094">
+        <v>5</v>
+      </c>
+      <c r="O1094">
+        <v>2</v>
+      </c>
+      <c r="P1094">
+        <v>9</v>
+      </c>
+      <c r="Q1094">
+        <v>1309</v>
+      </c>
+      <c r="R1094">
+        <v>62</v>
+      </c>
+      <c r="S1094">
+        <v>42</v>
+      </c>
+      <c r="T1094" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1094">
+        <v>17205</v>
+      </c>
+      <c r="V1094">
+        <v>5</v>
+      </c>
+      <c r="AC1094">
+        <f t="shared" si="153"/>
+        <v>5</v>
+      </c>
+      <c r="AD1094">
+        <f t="shared" si="154"/>
+        <v>4</v>
+      </c>
+      <c r="AE1094">
+        <f t="shared" si="155"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1095">
+        <v>1094</v>
+      </c>
+      <c r="B1095">
+        <v>1</v>
+      </c>
+      <c r="C1095" s="1">
+        <v>46150</v>
+      </c>
+      <c r="D1095" s="2">
+        <v>0.96736111111111112</v>
+      </c>
+      <c r="E1095" s="2">
+        <v>0.96736111111111112</v>
+      </c>
+      <c r="F1095" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1095" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1095" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1095" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q1095">
+        <v>1768</v>
+      </c>
+      <c r="R1095">
+        <v>84</v>
+      </c>
+      <c r="S1095">
+        <v>27</v>
+      </c>
+      <c r="T1095" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1095">
+        <v>17091</v>
+      </c>
+      <c r="V1095">
+        <v>2</v>
+      </c>
+      <c r="AC1095">
+        <f>IF(C1095=C1094, AC1094+1, 1)</f>
+        <v>6</v>
+      </c>
+      <c r="AD1095">
+        <f>IF(T1095="Loss",AD1094+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1095">
+        <f>IF(T1095="Win", AE1094+1, 0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1096">
+        <v>1095</v>
+      </c>
+      <c r="B1096">
+        <v>2</v>
+      </c>
+      <c r="C1096" s="1">
+        <v>46154</v>
+      </c>
+      <c r="D1096" s="2">
+        <v>1.7361111111111112E-2</v>
+      </c>
+      <c r="E1096" s="2">
+        <v>1.7361111111111112E-2</v>
+      </c>
+      <c r="G1096" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1096" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1096" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1096" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1096">
+        <v>10</v>
+      </c>
+      <c r="L1096">
+        <v>2</v>
+      </c>
+      <c r="M1096">
+        <v>8</v>
+      </c>
+      <c r="N1096">
+        <v>8</v>
+      </c>
+      <c r="O1096">
+        <v>3</v>
+      </c>
+      <c r="P1096">
+        <v>7</v>
+      </c>
+      <c r="Q1096">
+        <v>1813</v>
+      </c>
+      <c r="R1096">
+        <v>75</v>
+      </c>
+      <c r="S1096">
+        <v>38</v>
+      </c>
+      <c r="T1096" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1096">
+        <v>11387</v>
+      </c>
+      <c r="V1096">
+        <v>3</v>
+      </c>
+      <c r="AC1096" s="5">
+        <f>IF(C1096=C1095, AC1095+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1096" s="5">
+        <f>IF(T1096="Loss",AD1095+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1096" s="5">
+        <f>IF(T1096="Win", AE1095+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF1096" s="5"/>
+      <c r="AG1096" s="5"/>
+      <c r="AH1096" s="5"/>
+      <c r="AI1096" s="5"/>
+    </row>
+    <row r="1097" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1097">
+        <v>1096</v>
+      </c>
+      <c r="B1097">
+        <v>2</v>
+      </c>
+      <c r="C1097" s="1">
+        <v>46154</v>
+      </c>
+      <c r="D1097" s="2">
+        <v>4.9305555555555554E-2</v>
+      </c>
+      <c r="E1097" s="2">
+        <v>4.9305555555555554E-2</v>
+      </c>
+      <c r="F1097" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1097" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1097" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1097" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1097" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1097">
+        <v>15</v>
+      </c>
+      <c r="L1097">
+        <v>6</v>
+      </c>
+      <c r="M1097">
+        <v>8</v>
+      </c>
+      <c r="N1097">
+        <v>6</v>
+      </c>
+      <c r="O1097">
+        <v>0</v>
+      </c>
+      <c r="P1097">
+        <v>5</v>
+      </c>
+      <c r="Q1097">
+        <v>2280</v>
+      </c>
+      <c r="R1097">
+        <v>114</v>
+      </c>
+      <c r="S1097">
+        <v>57</v>
+      </c>
+      <c r="T1097" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1097">
+        <v>11143</v>
+      </c>
+      <c r="V1097">
+        <v>3</v>
+      </c>
+      <c r="AC1097" s="5">
+        <f>IF(C1097=C1096, AC1096+1, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AD1097" s="5">
+        <f>IF(T1097="Loss",AD1096+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1097" s="5">
+        <f>IF(T1097="Win", AE1096+1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF1097" s="5"/>
+      <c r="AG1097" s="5"/>
+      <c r="AH1097" s="5"/>
+      <c r="AI1097" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D06002-49B4-46DC-AA9B-0AF5C79C540D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D74EB15-DEA3-4BB4-931B-4BE12D08C96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="4020" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-2100" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6802" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6831" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -601,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1097" totalsRowShown="0">
-  <autoFilter ref="A1:AI1097" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1102" totalsRowShown="0">
+  <autoFilter ref="A1:AI1102" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -956,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1097"/>
+  <dimension ref="A1:AI1102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -95581,15 +95581,15 @@
         <v>2</v>
       </c>
       <c r="AC1095">
-        <f>IF(C1095=C1094, AC1094+1, 1)</f>
+        <f t="shared" ref="AC1095:AC1100" si="156">IF(C1095=C1094, AC1094+1, 1)</f>
         <v>6</v>
       </c>
       <c r="AD1095">
-        <f>IF(T1095="Loss",AD1094+1,0)</f>
+        <f t="shared" ref="AD1095:AD1100" si="157">IF(T1095="Loss",AD1094+1,0)</f>
         <v>0</v>
       </c>
       <c r="AE1095">
-        <f>IF(T1095="Win", AE1094+1, 0)</f>
+        <f t="shared" ref="AE1095:AE1100" si="158">IF(T1095="Win", AE1094+1, 0)</f>
         <v>1</v>
       </c>
     </row>
@@ -95657,22 +95657,18 @@
       <c r="V1096">
         <v>3</v>
       </c>
-      <c r="AC1096" s="5">
-        <f>IF(C1096=C1095, AC1095+1, 1)</f>
-        <v>1</v>
-      </c>
-      <c r="AD1096" s="5">
-        <f>IF(T1096="Loss",AD1095+1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AE1096" s="5">
-        <f>IF(T1096="Win", AE1095+1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF1096" s="5"/>
-      <c r="AG1096" s="5"/>
-      <c r="AH1096" s="5"/>
-      <c r="AI1096" s="5"/>
+      <c r="AC1096">
+        <f t="shared" si="156"/>
+        <v>1</v>
+      </c>
+      <c r="AD1096">
+        <f t="shared" si="157"/>
+        <v>1</v>
+      </c>
+      <c r="AE1096">
+        <f t="shared" si="158"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="1097" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1097">
@@ -95741,22 +95737,402 @@
       <c r="V1097">
         <v>3</v>
       </c>
-      <c r="AC1097" s="5">
-        <f>IF(C1097=C1096, AC1096+1, 1)</f>
-        <v>2</v>
-      </c>
-      <c r="AD1097" s="5">
-        <f>IF(T1097="Loss",AD1096+1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE1097" s="5">
-        <f>IF(T1097="Win", AE1096+1, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="AF1097" s="5"/>
-      <c r="AG1097" s="5"/>
-      <c r="AH1097" s="5"/>
-      <c r="AI1097" s="5"/>
+      <c r="AC1097">
+        <f t="shared" si="156"/>
+        <v>2</v>
+      </c>
+      <c r="AD1097">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
+      <c r="AE1097">
+        <f t="shared" si="158"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1098">
+        <v>1097</v>
+      </c>
+      <c r="B1098">
+        <v>1</v>
+      </c>
+      <c r="C1098" s="1">
+        <v>46154</v>
+      </c>
+      <c r="D1098" s="2">
+        <v>0.92152777777777772</v>
+      </c>
+      <c r="E1098" s="2">
+        <v>0.92152777777777772</v>
+      </c>
+      <c r="F1098" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1098" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1098" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1098" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1098" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1098">
+        <v>9</v>
+      </c>
+      <c r="L1098">
+        <v>7</v>
+      </c>
+      <c r="M1098">
+        <v>7</v>
+      </c>
+      <c r="T1098" t="s">
+        <v>63</v>
+      </c>
+      <c r="V1098">
+        <v>5</v>
+      </c>
+      <c r="AC1098">
+        <f t="shared" si="156"/>
+        <v>3</v>
+      </c>
+      <c r="AD1098">
+        <f t="shared" si="157"/>
+        <v>0</v>
+      </c>
+      <c r="AE1098">
+        <f t="shared" si="158"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1099">
+        <v>1098</v>
+      </c>
+      <c r="B1099">
+        <v>1</v>
+      </c>
+      <c r="C1099" s="1">
+        <v>46154</v>
+      </c>
+      <c r="D1099" s="2">
+        <v>0.94166666666666665</v>
+      </c>
+      <c r="E1099" s="2">
+        <v>0.94166666666666665</v>
+      </c>
+      <c r="F1099" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1099" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1099" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1099" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1099">
+        <v>5</v>
+      </c>
+      <c r="L1099">
+        <v>5</v>
+      </c>
+      <c r="M1099">
+        <v>10</v>
+      </c>
+      <c r="N1099">
+        <v>5</v>
+      </c>
+      <c r="O1099">
+        <v>6</v>
+      </c>
+      <c r="P1099">
+        <v>11</v>
+      </c>
+      <c r="Q1099">
+        <v>1682</v>
+      </c>
+      <c r="R1099">
+        <v>70</v>
+      </c>
+      <c r="S1099">
+        <v>30</v>
+      </c>
+      <c r="T1099" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1099">
+        <v>17795</v>
+      </c>
+      <c r="V1099">
+        <v>5</v>
+      </c>
+      <c r="AC1099">
+        <f t="shared" si="156"/>
+        <v>4</v>
+      </c>
+      <c r="AD1099">
+        <f t="shared" si="157"/>
+        <v>1</v>
+      </c>
+      <c r="AE1099">
+        <f t="shared" si="158"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1100">
+        <v>1099</v>
+      </c>
+      <c r="B1100">
+        <v>1</v>
+      </c>
+      <c r="C1100" s="1">
+        <v>46154</v>
+      </c>
+      <c r="D1100" s="2">
+        <v>0.97222222222222221</v>
+      </c>
+      <c r="E1100" s="2">
+        <v>0.97222222222222221</v>
+      </c>
+      <c r="F1100" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1100" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1100" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1100" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1100" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1100">
+        <v>8</v>
+      </c>
+      <c r="L1100">
+        <v>4</v>
+      </c>
+      <c r="M1100">
+        <v>11</v>
+      </c>
+      <c r="N1100">
+        <v>19</v>
+      </c>
+      <c r="O1100">
+        <v>3</v>
+      </c>
+      <c r="P1100">
+        <v>8</v>
+      </c>
+      <c r="Q1100">
+        <v>2529</v>
+      </c>
+      <c r="R1100">
+        <v>90</v>
+      </c>
+      <c r="S1100">
+        <v>44</v>
+      </c>
+      <c r="T1100" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1100">
+        <v>17521</v>
+      </c>
+      <c r="V1100">
+        <v>5</v>
+      </c>
+      <c r="AC1100">
+        <f t="shared" si="156"/>
+        <v>5</v>
+      </c>
+      <c r="AD1100">
+        <f t="shared" si="157"/>
+        <v>2</v>
+      </c>
+      <c r="AE1100">
+        <f t="shared" si="158"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1101">
+        <v>1100</v>
+      </c>
+      <c r="B1101">
+        <v>2</v>
+      </c>
+      <c r="C1101" s="1">
+        <v>46160</v>
+      </c>
+      <c r="D1101" s="2">
+        <v>0.8930555555555556</v>
+      </c>
+      <c r="E1101" s="2">
+        <v>0.8930555555555556</v>
+      </c>
+      <c r="F1101" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1101" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1101" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1101" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1101" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1101">
+        <v>10</v>
+      </c>
+      <c r="L1101">
+        <v>2</v>
+      </c>
+      <c r="M1101">
+        <v>10</v>
+      </c>
+      <c r="N1101">
+        <v>15</v>
+      </c>
+      <c r="O1101">
+        <v>2</v>
+      </c>
+      <c r="P1101">
+        <v>5</v>
+      </c>
+      <c r="Q1101">
+        <v>2218</v>
+      </c>
+      <c r="R1101">
+        <v>100</v>
+      </c>
+      <c r="S1101">
+        <v>32</v>
+      </c>
+      <c r="T1101" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1101">
+        <v>11495</v>
+      </c>
+      <c r="V1101">
+        <v>2</v>
+      </c>
+      <c r="AC1101" s="5">
+        <f>IF(C1101=C1100, AC1100+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1101" s="5">
+        <f>IF(T1101="Loss",AD1100+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1101" s="5">
+        <f>IF(T1101="Win", AE1100+1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF1101" s="5"/>
+      <c r="AG1101" s="5"/>
+      <c r="AH1101" s="5"/>
+      <c r="AI1101" s="5"/>
+    </row>
+    <row r="1102" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1102">
+        <v>1101</v>
+      </c>
+      <c r="B1102">
+        <v>2</v>
+      </c>
+      <c r="C1102" s="1">
+        <v>46160</v>
+      </c>
+      <c r="D1102" s="2">
+        <v>0.9194444444444444</v>
+      </c>
+      <c r="E1102" s="2">
+        <v>0.9194444444444444</v>
+      </c>
+      <c r="F1102" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1102" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1102" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1102" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1102" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1102">
+        <v>7</v>
+      </c>
+      <c r="L1102">
+        <v>1</v>
+      </c>
+      <c r="M1102">
+        <v>7</v>
+      </c>
+      <c r="N1102">
+        <v>9</v>
+      </c>
+      <c r="O1102">
+        <v>4</v>
+      </c>
+      <c r="P1102">
+        <v>9</v>
+      </c>
+      <c r="Q1102">
+        <v>2115</v>
+      </c>
+      <c r="R1102">
+        <v>100</v>
+      </c>
+      <c r="S1102">
+        <v>12</v>
+      </c>
+      <c r="T1102" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1102">
+        <v>11848</v>
+      </c>
+      <c r="V1102">
+        <v>2</v>
+      </c>
+      <c r="AC1102" s="5">
+        <f>IF(C1102=C1101, AC1101+1, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AD1102" s="5">
+        <f>IF(T1102="Loss",AD1101+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1102" s="5">
+        <f>IF(T1102="Win", AE1101+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF1102" s="5"/>
+      <c r="AG1102" s="5"/>
+      <c r="AH1102" s="5"/>
+      <c r="AI1102" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D74EB15-DEA3-4BB4-931B-4BE12D08C96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B528EA3-311B-428E-BCFD-033113B1073D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-2100" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6831" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6837" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -601,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1102" totalsRowShown="0">
-  <autoFilter ref="A1:AI1102" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1103" totalsRowShown="0">
+  <autoFilter ref="A1:AI1103" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -956,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1102"/>
+  <dimension ref="A1:AI1103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -96033,22 +96033,18 @@
       <c r="V1101">
         <v>2</v>
       </c>
-      <c r="AC1101" s="5">
+      <c r="AC1101">
         <f>IF(C1101=C1100, AC1100+1, 1)</f>
         <v>1</v>
       </c>
-      <c r="AD1101" s="5">
+      <c r="AD1101">
         <f>IF(T1101="Loss",AD1100+1,0)</f>
         <v>0</v>
       </c>
-      <c r="AE1101" s="5">
+      <c r="AE1101">
         <f>IF(T1101="Win", AE1100+1, 0)</f>
         <v>1</v>
       </c>
-      <c r="AF1101" s="5"/>
-      <c r="AG1101" s="5"/>
-      <c r="AH1101" s="5"/>
-      <c r="AI1101" s="5"/>
     </row>
     <row r="1102" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1102">
@@ -96117,22 +96113,102 @@
       <c r="V1102">
         <v>2</v>
       </c>
-      <c r="AC1102" s="5">
+      <c r="AC1102">
         <f>IF(C1102=C1101, AC1101+1, 1)</f>
         <v>2</v>
       </c>
-      <c r="AD1102" s="5">
+      <c r="AD1102">
         <f>IF(T1102="Loss",AD1101+1,0)</f>
         <v>1</v>
       </c>
-      <c r="AE1102" s="5">
+      <c r="AE1102">
         <f>IF(T1102="Win", AE1101+1, 0)</f>
         <v>0</v>
       </c>
-      <c r="AF1102" s="5"/>
-      <c r="AG1102" s="5"/>
-      <c r="AH1102" s="5"/>
-      <c r="AI1102" s="5"/>
+    </row>
+    <row r="1103" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1103">
+        <v>1102</v>
+      </c>
+      <c r="B1103">
+        <v>1</v>
+      </c>
+      <c r="C1103" s="1">
+        <v>46167</v>
+      </c>
+      <c r="D1103" s="2">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="E1103" s="2">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="F1103" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1103" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1103" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1103" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1103" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1103">
+        <v>7</v>
+      </c>
+      <c r="L1103">
+        <v>4</v>
+      </c>
+      <c r="M1103">
+        <v>4</v>
+      </c>
+      <c r="N1103">
+        <v>9</v>
+      </c>
+      <c r="O1103">
+        <v>2</v>
+      </c>
+      <c r="P1103">
+        <v>11</v>
+      </c>
+      <c r="Q1103">
+        <v>1975</v>
+      </c>
+      <c r="R1103">
+        <v>94</v>
+      </c>
+      <c r="S1103">
+        <v>56</v>
+      </c>
+      <c r="T1103" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1103">
+        <v>17162</v>
+      </c>
+      <c r="V1103">
+        <v>1</v>
+      </c>
+      <c r="AC1103" s="5">
+        <f>IF(C1103=C1102, AC1102+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1103" s="5">
+        <f>IF(T1103="Loss",AD1102+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1103" s="5">
+        <f>IF(T1103="Win", AE1102+1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF1103" s="5"/>
+      <c r="AG1103" s="5"/>
+      <c r="AH1103" s="5"/>
+      <c r="AI1103" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B528EA3-311B-428E-BCFD-033113B1073D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164C647C-54AE-42D8-9811-E1B59C95F4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-2100" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6837" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6844" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -601,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1103" totalsRowShown="0">
-  <autoFilter ref="A1:AI1103" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1104" totalsRowShown="0">
+  <autoFilter ref="A1:AI1104" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -956,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1103"/>
+  <dimension ref="A1:AI1104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -96193,22 +96193,105 @@
       <c r="V1103">
         <v>1</v>
       </c>
-      <c r="AC1103" s="5">
+      <c r="AC1103">
         <f>IF(C1103=C1102, AC1102+1, 1)</f>
         <v>1</v>
       </c>
-      <c r="AD1103" s="5">
+      <c r="AD1103">
         <f>IF(T1103="Loss",AD1102+1,0)</f>
         <v>0</v>
       </c>
-      <c r="AE1103" s="5">
+      <c r="AE1103">
         <f>IF(T1103="Win", AE1102+1, 0)</f>
         <v>1</v>
       </c>
-      <c r="AF1103" s="5"/>
-      <c r="AG1103" s="5"/>
-      <c r="AH1103" s="5"/>
-      <c r="AI1103" s="5"/>
+    </row>
+    <row r="1104" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1104">
+        <v>1103</v>
+      </c>
+      <c r="B1104">
+        <v>2</v>
+      </c>
+      <c r="C1104" s="1">
+        <v>46173</v>
+      </c>
+      <c r="D1104" s="2">
+        <v>0.77708333333333335</v>
+      </c>
+      <c r="E1104" s="2">
+        <v>0.77708333333333335</v>
+      </c>
+      <c r="F1104" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1104" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1104" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1104" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1104" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1104">
+        <v>4</v>
+      </c>
+      <c r="L1104">
+        <v>2</v>
+      </c>
+      <c r="M1104">
+        <v>6</v>
+      </c>
+      <c r="N1104">
+        <v>7</v>
+      </c>
+      <c r="O1104">
+        <v>1</v>
+      </c>
+      <c r="P1104">
+        <v>8</v>
+      </c>
+      <c r="Q1104">
+        <v>1251</v>
+      </c>
+      <c r="R1104">
+        <v>69</v>
+      </c>
+      <c r="S1104">
+        <v>27</v>
+      </c>
+      <c r="T1104" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1104">
+        <v>11571</v>
+      </c>
+      <c r="V1104">
+        <v>2</v>
+      </c>
+      <c r="AA1104" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC1104" s="5">
+        <f>IF(C1104=C1103, AC1103+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1104" s="5">
+        <f>IF(T1104="Loss",AD1103+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1104" s="5">
+        <f>IF(T1104="Win", AE1103+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF1104" s="5"/>
+      <c r="AG1104" s="5"/>
+      <c r="AH1104" s="5"/>
+      <c r="AI1104" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164C647C-54AE-42D8-9811-E1B59C95F4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F408985D-D6A4-43D4-844A-3170C4738E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-2100" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6844" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6930" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -601,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1104" totalsRowShown="0">
-  <autoFilter ref="A1:AI1104" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1118" totalsRowShown="0">
+  <autoFilter ref="A1:AI1118" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -956,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1104"/>
+  <dimension ref="A1:AI1118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -95063,7 +95063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1089" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1089" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1089">
         <v>1088</v>
       </c>
@@ -95140,7 +95140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1090" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1090" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1090">
         <v>1089</v>
       </c>
@@ -95220,7 +95220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1091" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1091" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1091">
         <v>1090</v>
       </c>
@@ -95300,7 +95300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1092" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1092" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1092">
         <v>1091</v>
       </c>
@@ -95380,7 +95380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1093" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1093" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1093">
         <v>1092</v>
       </c>
@@ -95454,7 +95454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1094" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1094" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1094">
         <v>1093</v>
       </c>
@@ -95534,7 +95534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1095" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1095" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1095">
         <v>1094</v>
       </c>
@@ -95593,7 +95593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1096" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1096" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1096">
         <v>1095</v>
       </c>
@@ -95670,7 +95670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1097" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1097" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1097">
         <v>1096</v>
       </c>
@@ -95750,7 +95750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1098" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1098" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1098">
         <v>1097</v>
       </c>
@@ -95809,7 +95809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1099" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1099" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1099">
         <v>1098</v>
       </c>
@@ -95886,7 +95886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1100" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1100" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1100">
         <v>1099</v>
       </c>
@@ -95966,7 +95966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1101" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1101" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1101">
         <v>1100</v>
       </c>
@@ -96034,19 +96034,19 @@
         <v>2</v>
       </c>
       <c r="AC1101">
-        <f>IF(C1101=C1100, AC1100+1, 1)</f>
+        <f t="shared" ref="AC1101:AC1106" si="159">IF(C1101=C1100, AC1100+1, 1)</f>
         <v>1</v>
       </c>
       <c r="AD1101">
-        <f>IF(T1101="Loss",AD1100+1,0)</f>
+        <f t="shared" ref="AD1101:AD1106" si="160">IF(T1101="Loss",AD1100+1,0)</f>
         <v>0</v>
       </c>
       <c r="AE1101">
-        <f>IF(T1101="Win", AE1100+1, 0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1102" spans="1:35" x14ac:dyDescent="0.25">
+        <f t="shared" ref="AE1101:AE1106" si="161">IF(T1101="Win", AE1100+1, 0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1102">
         <v>1101</v>
       </c>
@@ -96114,19 +96114,19 @@
         <v>2</v>
       </c>
       <c r="AC1102">
-        <f>IF(C1102=C1101, AC1101+1, 1)</f>
+        <f t="shared" si="159"/>
         <v>2</v>
       </c>
       <c r="AD1102">
-        <f>IF(T1102="Loss",AD1101+1,0)</f>
+        <f t="shared" si="160"/>
         <v>1</v>
       </c>
       <c r="AE1102">
-        <f>IF(T1102="Win", AE1101+1, 0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1103" spans="1:35" x14ac:dyDescent="0.25">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1103">
         <v>1102</v>
       </c>
@@ -96194,19 +96194,19 @@
         <v>1</v>
       </c>
       <c r="AC1103">
-        <f>IF(C1103=C1102, AC1102+1, 1)</f>
+        <f t="shared" si="159"/>
         <v>1</v>
       </c>
       <c r="AD1103">
-        <f>IF(T1103="Loss",AD1102+1,0)</f>
+        <f t="shared" si="160"/>
         <v>0</v>
       </c>
       <c r="AE1103">
-        <f>IF(T1103="Win", AE1102+1, 0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1104" spans="1:35" x14ac:dyDescent="0.25">
+        <f t="shared" si="161"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1104">
         <v>1103</v>
       </c>
@@ -96276,22 +96276,1148 @@
       <c r="AA1104" t="s">
         <v>71</v>
       </c>
-      <c r="AC1104" s="5">
-        <f>IF(C1104=C1103, AC1103+1, 1)</f>
-        <v>1</v>
-      </c>
-      <c r="AD1104" s="5">
-        <f>IF(T1104="Loss",AD1103+1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AE1104" s="5">
-        <f>IF(T1104="Win", AE1103+1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF1104" s="5"/>
-      <c r="AG1104" s="5"/>
-      <c r="AH1104" s="5"/>
-      <c r="AI1104" s="5"/>
+      <c r="AC1104">
+        <f t="shared" si="159"/>
+        <v>1</v>
+      </c>
+      <c r="AD1104">
+        <f t="shared" si="160"/>
+        <v>1</v>
+      </c>
+      <c r="AE1104">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1105">
+        <v>1104</v>
+      </c>
+      <c r="B1105">
+        <v>1</v>
+      </c>
+      <c r="C1105" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D1105" s="2">
+        <v>0.75763888888888886</v>
+      </c>
+      <c r="E1105" s="2">
+        <v>0.75763888888888886</v>
+      </c>
+      <c r="F1105" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1105" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1105" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1105" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1105" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1105">
+        <v>4</v>
+      </c>
+      <c r="L1105">
+        <v>1</v>
+      </c>
+      <c r="M1105">
+        <v>5</v>
+      </c>
+      <c r="N1105">
+        <v>8</v>
+      </c>
+      <c r="O1105">
+        <v>4</v>
+      </c>
+      <c r="P1105">
+        <v>9</v>
+      </c>
+      <c r="Q1105">
+        <v>1523</v>
+      </c>
+      <c r="R1105">
+        <v>80</v>
+      </c>
+      <c r="S1105">
+        <v>41</v>
+      </c>
+      <c r="T1105" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1105" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1105">
+        <v>1</v>
+      </c>
+      <c r="AC1105">
+        <f t="shared" si="159"/>
+        <v>1</v>
+      </c>
+      <c r="AD1105">
+        <f t="shared" si="160"/>
+        <v>2</v>
+      </c>
+      <c r="AE1105">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
+      <c r="AF1105">
+        <v>-5.37</v>
+      </c>
+      <c r="AG1105">
+        <v>43</v>
+      </c>
+      <c r="AH1105">
+        <v>90</v>
+      </c>
+      <c r="AI1105">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1106">
+        <v>1105</v>
+      </c>
+      <c r="B1106">
+        <v>1</v>
+      </c>
+      <c r="C1106" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D1106" s="2">
+        <v>0.78194444444444444</v>
+      </c>
+      <c r="E1106" s="2">
+        <v>0.78194444444444444</v>
+      </c>
+      <c r="F1106" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1106" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1106" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1106" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1106" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1106">
+        <v>0</v>
+      </c>
+      <c r="L1106">
+        <v>2</v>
+      </c>
+      <c r="M1106">
+        <v>4</v>
+      </c>
+      <c r="N1106">
+        <v>7</v>
+      </c>
+      <c r="O1106">
+        <v>3</v>
+      </c>
+      <c r="P1106">
+        <v>10</v>
+      </c>
+      <c r="Q1106">
+        <v>1057</v>
+      </c>
+      <c r="R1106">
+        <v>66</v>
+      </c>
+      <c r="S1106">
+        <v>14</v>
+      </c>
+      <c r="T1106" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1106" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1106">
+        <v>1</v>
+      </c>
+      <c r="AC1106">
+        <f t="shared" si="159"/>
+        <v>2</v>
+      </c>
+      <c r="AD1106">
+        <f t="shared" si="160"/>
+        <v>3</v>
+      </c>
+      <c r="AE1106">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
+      <c r="AF1106">
+        <v>-7.43</v>
+      </c>
+      <c r="AG1106">
+        <v>18</v>
+      </c>
+      <c r="AH1106">
+        <v>87</v>
+      </c>
+      <c r="AI1106">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1107">
+        <v>1106</v>
+      </c>
+      <c r="B1107">
+        <v>1</v>
+      </c>
+      <c r="C1107" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D1107" s="2">
+        <v>0.82430555555555551</v>
+      </c>
+      <c r="E1107" s="2">
+        <v>0.82430555555555551</v>
+      </c>
+      <c r="F1107" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1107" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1107" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1107" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1107" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1107">
+        <v>3</v>
+      </c>
+      <c r="L1107">
+        <v>1</v>
+      </c>
+      <c r="M1107">
+        <v>4</v>
+      </c>
+      <c r="N1107">
+        <v>10</v>
+      </c>
+      <c r="O1107">
+        <v>1</v>
+      </c>
+      <c r="P1107">
+        <v>5</v>
+      </c>
+      <c r="Q1107">
+        <v>1150</v>
+      </c>
+      <c r="R1107">
+        <v>63</v>
+      </c>
+      <c r="S1107">
+        <v>46</v>
+      </c>
+      <c r="T1107" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1107" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1107">
+        <v>1</v>
+      </c>
+      <c r="AC1107">
+        <f t="shared" ref="AC1107:AC1111" si="162">IF(C1107=C1106, AC1106+1, 1)</f>
+        <v>3</v>
+      </c>
+      <c r="AD1107">
+        <f t="shared" ref="AD1107:AD1111" si="163">IF(T1107="Loss",AD1106+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1107">
+        <f t="shared" ref="AE1107:AE1111" si="164">IF(T1107="Win", AE1106+1, 0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1108">
+        <v>1107</v>
+      </c>
+      <c r="B1108">
+        <v>2</v>
+      </c>
+      <c r="C1108" s="1">
+        <v>46184</v>
+      </c>
+      <c r="D1108" s="2">
+        <v>0.79097222222222219</v>
+      </c>
+      <c r="E1108" s="2">
+        <v>0.79097222222222219</v>
+      </c>
+      <c r="F1108" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1108" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1108" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1108" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1108" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1108">
+        <v>12</v>
+      </c>
+      <c r="L1108">
+        <v>5</v>
+      </c>
+      <c r="M1108">
+        <v>7</v>
+      </c>
+      <c r="N1108">
+        <v>8</v>
+      </c>
+      <c r="O1108">
+        <v>1</v>
+      </c>
+      <c r="P1108">
+        <v>9</v>
+      </c>
+      <c r="Q1108">
+        <v>2073</v>
+      </c>
+      <c r="R1108">
+        <v>94</v>
+      </c>
+      <c r="S1108">
+        <v>25</v>
+      </c>
+      <c r="T1108" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1108">
+        <v>11217</v>
+      </c>
+      <c r="V1108">
+        <v>2</v>
+      </c>
+      <c r="AC1108">
+        <f t="shared" si="162"/>
+        <v>1</v>
+      </c>
+      <c r="AD1108">
+        <f t="shared" si="163"/>
+        <v>0</v>
+      </c>
+      <c r="AE1108">
+        <f t="shared" si="164"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1109">
+        <v>1108</v>
+      </c>
+      <c r="B1109">
+        <v>2</v>
+      </c>
+      <c r="C1109" s="1">
+        <v>46184</v>
+      </c>
+      <c r="D1109" s="2">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="E1109" s="2">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="F1109" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1109" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1109" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1109" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1109" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1109">
+        <v>7</v>
+      </c>
+      <c r="L1109">
+        <v>0</v>
+      </c>
+      <c r="M1109">
+        <v>3</v>
+      </c>
+      <c r="N1109">
+        <v>10</v>
+      </c>
+      <c r="O1109">
+        <v>5</v>
+      </c>
+      <c r="P1109">
+        <v>8</v>
+      </c>
+      <c r="Q1109">
+        <v>1491</v>
+      </c>
+      <c r="R1109">
+        <v>82</v>
+      </c>
+      <c r="S1109">
+        <v>41</v>
+      </c>
+      <c r="T1109" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1109">
+        <v>11580</v>
+      </c>
+      <c r="V1109">
+        <v>2</v>
+      </c>
+      <c r="AC1109">
+        <f t="shared" si="162"/>
+        <v>2</v>
+      </c>
+      <c r="AD1109">
+        <f t="shared" si="163"/>
+        <v>0</v>
+      </c>
+      <c r="AE1109">
+        <f t="shared" si="164"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1110">
+        <v>1109</v>
+      </c>
+      <c r="B1110">
+        <v>2</v>
+      </c>
+      <c r="C1110" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D1110" s="2">
+        <v>0.67569444444444449</v>
+      </c>
+      <c r="E1110" s="2">
+        <v>0.67569444444444449</v>
+      </c>
+      <c r="F1110" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1110" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1110" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1110" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1110" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1110">
+        <v>7</v>
+      </c>
+      <c r="L1110">
+        <v>7</v>
+      </c>
+      <c r="M1110">
+        <v>8</v>
+      </c>
+      <c r="N1110">
+        <v>9</v>
+      </c>
+      <c r="O1110">
+        <v>3</v>
+      </c>
+      <c r="P1110">
+        <v>9</v>
+      </c>
+      <c r="Q1110">
+        <v>2116</v>
+      </c>
+      <c r="R1110">
+        <v>96</v>
+      </c>
+      <c r="S1110">
+        <v>43</v>
+      </c>
+      <c r="T1110" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1110">
+        <v>11896</v>
+      </c>
+      <c r="V1110">
+        <v>2</v>
+      </c>
+      <c r="AC1110">
+        <f t="shared" si="162"/>
+        <v>1</v>
+      </c>
+      <c r="AD1110">
+        <f t="shared" si="163"/>
+        <v>1</v>
+      </c>
+      <c r="AE1110">
+        <f t="shared" si="164"/>
+        <v>0</v>
+      </c>
+      <c r="AF1110">
+        <v>-0.67</v>
+      </c>
+      <c r="AG1110">
+        <v>43</v>
+      </c>
+      <c r="AH1110">
+        <v>72</v>
+      </c>
+      <c r="AI1110">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1111">
+        <v>1110</v>
+      </c>
+      <c r="B1111">
+        <v>2</v>
+      </c>
+      <c r="C1111" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D1111" s="2">
+        <v>0.70486111111111116</v>
+      </c>
+      <c r="E1111" s="2">
+        <v>0.70486111111111116</v>
+      </c>
+      <c r="F1111" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1111" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1111" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1111" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1111" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1111">
+        <v>13</v>
+      </c>
+      <c r="L1111">
+        <v>4</v>
+      </c>
+      <c r="M1111">
+        <v>8</v>
+      </c>
+      <c r="N1111">
+        <v>12</v>
+      </c>
+      <c r="O1111">
+        <v>5</v>
+      </c>
+      <c r="P1111">
+        <v>8</v>
+      </c>
+      <c r="Q1111">
+        <v>2622</v>
+      </c>
+      <c r="R1111">
+        <v>114</v>
+      </c>
+      <c r="S1111">
+        <v>52</v>
+      </c>
+      <c r="T1111" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1111">
+        <v>11537</v>
+      </c>
+      <c r="V1111">
+        <v>2</v>
+      </c>
+      <c r="AC1111">
+        <f t="shared" si="162"/>
+        <v>2</v>
+      </c>
+      <c r="AD1111">
+        <f t="shared" si="163"/>
+        <v>0</v>
+      </c>
+      <c r="AE1111">
+        <f t="shared" si="164"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1112">
+        <v>1111</v>
+      </c>
+      <c r="B1112">
+        <v>2</v>
+      </c>
+      <c r="C1112" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D1112" s="2">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="E1112" s="2">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="F1112" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1112" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1112" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1112" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1112" t="s">
+        <v>53</v>
+      </c>
+      <c r="T1112" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1112">
+        <v>11888</v>
+      </c>
+      <c r="V1112">
+        <v>2</v>
+      </c>
+      <c r="AC1112">
+        <f t="shared" ref="AC1112:AC1117" si="165">IF(C1112=C1111, AC1111+1, 1)</f>
+        <v>3</v>
+      </c>
+      <c r="AD1112">
+        <f t="shared" ref="AD1112:AD1117" si="166">IF(T1112="Loss",AD1111+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1112">
+        <f t="shared" ref="AE1112:AE1117" si="167">IF(T1112="Win", AE1111+1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1113">
+        <v>1112</v>
+      </c>
+      <c r="B1113">
+        <v>2</v>
+      </c>
+      <c r="C1113" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D1113" s="2">
+        <v>0.76458333333333328</v>
+      </c>
+      <c r="E1113" s="2">
+        <v>0.76458333333333328</v>
+      </c>
+      <c r="F1113" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1113" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1113" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1113" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1113">
+        <v>20</v>
+      </c>
+      <c r="L1113">
+        <v>0</v>
+      </c>
+      <c r="M1113">
+        <v>9</v>
+      </c>
+      <c r="N1113">
+        <v>14</v>
+      </c>
+      <c r="O1113">
+        <v>4</v>
+      </c>
+      <c r="P1113">
+        <v>11</v>
+      </c>
+      <c r="Q1113">
+        <v>3591</v>
+      </c>
+      <c r="R1113">
+        <v>119</v>
+      </c>
+      <c r="S1113">
+        <v>32</v>
+      </c>
+      <c r="T1113" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1113">
+        <v>11473</v>
+      </c>
+      <c r="V1113">
+        <v>2</v>
+      </c>
+      <c r="AC1113">
+        <f t="shared" si="165"/>
+        <v>4</v>
+      </c>
+      <c r="AD1113">
+        <f t="shared" si="166"/>
+        <v>0</v>
+      </c>
+      <c r="AE1113">
+        <f t="shared" si="167"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1114">
+        <v>1113</v>
+      </c>
+      <c r="B1114">
+        <v>2</v>
+      </c>
+      <c r="C1114" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D1114" s="2">
+        <v>0.89444444444444449</v>
+      </c>
+      <c r="E1114" s="2">
+        <v>0.89444444444444449</v>
+      </c>
+      <c r="F1114" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1114" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1114" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1114" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1114" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1114">
+        <v>6</v>
+      </c>
+      <c r="L1114">
+        <v>7</v>
+      </c>
+      <c r="M1114">
+        <v>9</v>
+      </c>
+      <c r="N1114">
+        <v>15</v>
+      </c>
+      <c r="O1114">
+        <v>7</v>
+      </c>
+      <c r="P1114">
+        <v>3</v>
+      </c>
+      <c r="Q1114">
+        <v>2758</v>
+      </c>
+      <c r="R1114">
+        <v>119</v>
+      </c>
+      <c r="S1114">
+        <v>28</v>
+      </c>
+      <c r="T1114" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1114">
+        <v>11840</v>
+      </c>
+      <c r="V1114">
+        <v>2</v>
+      </c>
+      <c r="AC1114">
+        <f t="shared" si="165"/>
+        <v>5</v>
+      </c>
+      <c r="AD1114">
+        <f t="shared" si="166"/>
+        <v>0</v>
+      </c>
+      <c r="AE1114">
+        <f t="shared" si="167"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1115">
+        <v>1114</v>
+      </c>
+      <c r="B1115">
+        <v>2</v>
+      </c>
+      <c r="C1115" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D1115" s="2">
+        <v>0.92083333333333328</v>
+      </c>
+      <c r="E1115" s="2">
+        <v>0.92083333333333328</v>
+      </c>
+      <c r="F1115" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1115" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1115" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1115" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1115" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1115">
+        <v>14</v>
+      </c>
+      <c r="L1115">
+        <v>3</v>
+      </c>
+      <c r="M1115">
+        <v>9</v>
+      </c>
+      <c r="N1115">
+        <v>8</v>
+      </c>
+      <c r="O1115">
+        <v>2</v>
+      </c>
+      <c r="P1115">
+        <v>3</v>
+      </c>
+      <c r="Q1115">
+        <v>2041</v>
+      </c>
+      <c r="R1115">
+        <v>113</v>
+      </c>
+      <c r="S1115">
+        <v>13</v>
+      </c>
+      <c r="T1115" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1115">
+        <v>12208</v>
+      </c>
+      <c r="V1115">
+        <v>2</v>
+      </c>
+      <c r="AA1115" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC1115">
+        <f t="shared" si="165"/>
+        <v>6</v>
+      </c>
+      <c r="AD1115">
+        <f t="shared" si="166"/>
+        <v>0</v>
+      </c>
+      <c r="AE1115">
+        <f t="shared" si="167"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1116">
+        <v>1115</v>
+      </c>
+      <c r="B1116">
+        <v>2</v>
+      </c>
+      <c r="C1116" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D1116" s="2">
+        <v>0.94374999999999998</v>
+      </c>
+      <c r="E1116" s="2">
+        <v>0.94374999999999998</v>
+      </c>
+      <c r="F1116" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1116" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1116" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1116" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1116" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1116">
+        <v>2</v>
+      </c>
+      <c r="L1116">
+        <v>2</v>
+      </c>
+      <c r="M1116">
+        <v>6</v>
+      </c>
+      <c r="N1116">
+        <v>16</v>
+      </c>
+      <c r="O1116">
+        <v>4</v>
+      </c>
+      <c r="P1116">
+        <v>9</v>
+      </c>
+      <c r="Q1116">
+        <v>1935</v>
+      </c>
+      <c r="R1116">
+        <v>101</v>
+      </c>
+      <c r="S1116">
+        <v>33</v>
+      </c>
+      <c r="T1116" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1116">
+        <v>12575</v>
+      </c>
+      <c r="V1116">
+        <v>2</v>
+      </c>
+      <c r="AC1116">
+        <f t="shared" si="165"/>
+        <v>7</v>
+      </c>
+      <c r="AD1116">
+        <f t="shared" si="166"/>
+        <v>1</v>
+      </c>
+      <c r="AE1116">
+        <f t="shared" si="167"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1117">
+        <v>1116</v>
+      </c>
+      <c r="B1117">
+        <v>2</v>
+      </c>
+      <c r="C1117" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D1117" s="2">
+        <v>0.97083333333333333</v>
+      </c>
+      <c r="E1117" s="2">
+        <v>0.97083333333333333</v>
+      </c>
+      <c r="F1117" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1117" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1117" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1117" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1117">
+        <v>5</v>
+      </c>
+      <c r="L1117">
+        <v>4</v>
+      </c>
+      <c r="M1117">
+        <v>9</v>
+      </c>
+      <c r="N1117">
+        <v>1</v>
+      </c>
+      <c r="O1117">
+        <v>0</v>
+      </c>
+      <c r="P1117">
+        <v>4</v>
+      </c>
+      <c r="Q1117">
+        <v>1046</v>
+      </c>
+      <c r="R1117">
+        <v>65</v>
+      </c>
+      <c r="S1117">
+        <v>0</v>
+      </c>
+      <c r="T1117" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1117">
+        <v>12248</v>
+      </c>
+      <c r="V1117">
+        <v>2</v>
+      </c>
+      <c r="AC1117">
+        <f t="shared" si="165"/>
+        <v>8</v>
+      </c>
+      <c r="AD1117">
+        <f t="shared" si="166"/>
+        <v>2</v>
+      </c>
+      <c r="AE1117">
+        <f t="shared" si="167"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1118">
+        <v>1117</v>
+      </c>
+      <c r="B1118">
+        <v>1</v>
+      </c>
+      <c r="C1118" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D1118" s="2">
+        <v>0.82638888888888884</v>
+      </c>
+      <c r="E1118" s="2">
+        <v>0.82638888888888884</v>
+      </c>
+      <c r="F1118" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1118" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1118" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1118" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1118" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1118">
+        <v>10</v>
+      </c>
+      <c r="L1118">
+        <v>4</v>
+      </c>
+      <c r="M1118">
+        <v>7</v>
+      </c>
+      <c r="N1118">
+        <v>12</v>
+      </c>
+      <c r="O1118">
+        <v>4</v>
+      </c>
+      <c r="P1118">
+        <v>10</v>
+      </c>
+      <c r="Q1118">
+        <v>1855</v>
+      </c>
+      <c r="R1118">
+        <v>77</v>
+      </c>
+      <c r="S1118">
+        <v>18</v>
+      </c>
+      <c r="T1118" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1118">
+        <v>16521</v>
+      </c>
+      <c r="V1118">
+        <v>2</v>
+      </c>
+      <c r="AC1118" s="5">
+        <f>IF(C1118=C1117, AC1117+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1118" s="5">
+        <f>IF(T1118="Loss",AD1117+1,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AE1118" s="5">
+        <f>IF(T1118="Win", AE1117+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF1118" s="5"/>
+      <c r="AG1118" s="5"/>
+      <c r="AH1118" s="5"/>
+      <c r="AI1118" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F408985D-D6A4-43D4-844A-3170C4738E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBC5245-47EB-4523-9318-00F66277C612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-2100" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6930" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6965" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -601,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1118" totalsRowShown="0">
-  <autoFilter ref="A1:AI1118" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1124" totalsRowShown="0">
+  <autoFilter ref="A1:AI1124" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -956,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1118"/>
+  <dimension ref="A1:AI1124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -97402,22 +97402,480 @@
       <c r="V1118">
         <v>2</v>
       </c>
-      <c r="AC1118" s="5">
-        <f>IF(C1118=C1117, AC1117+1, 1)</f>
-        <v>1</v>
-      </c>
-      <c r="AD1118" s="5">
-        <f>IF(T1118="Loss",AD1117+1,0)</f>
-        <v>3</v>
-      </c>
-      <c r="AE1118" s="5">
-        <f>IF(T1118="Win", AE1117+1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF1118" s="5"/>
-      <c r="AG1118" s="5"/>
-      <c r="AH1118" s="5"/>
-      <c r="AI1118" s="5"/>
+      <c r="AC1118">
+        <f t="shared" ref="AC1118:AC1123" si="168">IF(C1118=C1117, AC1117+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1118">
+        <f t="shared" ref="AD1118:AD1123" si="169">IF(T1118="Loss",AD1117+1,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AE1118">
+        <f t="shared" ref="AE1118:AE1123" si="170">IF(T1118="Win", AE1117+1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1119">
+        <v>1118</v>
+      </c>
+      <c r="B1119">
+        <v>2</v>
+      </c>
+      <c r="C1119" s="1">
+        <v>46190</v>
+      </c>
+      <c r="F1119" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1119" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1119" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1119" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1119">
+        <v>16</v>
+      </c>
+      <c r="L1119">
+        <v>3</v>
+      </c>
+      <c r="M1119">
+        <v>11</v>
+      </c>
+      <c r="N1119">
+        <v>8</v>
+      </c>
+      <c r="O1119">
+        <v>4</v>
+      </c>
+      <c r="P1119">
+        <v>10</v>
+      </c>
+      <c r="R1119">
+        <v>87</v>
+      </c>
+      <c r="S1119">
+        <v>37</v>
+      </c>
+      <c r="T1119" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1119">
+        <v>11898</v>
+      </c>
+      <c r="V1119">
+        <v>2</v>
+      </c>
+      <c r="AC1119">
+        <f t="shared" si="168"/>
+        <v>1</v>
+      </c>
+      <c r="AD1119">
+        <f t="shared" si="169"/>
+        <v>4</v>
+      </c>
+      <c r="AE1119">
+        <f t="shared" si="170"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1120">
+        <v>1119</v>
+      </c>
+      <c r="B1120">
+        <v>2</v>
+      </c>
+      <c r="C1120" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D1120" s="2">
+        <v>0.8256944444444444</v>
+      </c>
+      <c r="E1120" s="2">
+        <v>0.8256944444444444</v>
+      </c>
+      <c r="F1120" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1120" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1120" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1120" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1120" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1120">
+        <v>2</v>
+      </c>
+      <c r="L1120">
+        <v>1</v>
+      </c>
+      <c r="M1120">
+        <v>4</v>
+      </c>
+      <c r="N1120">
+        <v>7</v>
+      </c>
+      <c r="O1120">
+        <v>2</v>
+      </c>
+      <c r="P1120">
+        <v>10</v>
+      </c>
+      <c r="Q1120">
+        <v>1318</v>
+      </c>
+      <c r="R1120">
+        <v>77</v>
+      </c>
+      <c r="S1120">
+        <v>33</v>
+      </c>
+      <c r="T1120" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1120">
+        <v>11538</v>
+      </c>
+      <c r="V1120">
+        <v>2</v>
+      </c>
+      <c r="AC1120">
+        <f t="shared" si="168"/>
+        <v>2</v>
+      </c>
+      <c r="AD1120">
+        <f t="shared" si="169"/>
+        <v>5</v>
+      </c>
+      <c r="AE1120">
+        <f t="shared" si="170"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1121">
+        <v>1120</v>
+      </c>
+      <c r="B1121">
+        <v>1</v>
+      </c>
+      <c r="C1121" s="1">
+        <v>46193</v>
+      </c>
+      <c r="D1121" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="E1121" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="F1121" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1121" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1121" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1121" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1121" t="s">
+        <v>53</v>
+      </c>
+      <c r="R1121">
+        <v>69</v>
+      </c>
+      <c r="S1121">
+        <v>40</v>
+      </c>
+      <c r="T1121" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1121">
+        <v>16403</v>
+      </c>
+      <c r="V1121">
+        <v>5</v>
+      </c>
+      <c r="AC1121">
+        <f t="shared" si="168"/>
+        <v>1</v>
+      </c>
+      <c r="AD1121">
+        <f t="shared" si="169"/>
+        <v>6</v>
+      </c>
+      <c r="AE1121">
+        <f t="shared" si="170"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1122">
+        <v>1121</v>
+      </c>
+      <c r="B1122">
+        <v>1</v>
+      </c>
+      <c r="C1122" s="1">
+        <v>46193</v>
+      </c>
+      <c r="D1122" s="2">
+        <v>0.92222222222222228</v>
+      </c>
+      <c r="E1122" s="2">
+        <v>0.92222222222222228</v>
+      </c>
+      <c r="F1122" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1122" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1122" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1122" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1122" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1122">
+        <v>1</v>
+      </c>
+      <c r="L1122">
+        <v>0</v>
+      </c>
+      <c r="M1122">
+        <v>12</v>
+      </c>
+      <c r="N1122">
+        <v>0</v>
+      </c>
+      <c r="O1122">
+        <v>0</v>
+      </c>
+      <c r="P1122">
+        <v>1</v>
+      </c>
+      <c r="Q1122">
+        <v>338</v>
+      </c>
+      <c r="R1122">
+        <v>26</v>
+      </c>
+      <c r="S1122">
+        <v>100</v>
+      </c>
+      <c r="T1122" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1122">
+        <v>16300</v>
+      </c>
+      <c r="V1122">
+        <v>5</v>
+      </c>
+      <c r="AC1122">
+        <f t="shared" si="168"/>
+        <v>2</v>
+      </c>
+      <c r="AD1122">
+        <f t="shared" si="169"/>
+        <v>7</v>
+      </c>
+      <c r="AE1122">
+        <f t="shared" si="170"/>
+        <v>0</v>
+      </c>
+      <c r="AF1122">
+        <v>-14.37</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1123">
+        <v>1122</v>
+      </c>
+      <c r="B1123">
+        <v>1</v>
+      </c>
+      <c r="C1123" s="1">
+        <v>46193</v>
+      </c>
+      <c r="D1123" s="2">
+        <v>0.94097222222222221</v>
+      </c>
+      <c r="E1123" s="2">
+        <v>0.94097222222222221</v>
+      </c>
+      <c r="F1123" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1123" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1123" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1123" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1123" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1123">
+        <v>1</v>
+      </c>
+      <c r="L1123">
+        <v>3</v>
+      </c>
+      <c r="M1123">
+        <v>9</v>
+      </c>
+      <c r="N1123">
+        <v>3</v>
+      </c>
+      <c r="O1123">
+        <v>11</v>
+      </c>
+      <c r="P1123">
+        <v>6</v>
+      </c>
+      <c r="Q1123">
+        <v>1061</v>
+      </c>
+      <c r="R1123">
+        <v>55</v>
+      </c>
+      <c r="S1123">
+        <v>25</v>
+      </c>
+      <c r="T1123" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1123">
+        <v>16067</v>
+      </c>
+      <c r="V1123">
+        <v>2</v>
+      </c>
+      <c r="AC1123">
+        <f t="shared" si="168"/>
+        <v>3</v>
+      </c>
+      <c r="AD1123">
+        <f t="shared" si="169"/>
+        <v>8</v>
+      </c>
+      <c r="AE1123">
+        <f t="shared" si="170"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1124">
+        <v>1123</v>
+      </c>
+      <c r="B1124">
+        <v>1</v>
+      </c>
+      <c r="C1124" s="1">
+        <v>46194</v>
+      </c>
+      <c r="D1124" s="2">
+        <v>0.78194444444444444</v>
+      </c>
+      <c r="E1124" s="2">
+        <v>0.78194444444444444</v>
+      </c>
+      <c r="F1124" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1124" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1124" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1124" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1124" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1124">
+        <v>5</v>
+      </c>
+      <c r="L1124">
+        <v>3</v>
+      </c>
+      <c r="M1124">
+        <v>11</v>
+      </c>
+      <c r="N1124">
+        <v>7</v>
+      </c>
+      <c r="O1124">
+        <v>1</v>
+      </c>
+      <c r="P1124">
+        <v>8</v>
+      </c>
+      <c r="Q1124">
+        <v>1561</v>
+      </c>
+      <c r="R1124">
+        <v>55</v>
+      </c>
+      <c r="S1124">
+        <v>33</v>
+      </c>
+      <c r="T1124" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1124">
+        <v>15726</v>
+      </c>
+      <c r="V1124">
+        <v>2</v>
+      </c>
+      <c r="AC1124" s="5">
+        <f>IF(C1124=C1123, AC1123+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1124" s="5">
+        <f>IF(T1124="Loss",AD1123+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1124" s="5">
+        <f>IF(T1124="Win", AE1123+1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF1124" s="5">
+        <v>-1.48</v>
+      </c>
+      <c r="AG1124" s="5">
+        <v>28</v>
+      </c>
+      <c r="AH1124" s="5">
+        <v>56</v>
+      </c>
+      <c r="AI1124" s="5">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBC5245-47EB-4523-9318-00F66277C612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6777A83C-ECA7-41BF-91E5-B0287198CADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-2100" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6965" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7007" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -601,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1124" totalsRowShown="0">
-  <autoFilter ref="A1:AI1124" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1131" totalsRowShown="0">
+  <autoFilter ref="A1:AI1131" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -956,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1124"/>
+  <dimension ref="A1:AI1131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -97852,30 +97852,582 @@
       <c r="V1124">
         <v>2</v>
       </c>
-      <c r="AC1124" s="5">
-        <f>IF(C1124=C1123, AC1123+1, 1)</f>
-        <v>1</v>
-      </c>
-      <c r="AD1124" s="5">
-        <f>IF(T1124="Loss",AD1123+1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE1124" s="5">
-        <f>IF(T1124="Win", AE1123+1, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="AF1124" s="5">
+      <c r="AC1124">
+        <f t="shared" ref="AC1124:AC1129" si="171">IF(C1124=C1123, AC1123+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1124">
+        <f t="shared" ref="AD1124:AD1129" si="172">IF(T1124="Loss",AD1123+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1124">
+        <f t="shared" ref="AE1124:AE1129" si="173">IF(T1124="Win", AE1123+1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF1124">
         <v>-1.48</v>
       </c>
-      <c r="AG1124" s="5">
+      <c r="AG1124">
         <v>28</v>
       </c>
-      <c r="AH1124" s="5">
+      <c r="AH1124">
         <v>56</v>
       </c>
-      <c r="AI1124" s="5">
+      <c r="AI1124">
         <v>60</v>
       </c>
+    </row>
+    <row r="1125" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1125">
+        <v>1124</v>
+      </c>
+      <c r="B1125">
+        <v>1</v>
+      </c>
+      <c r="C1125" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D1125" s="2">
+        <v>0.79236111111111107</v>
+      </c>
+      <c r="E1125" s="2">
+        <v>0.79236111111111107</v>
+      </c>
+      <c r="F1125" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1125" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1125" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1125" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1125" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1125">
+        <v>6</v>
+      </c>
+      <c r="L1125">
+        <v>2</v>
+      </c>
+      <c r="M1125">
+        <v>10</v>
+      </c>
+      <c r="N1125">
+        <v>7</v>
+      </c>
+      <c r="O1125">
+        <v>5</v>
+      </c>
+      <c r="P1125">
+        <v>7</v>
+      </c>
+      <c r="Q1125">
+        <v>1640</v>
+      </c>
+      <c r="R1125">
+        <v>71</v>
+      </c>
+      <c r="T1125" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1125">
+        <v>16078</v>
+      </c>
+      <c r="V1125">
+        <v>5</v>
+      </c>
+      <c r="AC1125">
+        <f t="shared" si="171"/>
+        <v>1</v>
+      </c>
+      <c r="AD1125">
+        <f t="shared" si="172"/>
+        <v>1</v>
+      </c>
+      <c r="AE1125">
+        <f t="shared" si="173"/>
+        <v>0</v>
+      </c>
+      <c r="AF1125">
+        <v>-5.98</v>
+      </c>
+      <c r="AG1125">
+        <v>53</v>
+      </c>
+      <c r="AH1125">
+        <v>43</v>
+      </c>
+      <c r="AI1125">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1126">
+        <v>1125</v>
+      </c>
+      <c r="B1126">
+        <v>1</v>
+      </c>
+      <c r="C1126" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D1126" s="2">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="E1126" s="2">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="F1126" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1126" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1126" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1126" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1126" t="s">
+        <v>57</v>
+      </c>
+      <c r="T1126" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1126">
+        <v>15769</v>
+      </c>
+      <c r="V1126">
+        <v>5</v>
+      </c>
+      <c r="AC1126">
+        <f t="shared" si="171"/>
+        <v>2</v>
+      </c>
+      <c r="AD1126">
+        <f t="shared" si="172"/>
+        <v>0</v>
+      </c>
+      <c r="AE1126">
+        <f t="shared" si="173"/>
+        <v>1</v>
+      </c>
+      <c r="AF1126">
+        <v>-0.46</v>
+      </c>
+      <c r="AG1126">
+        <v>27</v>
+      </c>
+      <c r="AH1126">
+        <v>77</v>
+      </c>
+      <c r="AI1126">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1127">
+        <v>1126</v>
+      </c>
+      <c r="B1127">
+        <v>1</v>
+      </c>
+      <c r="C1127" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D1127" s="2">
+        <v>0.88263888888888886</v>
+      </c>
+      <c r="E1127" s="2">
+        <v>0.88263888888888886</v>
+      </c>
+      <c r="F1127" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1127" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1127" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1127" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1127" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1127">
+        <v>5</v>
+      </c>
+      <c r="L1127">
+        <v>1</v>
+      </c>
+      <c r="M1127">
+        <v>11</v>
+      </c>
+      <c r="N1127">
+        <v>1</v>
+      </c>
+      <c r="O1127">
+        <v>0</v>
+      </c>
+      <c r="P1127">
+        <v>5</v>
+      </c>
+      <c r="Q1127">
+        <v>1067</v>
+      </c>
+      <c r="R1127">
+        <v>59</v>
+      </c>
+      <c r="S1127">
+        <v>33</v>
+      </c>
+      <c r="T1127" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1127">
+        <v>16142</v>
+      </c>
+      <c r="V1127">
+        <v>1</v>
+      </c>
+      <c r="AC1127">
+        <f t="shared" si="171"/>
+        <v>3</v>
+      </c>
+      <c r="AD1127">
+        <f t="shared" si="172"/>
+        <v>1</v>
+      </c>
+      <c r="AE1127">
+        <f t="shared" si="173"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1128">
+        <v>1127</v>
+      </c>
+      <c r="B1128">
+        <v>1</v>
+      </c>
+      <c r="C1128" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D1128" s="2">
+        <v>0.91388888888888886</v>
+      </c>
+      <c r="E1128" s="2">
+        <v>0.91388888888888886</v>
+      </c>
+      <c r="F1128" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1128" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1128" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1128" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1128" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1128">
+        <v>4</v>
+      </c>
+      <c r="L1128">
+        <v>4</v>
+      </c>
+      <c r="M1128">
+        <v>6</v>
+      </c>
+      <c r="N1128">
+        <v>9</v>
+      </c>
+      <c r="O1128">
+        <v>3</v>
+      </c>
+      <c r="P1128">
+        <v>7</v>
+      </c>
+      <c r="Q1128">
+        <v>1453</v>
+      </c>
+      <c r="R1128">
+        <v>69</v>
+      </c>
+      <c r="T1128" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1128">
+        <v>15916</v>
+      </c>
+      <c r="V1128">
+        <v>1</v>
+      </c>
+      <c r="AC1128">
+        <f t="shared" si="171"/>
+        <v>4</v>
+      </c>
+      <c r="AD1128">
+        <f t="shared" si="172"/>
+        <v>2</v>
+      </c>
+      <c r="AE1128">
+        <f t="shared" si="173"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1129">
+        <v>1128</v>
+      </c>
+      <c r="B1129">
+        <v>1</v>
+      </c>
+      <c r="C1129" s="1">
+        <v>46200</v>
+      </c>
+      <c r="D1129" s="2">
+        <v>0.84652777777777777</v>
+      </c>
+      <c r="E1129" s="2">
+        <v>0.84652777777777777</v>
+      </c>
+      <c r="F1129" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1129" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1129" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1129" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1129" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1129">
+        <v>9</v>
+      </c>
+      <c r="L1129">
+        <v>4</v>
+      </c>
+      <c r="M1129">
+        <v>12</v>
+      </c>
+      <c r="N1129">
+        <v>10</v>
+      </c>
+      <c r="O1129">
+        <v>2</v>
+      </c>
+      <c r="P1129">
+        <v>9</v>
+      </c>
+      <c r="Q1129">
+        <v>2015</v>
+      </c>
+      <c r="R1129">
+        <v>67</v>
+      </c>
+      <c r="T1129" t="s">
+        <v>65</v>
+      </c>
+      <c r="U1129">
+        <v>15536</v>
+      </c>
+      <c r="V1129">
+        <v>1</v>
+      </c>
+      <c r="AC1129">
+        <f t="shared" si="171"/>
+        <v>1</v>
+      </c>
+      <c r="AD1129">
+        <f t="shared" si="172"/>
+        <v>0</v>
+      </c>
+      <c r="AE1129">
+        <f t="shared" si="173"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1130">
+        <v>1129</v>
+      </c>
+      <c r="B1130">
+        <v>2</v>
+      </c>
+      <c r="C1130" s="1">
+        <v>46201</v>
+      </c>
+      <c r="D1130" s="2">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="E1130" s="2">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="F1130" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1130" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1130" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1130" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1130" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1130">
+        <v>5</v>
+      </c>
+      <c r="L1130">
+        <v>2</v>
+      </c>
+      <c r="M1130">
+        <v>7</v>
+      </c>
+      <c r="N1130">
+        <v>12</v>
+      </c>
+      <c r="O1130">
+        <v>3</v>
+      </c>
+      <c r="P1130">
+        <v>10</v>
+      </c>
+      <c r="Q1130">
+        <v>1806</v>
+      </c>
+      <c r="R1130">
+        <v>86</v>
+      </c>
+      <c r="S1130">
+        <v>35</v>
+      </c>
+      <c r="T1130" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1130">
+        <v>11178</v>
+      </c>
+      <c r="V1130">
+        <v>5</v>
+      </c>
+      <c r="AC1130">
+        <f>IF(C1130=C1129, AC1129+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1130">
+        <f>IF(T1130="Loss",AD1129+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1130">
+        <f>IF(T1130="Win", AE1129+1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1131">
+        <v>1130</v>
+      </c>
+      <c r="B1131">
+        <v>1</v>
+      </c>
+      <c r="C1131" s="1">
+        <v>46201</v>
+      </c>
+      <c r="D1131" s="2">
+        <v>0.72152777777777777</v>
+      </c>
+      <c r="E1131" s="2">
+        <v>0.72152777777777777</v>
+      </c>
+      <c r="F1131" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1131" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1131" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1131" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1131" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1131">
+        <v>2</v>
+      </c>
+      <c r="L1131">
+        <v>5</v>
+      </c>
+      <c r="M1131">
+        <v>9</v>
+      </c>
+      <c r="N1131">
+        <v>11</v>
+      </c>
+      <c r="O1131">
+        <v>4</v>
+      </c>
+      <c r="P1131">
+        <v>5</v>
+      </c>
+      <c r="Q1131">
+        <v>1515</v>
+      </c>
+      <c r="R1131">
+        <v>72</v>
+      </c>
+      <c r="S1131">
+        <v>23</v>
+      </c>
+      <c r="T1131" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1131">
+        <v>15474</v>
+      </c>
+      <c r="V1131">
+        <v>1</v>
+      </c>
+      <c r="AC1131" s="5">
+        <f>IF(C1131=C1130, AC1130+1, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AD1131" s="5">
+        <f>IF(T1131="Loss",AD1130+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1131" s="5">
+        <f>IF(T1131="Win", AE1130+1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF1131" s="5"/>
+      <c r="AG1131" s="5"/>
+      <c r="AH1131" s="5"/>
+      <c r="AI1131" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6777A83C-ECA7-41BF-91E5-B0287198CADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A88E54-6318-45B5-9E16-5764F6EFF28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-2100" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7007" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7031" uniqueCount="119">
   <si>
     <t>ID</t>
   </si>
@@ -514,6 +514,9 @@
   <si>
     <t>BC-&gt;S</t>
   </si>
+  <si>
+    <t>FIrst</t>
+  </si>
 </sst>
 </file>
 
@@ -548,13 +551,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -601,8 +603,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1131" totalsRowShown="0">
-  <autoFilter ref="A1:AI1131" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1135" totalsRowShown="0">
+  <autoFilter ref="A1:AI1135" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -956,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1131"/>
+  <dimension ref="A1:AI1135"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -98333,15 +98335,15 @@
         <v>5</v>
       </c>
       <c r="AC1130">
-        <f>IF(C1130=C1129, AC1129+1, 1)</f>
+        <f t="shared" ref="AC1130:AC1135" si="174">IF(C1130=C1129, AC1129+1, 1)</f>
         <v>1</v>
       </c>
       <c r="AD1130">
-        <f>IF(T1130="Loss",AD1129+1,0)</f>
+        <f t="shared" ref="AD1130:AD1135" si="175">IF(T1130="Loss",AD1129+1,0)</f>
         <v>1</v>
       </c>
       <c r="AE1130">
-        <f>IF(T1130="Win", AE1129+1, 0)</f>
+        <f t="shared" ref="AE1130:AE1135" si="176">IF(T1130="Win", AE1129+1, 0)</f>
         <v>0</v>
       </c>
     </row>
@@ -98412,22 +98414,344 @@
       <c r="V1131">
         <v>1</v>
       </c>
-      <c r="AC1131" s="5">
-        <f>IF(C1131=C1130, AC1130+1, 1)</f>
-        <v>2</v>
-      </c>
-      <c r="AD1131" s="5">
-        <f>IF(T1131="Loss",AD1130+1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE1131" s="5">
-        <f>IF(T1131="Win", AE1130+1, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="AF1131" s="5"/>
-      <c r="AG1131" s="5"/>
-      <c r="AH1131" s="5"/>
-      <c r="AI1131" s="5"/>
+      <c r="AC1131">
+        <f t="shared" si="174"/>
+        <v>2</v>
+      </c>
+      <c r="AD1131">
+        <f t="shared" si="175"/>
+        <v>0</v>
+      </c>
+      <c r="AE1131">
+        <f t="shared" si="176"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1132">
+        <v>1131</v>
+      </c>
+      <c r="B1132">
+        <v>1</v>
+      </c>
+      <c r="C1132" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D1132" s="2">
+        <v>0.76458333333333328</v>
+      </c>
+      <c r="E1132" s="2">
+        <v>0.76458333333333328</v>
+      </c>
+      <c r="F1132" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1132" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1132" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1132" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1132" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1132">
+        <v>10</v>
+      </c>
+      <c r="L1132">
+        <v>3</v>
+      </c>
+      <c r="M1132">
+        <v>12</v>
+      </c>
+      <c r="N1132">
+        <v>12</v>
+      </c>
+      <c r="O1132">
+        <v>0</v>
+      </c>
+      <c r="P1132">
+        <v>9</v>
+      </c>
+      <c r="Q1132">
+        <v>2446</v>
+      </c>
+      <c r="R1132">
+        <v>81</v>
+      </c>
+      <c r="T1132" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1132">
+        <v>15747</v>
+      </c>
+      <c r="V1132">
+        <v>1</v>
+      </c>
+      <c r="AC1132">
+        <f t="shared" si="174"/>
+        <v>1</v>
+      </c>
+      <c r="AD1132">
+        <f t="shared" si="175"/>
+        <v>1</v>
+      </c>
+      <c r="AE1132">
+        <f t="shared" si="176"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1133">
+        <v>1132</v>
+      </c>
+      <c r="B1133">
+        <v>1</v>
+      </c>
+      <c r="C1133" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D1133" s="2">
+        <v>0.81805555555555554</v>
+      </c>
+      <c r="E1133" s="2">
+        <v>0.81805555555555554</v>
+      </c>
+      <c r="F1133" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1133" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1133" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1133" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1133" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1133">
+        <v>9</v>
+      </c>
+      <c r="L1133">
+        <v>1</v>
+      </c>
+      <c r="M1133">
+        <v>3</v>
+      </c>
+      <c r="N1133">
+        <v>17</v>
+      </c>
+      <c r="O1133">
+        <v>1</v>
+      </c>
+      <c r="P1133">
+        <v>5</v>
+      </c>
+      <c r="Q1133">
+        <v>1813</v>
+      </c>
+      <c r="R1133">
+        <v>95</v>
+      </c>
+      <c r="S1133">
+        <v>57</v>
+      </c>
+      <c r="T1133" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1133">
+        <v>15402</v>
+      </c>
+      <c r="V1133">
+        <v>1</v>
+      </c>
+      <c r="AC1133">
+        <f t="shared" si="174"/>
+        <v>2</v>
+      </c>
+      <c r="AD1133">
+        <f t="shared" si="175"/>
+        <v>0</v>
+      </c>
+      <c r="AE1133">
+        <f t="shared" si="176"/>
+        <v>1</v>
+      </c>
+      <c r="AF1133">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="AG1133">
+        <v>45</v>
+      </c>
+      <c r="AH1133">
+        <v>92</v>
+      </c>
+      <c r="AI1133">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1134">
+        <v>1133</v>
+      </c>
+      <c r="B1134">
+        <v>1</v>
+      </c>
+      <c r="C1134" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D1134" s="2">
+        <v>0.84791666666666665</v>
+      </c>
+      <c r="E1134" s="2">
+        <v>0.84791666666666665</v>
+      </c>
+      <c r="F1134" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1134" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1134" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1134" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1134" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1134">
+        <v>9</v>
+      </c>
+      <c r="L1134">
+        <v>5</v>
+      </c>
+      <c r="M1134">
+        <v>14</v>
+      </c>
+      <c r="N1134">
+        <v>12</v>
+      </c>
+      <c r="O1134">
+        <v>3</v>
+      </c>
+      <c r="P1134">
+        <v>9</v>
+      </c>
+      <c r="Q1134">
+        <v>2319</v>
+      </c>
+      <c r="R1134">
+        <v>77</v>
+      </c>
+      <c r="T1134" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1134">
+        <v>15611</v>
+      </c>
+      <c r="V1134">
+        <v>1</v>
+      </c>
+      <c r="AC1134">
+        <f t="shared" si="174"/>
+        <v>3</v>
+      </c>
+      <c r="AD1134">
+        <f t="shared" si="175"/>
+        <v>0</v>
+      </c>
+      <c r="AE1134">
+        <f t="shared" si="176"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1135">
+        <v>1134</v>
+      </c>
+      <c r="B1135">
+        <v>1</v>
+      </c>
+      <c r="C1135" s="1">
+        <v>46207</v>
+      </c>
+      <c r="D1135" s="2">
+        <v>0.78055555555555556</v>
+      </c>
+      <c r="E1135" s="2">
+        <v>0.78055555555555556</v>
+      </c>
+      <c r="F1135" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1135" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1135" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1135" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1135" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1135">
+        <v>4</v>
+      </c>
+      <c r="L1135">
+        <v>3</v>
+      </c>
+      <c r="M1135">
+        <v>3</v>
+      </c>
+      <c r="N1135">
+        <v>14</v>
+      </c>
+      <c r="O1135">
+        <v>3</v>
+      </c>
+      <c r="P1135">
+        <v>4</v>
+      </c>
+      <c r="Q1135">
+        <v>1698</v>
+      </c>
+      <c r="R1135">
+        <v>94</v>
+      </c>
+      <c r="S1135">
+        <v>11</v>
+      </c>
+      <c r="T1135" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1135">
+        <v>15970</v>
+      </c>
+      <c r="V1135">
+        <v>1</v>
+      </c>
+      <c r="AC1135">
+        <f t="shared" si="174"/>
+        <v>1</v>
+      </c>
+      <c r="AD1135">
+        <f t="shared" si="175"/>
+        <v>0</v>
+      </c>
+      <c r="AE1135">
+        <f t="shared" si="176"/>
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A88E54-6318-45B5-9E16-5764F6EFF28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5881BE9-1AF6-40CC-B48C-623B21839E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-2100" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7031" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7051" uniqueCount="120">
   <si>
     <t>ID</t>
   </si>
@@ -517,6 +517,9 @@
   <si>
     <t>FIrst</t>
   </si>
+  <si>
+    <t>Season Five. -Overpass +Cache</t>
+  </si>
 </sst>
 </file>
 
@@ -551,12 +554,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -603,8 +607,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1135" totalsRowShown="0">
-  <autoFilter ref="A1:AI1135" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1138" totalsRowShown="0">
+  <autoFilter ref="A1:AI1138" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -958,7 +962,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1135"/>
+  <dimension ref="A1:AI1138"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -98753,6 +98757,234 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1136" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1136">
+        <v>1135</v>
+      </c>
+      <c r="B1136">
+        <v>1</v>
+      </c>
+      <c r="C1136" s="1">
+        <v>46216</v>
+      </c>
+      <c r="D1136" s="2">
+        <v>0.77222222222222225</v>
+      </c>
+      <c r="E1136" s="2">
+        <v>0.77222222222222225</v>
+      </c>
+      <c r="F1136" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1136" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1136" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1136" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1136" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1136">
+        <v>5</v>
+      </c>
+      <c r="L1136">
+        <v>3</v>
+      </c>
+      <c r="M1136">
+        <v>8</v>
+      </c>
+      <c r="N1136">
+        <v>3</v>
+      </c>
+      <c r="O1136">
+        <v>3</v>
+      </c>
+      <c r="P1136">
+        <v>9</v>
+      </c>
+      <c r="Q1136">
+        <v>1322</v>
+      </c>
+      <c r="R1136">
+        <v>60</v>
+      </c>
+      <c r="S1136">
+        <v>25</v>
+      </c>
+      <c r="T1136" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1136" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1136">
+        <v>1</v>
+      </c>
+      <c r="AC1136" s="5">
+        <f>IF(C1136=C1135, AC1135+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1136" s="5">
+        <f>IF(T1136="Loss",AD1135+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1136" s="5">
+        <f>IF(T1136="Win", AE1135+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF1136" s="5"/>
+      <c r="AG1136" s="5"/>
+      <c r="AH1136" s="5"/>
+      <c r="AI1136" s="5"/>
+    </row>
+    <row r="1137" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1137">
+        <v>1136</v>
+      </c>
+      <c r="B1137">
+        <v>1</v>
+      </c>
+      <c r="C1137" s="1">
+        <v>46216</v>
+      </c>
+      <c r="D1137" s="2">
+        <v>0.80347222222222225</v>
+      </c>
+      <c r="E1137" s="2">
+        <v>0.80347222222222225</v>
+      </c>
+      <c r="F1137" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1137" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1137" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1137" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1137">
+        <v>6</v>
+      </c>
+      <c r="L1137">
+        <v>3</v>
+      </c>
+      <c r="M1137">
+        <v>8</v>
+      </c>
+      <c r="N1137">
+        <v>6</v>
+      </c>
+      <c r="O1137">
+        <v>4</v>
+      </c>
+      <c r="P1137">
+        <v>8</v>
+      </c>
+      <c r="T1137" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1137" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1137">
+        <v>1</v>
+      </c>
+      <c r="AC1137" s="5">
+        <f>IF(C1137=C1136, AC1136+1, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AD1137" s="5">
+        <f>IF(T1137="Loss",AD1136+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1137" s="5">
+        <f>IF(T1137="Win", AE1136+1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF1137" s="5"/>
+      <c r="AG1137" s="5"/>
+      <c r="AH1137" s="5"/>
+      <c r="AI1137" s="5"/>
+    </row>
+    <row r="1138" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1138">
+        <v>1137</v>
+      </c>
+      <c r="B1138">
+        <v>1</v>
+      </c>
+      <c r="C1138" s="1">
+        <v>46216</v>
+      </c>
+      <c r="D1138" s="2">
+        <v>0.8305555555555556</v>
+      </c>
+      <c r="E1138" s="2">
+        <v>0.8305555555555556</v>
+      </c>
+      <c r="F1138" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1138" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1138" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1138" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1138" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1138">
+        <v>5</v>
+      </c>
+      <c r="L1138">
+        <v>4</v>
+      </c>
+      <c r="M1138">
+        <v>7</v>
+      </c>
+      <c r="N1138">
+        <v>8</v>
+      </c>
+      <c r="O1138">
+        <v>5</v>
+      </c>
+      <c r="P1138">
+        <v>9</v>
+      </c>
+      <c r="U1138" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1138">
+        <v>5</v>
+      </c>
+      <c r="AC1138" s="5">
+        <f>IF(C1138=C1137, AC1137+1, 1)</f>
+        <v>3</v>
+      </c>
+      <c r="AD1138" s="5">
+        <f>IF(T1138="Loss",AD1137+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1138" s="5">
+        <f>IF(T1138="Win", AE1137+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF1138" s="5"/>
+      <c r="AG1138" s="5"/>
+      <c r="AH1138" s="5"/>
+      <c r="AI1138" s="5"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -98914,7 +99146,7 @@
         <v>24</v>
       </c>
       <c r="H8" s="3">
-        <v>45678</v>
+        <v>46043</v>
       </c>
       <c r="I8" t="s">
         <v>116</v>
@@ -98926,6 +99158,12 @@
       </c>
       <c r="B9" t="s">
         <v>27</v>
+      </c>
+      <c r="H9" s="3">
+        <v>46211</v>
+      </c>
+      <c r="I9" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5881BE9-1AF6-40CC-B48C-623B21839E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB5410F-E6CE-400A-8DF0-939973BF5F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-2100" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7051" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7135" uniqueCount="121">
   <si>
     <t>ID</t>
   </si>
@@ -520,6 +520,9 @@
   <si>
     <t>Season Five. -Overpass +Cache</t>
   </si>
+  <si>
+    <t>Cache</t>
+  </si>
 </sst>
 </file>
 
@@ -607,8 +610,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1138" totalsRowShown="0">
-  <autoFilter ref="A1:AI1138" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1150" totalsRowShown="0">
+  <autoFilter ref="A1:AI1150" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -962,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1138"/>
+  <dimension ref="A1:AI1150"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -98824,22 +98827,18 @@
       <c r="V1136">
         <v>1</v>
       </c>
-      <c r="AC1136" s="5">
-        <f>IF(C1136=C1135, AC1135+1, 1)</f>
-        <v>1</v>
-      </c>
-      <c r="AD1136" s="5">
-        <f>IF(T1136="Loss",AD1135+1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AE1136" s="5">
-        <f>IF(T1136="Win", AE1135+1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF1136" s="5"/>
-      <c r="AG1136" s="5"/>
-      <c r="AH1136" s="5"/>
-      <c r="AI1136" s="5"/>
+      <c r="AC1136">
+        <f t="shared" ref="AC1136:AC1142" si="177">IF(C1136=C1135, AC1135+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1136">
+        <f t="shared" ref="AD1136:AD1142" si="178">IF(T1136="Loss",AD1135+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1136">
+        <f t="shared" ref="AE1136:AE1142" si="179">IF(T1136="Win", AE1135+1, 0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="1137" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1137">
@@ -98888,7 +98887,7 @@
         <v>8</v>
       </c>
       <c r="T1137" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="U1137" t="s">
         <v>108</v>
@@ -98896,22 +98895,18 @@
       <c r="V1137">
         <v>1</v>
       </c>
-      <c r="AC1137" s="5">
-        <f>IF(C1137=C1136, AC1136+1, 1)</f>
-        <v>2</v>
-      </c>
-      <c r="AD1137" s="5">
-        <f>IF(T1137="Loss",AD1136+1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE1137" s="5">
-        <f>IF(T1137="Win", AE1136+1, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="AF1137" s="5"/>
-      <c r="AG1137" s="5"/>
-      <c r="AH1137" s="5"/>
-      <c r="AI1137" s="5"/>
+      <c r="AC1137">
+        <f t="shared" si="177"/>
+        <v>2</v>
+      </c>
+      <c r="AD1137">
+        <f t="shared" si="178"/>
+        <v>2</v>
+      </c>
+      <c r="AE1137">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="1138" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1138">
@@ -98962,28 +98957,888 @@
       <c r="P1138">
         <v>9</v>
       </c>
+      <c r="T1138" t="s">
+        <v>63</v>
+      </c>
       <c r="U1138" t="s">
         <v>108</v>
       </c>
       <c r="V1138">
         <v>5</v>
       </c>
-      <c r="AC1138" s="5">
-        <f>IF(C1138=C1137, AC1137+1, 1)</f>
-        <v>3</v>
-      </c>
-      <c r="AD1138" s="5">
-        <f>IF(T1138="Loss",AD1137+1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE1138" s="5">
-        <f>IF(T1138="Win", AE1137+1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF1138" s="5"/>
-      <c r="AG1138" s="5"/>
-      <c r="AH1138" s="5"/>
-      <c r="AI1138" s="5"/>
+      <c r="AC1138">
+        <f t="shared" si="177"/>
+        <v>3</v>
+      </c>
+      <c r="AD1138">
+        <f t="shared" si="178"/>
+        <v>0</v>
+      </c>
+      <c r="AE1138">
+        <f t="shared" si="179"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1139">
+        <v>1138</v>
+      </c>
+      <c r="B1139">
+        <v>1</v>
+      </c>
+      <c r="C1139" s="1">
+        <v>46217</v>
+      </c>
+      <c r="D1139" s="2">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="E1139" s="2">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="F1139" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1139" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1139" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1139" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1139" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1139">
+        <v>4</v>
+      </c>
+      <c r="L1139">
+        <v>7</v>
+      </c>
+      <c r="M1139">
+        <v>11</v>
+      </c>
+      <c r="N1139">
+        <v>4</v>
+      </c>
+      <c r="O1139">
+        <v>0</v>
+      </c>
+      <c r="P1139">
+        <v>7</v>
+      </c>
+      <c r="Q1139">
+        <v>1143</v>
+      </c>
+      <c r="R1139">
+        <v>57</v>
+      </c>
+      <c r="T1139" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1139" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1139">
+        <v>1</v>
+      </c>
+      <c r="AC1139">
+        <f t="shared" si="177"/>
+        <v>1</v>
+      </c>
+      <c r="AD1139">
+        <f t="shared" si="178"/>
+        <v>1</v>
+      </c>
+      <c r="AE1139">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1140">
+        <v>1139</v>
+      </c>
+      <c r="B1140">
+        <v>1</v>
+      </c>
+      <c r="C1140" s="1">
+        <v>46217</v>
+      </c>
+      <c r="D1140" s="2">
+        <v>0.82013888888888886</v>
+      </c>
+      <c r="E1140" s="2">
+        <v>0.82013888888888886</v>
+      </c>
+      <c r="F1140" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1140" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1140" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1140" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1140" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1140">
+        <v>6</v>
+      </c>
+      <c r="L1140">
+        <v>3</v>
+      </c>
+      <c r="M1140">
+        <v>8</v>
+      </c>
+      <c r="N1140">
+        <v>5</v>
+      </c>
+      <c r="O1140">
+        <v>1</v>
+      </c>
+      <c r="P1140">
+        <v>6</v>
+      </c>
+      <c r="R1140">
+        <v>70</v>
+      </c>
+      <c r="S1140">
+        <v>27</v>
+      </c>
+      <c r="T1140" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1140" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1140">
+        <v>1</v>
+      </c>
+      <c r="AC1140">
+        <f t="shared" si="177"/>
+        <v>2</v>
+      </c>
+      <c r="AD1140">
+        <f t="shared" si="178"/>
+        <v>2</v>
+      </c>
+      <c r="AE1140">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1141">
+        <v>1140</v>
+      </c>
+      <c r="B1141">
+        <v>1</v>
+      </c>
+      <c r="C1141" s="1">
+        <v>46218</v>
+      </c>
+      <c r="D1141" s="2">
+        <v>0.80902777777777779</v>
+      </c>
+      <c r="E1141" s="2">
+        <v>0.80902777777777779</v>
+      </c>
+      <c r="F1141" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1141" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1141" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1141" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1141" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1141">
+        <v>4</v>
+      </c>
+      <c r="L1141">
+        <v>4</v>
+      </c>
+      <c r="M1141">
+        <v>9</v>
+      </c>
+      <c r="N1141">
+        <v>2</v>
+      </c>
+      <c r="O1141">
+        <v>8</v>
+      </c>
+      <c r="P1141">
+        <v>9</v>
+      </c>
+      <c r="Q1141">
+        <v>1559</v>
+      </c>
+      <c r="R1141">
+        <v>64</v>
+      </c>
+      <c r="S1141">
+        <v>33</v>
+      </c>
+      <c r="T1141" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1141" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1141">
+        <v>1</v>
+      </c>
+      <c r="AC1141">
+        <f t="shared" si="177"/>
+        <v>1</v>
+      </c>
+      <c r="AD1141">
+        <f t="shared" si="178"/>
+        <v>0</v>
+      </c>
+      <c r="AE1141">
+        <f t="shared" si="179"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1142">
+        <v>1141</v>
+      </c>
+      <c r="B1142">
+        <v>1</v>
+      </c>
+      <c r="C1142" s="1">
+        <v>46219</v>
+      </c>
+      <c r="D1142" s="2">
+        <v>0.74444444444444446</v>
+      </c>
+      <c r="E1142" s="2">
+        <v>0.74444444444444446</v>
+      </c>
+      <c r="F1142" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1142" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1142" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1142" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1142" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q1142">
+        <v>2222</v>
+      </c>
+      <c r="R1142">
+        <v>111</v>
+      </c>
+      <c r="S1142">
+        <v>47</v>
+      </c>
+      <c r="T1142" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1142" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1142">
+        <v>1</v>
+      </c>
+      <c r="AC1142">
+        <f t="shared" si="177"/>
+        <v>1</v>
+      </c>
+      <c r="AD1142">
+        <f t="shared" si="178"/>
+        <v>0</v>
+      </c>
+      <c r="AE1142">
+        <f t="shared" si="179"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1143">
+        <v>1142</v>
+      </c>
+      <c r="B1143">
+        <v>1</v>
+      </c>
+      <c r="C1143" s="1">
+        <v>46220</v>
+      </c>
+      <c r="D1143" s="2">
+        <v>0.80277777777777781</v>
+      </c>
+      <c r="E1143" s="2">
+        <v>0.80277777777777781</v>
+      </c>
+      <c r="F1143" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1143" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1143" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1143" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1143" t="s">
+        <v>57</v>
+      </c>
+      <c r="T1143" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1143" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1143">
+        <v>1</v>
+      </c>
+      <c r="AA1143" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC1143">
+        <f t="shared" ref="AC1143:AC1148" si="180">IF(C1143=C1142, AC1142+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1143">
+        <f t="shared" ref="AD1143:AD1148" si="181">IF(T1143="Loss",AD1142+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1143">
+        <f t="shared" ref="AE1143:AE1148" si="182">IF(T1143="Win", AE1142+1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1144">
+        <v>1143</v>
+      </c>
+      <c r="B1144">
+        <v>1</v>
+      </c>
+      <c r="C1144" s="1">
+        <v>46220</v>
+      </c>
+      <c r="D1144" s="2">
+        <v>0.82777777777777772</v>
+      </c>
+      <c r="E1144" s="2">
+        <v>0.82777777777777772</v>
+      </c>
+      <c r="F1144" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1144" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1144" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1144" t="s">
+        <v>120</v>
+      </c>
+      <c r="J1144" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1144">
+        <v>9</v>
+      </c>
+      <c r="L1144">
+        <v>1</v>
+      </c>
+      <c r="M1144">
+        <v>8</v>
+      </c>
+      <c r="N1144">
+        <v>14</v>
+      </c>
+      <c r="O1144">
+        <v>4</v>
+      </c>
+      <c r="P1144">
+        <v>8</v>
+      </c>
+      <c r="Q1144">
+        <v>2108</v>
+      </c>
+      <c r="R1144">
+        <v>87</v>
+      </c>
+      <c r="S1144">
+        <v>21</v>
+      </c>
+      <c r="T1144" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1144" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1144">
+        <v>1</v>
+      </c>
+      <c r="AC1144">
+        <f t="shared" si="180"/>
+        <v>2</v>
+      </c>
+      <c r="AD1144">
+        <f t="shared" si="181"/>
+        <v>0</v>
+      </c>
+      <c r="AE1144">
+        <f t="shared" si="182"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1145">
+        <v>1144</v>
+      </c>
+      <c r="B1145">
+        <v>1</v>
+      </c>
+      <c r="C1145" s="1">
+        <v>46221</v>
+      </c>
+      <c r="D1145" s="2">
+        <v>0.82222222222222219</v>
+      </c>
+      <c r="E1145" s="2">
+        <v>0.82222222222222219</v>
+      </c>
+      <c r="F1145" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1145" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1145" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1145" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1145" t="s">
+        <v>53</v>
+      </c>
+      <c r="T1145" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1145" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1145">
+        <v>1</v>
+      </c>
+      <c r="AC1145">
+        <f t="shared" si="180"/>
+        <v>1</v>
+      </c>
+      <c r="AD1145">
+        <f t="shared" si="181"/>
+        <v>0</v>
+      </c>
+      <c r="AE1145">
+        <f t="shared" si="182"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1146">
+        <v>1145</v>
+      </c>
+      <c r="B1146">
+        <v>1</v>
+      </c>
+      <c r="C1146" s="1">
+        <v>46221</v>
+      </c>
+      <c r="D1146" s="2">
+        <v>0.84861111111111109</v>
+      </c>
+      <c r="E1146" s="2">
+        <v>0.84861111111111109</v>
+      </c>
+      <c r="F1146" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1146" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1146" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1146" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1146" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1146">
+        <v>9</v>
+      </c>
+      <c r="L1146">
+        <v>2</v>
+      </c>
+      <c r="M1146">
+        <v>8</v>
+      </c>
+      <c r="T1146" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1146" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1146">
+        <v>1</v>
+      </c>
+      <c r="AC1146">
+        <f t="shared" si="180"/>
+        <v>2</v>
+      </c>
+      <c r="AD1146">
+        <f t="shared" si="181"/>
+        <v>1</v>
+      </c>
+      <c r="AE1146">
+        <f t="shared" si="182"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1147">
+        <v>1146</v>
+      </c>
+      <c r="B1147">
+        <v>1</v>
+      </c>
+      <c r="C1147" s="1">
+        <v>46221</v>
+      </c>
+      <c r="D1147" s="2">
+        <v>0.89097222222222228</v>
+      </c>
+      <c r="E1147" s="2">
+        <v>0.89097222222222228</v>
+      </c>
+      <c r="F1147" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1147" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1147" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1147" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1147" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1147">
+        <v>1</v>
+      </c>
+      <c r="L1147">
+        <v>0</v>
+      </c>
+      <c r="M1147">
+        <v>5</v>
+      </c>
+      <c r="N1147">
+        <v>8</v>
+      </c>
+      <c r="O1147">
+        <v>1</v>
+      </c>
+      <c r="P1147">
+        <v>9</v>
+      </c>
+      <c r="Q1147">
+        <v>894</v>
+      </c>
+      <c r="R1147">
+        <v>52</v>
+      </c>
+      <c r="S1147">
+        <v>44</v>
+      </c>
+      <c r="T1147" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1147" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1147">
+        <v>1</v>
+      </c>
+      <c r="AC1147">
+        <f t="shared" si="180"/>
+        <v>3</v>
+      </c>
+      <c r="AD1147">
+        <f t="shared" si="181"/>
+        <v>2</v>
+      </c>
+      <c r="AE1147">
+        <f t="shared" si="182"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1148">
+        <v>1147</v>
+      </c>
+      <c r="B1148">
+        <v>1</v>
+      </c>
+      <c r="C1148" s="1">
+        <v>46283</v>
+      </c>
+      <c r="D1148" s="2">
+        <v>0.92083333333333328</v>
+      </c>
+      <c r="E1148" s="2">
+        <v>0.92083333333333328</v>
+      </c>
+      <c r="F1148" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1148" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1148" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1148" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1148" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1148">
+        <v>3</v>
+      </c>
+      <c r="L1148">
+        <v>5</v>
+      </c>
+      <c r="M1148">
+        <v>5</v>
+      </c>
+      <c r="N1148">
+        <v>11</v>
+      </c>
+      <c r="O1148">
+        <v>1</v>
+      </c>
+      <c r="P1148">
+        <v>6</v>
+      </c>
+      <c r="R1148">
+        <v>62</v>
+      </c>
+      <c r="S1148">
+        <v>14</v>
+      </c>
+      <c r="T1148" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1148" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1148">
+        <v>1</v>
+      </c>
+      <c r="AC1148">
+        <f t="shared" si="180"/>
+        <v>1</v>
+      </c>
+      <c r="AD1148">
+        <f t="shared" si="181"/>
+        <v>0</v>
+      </c>
+      <c r="AE1148">
+        <f t="shared" si="182"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1149">
+        <v>1148</v>
+      </c>
+      <c r="B1149">
+        <v>1</v>
+      </c>
+      <c r="C1149" s="1">
+        <v>46284</v>
+      </c>
+      <c r="D1149" s="2">
+        <v>0.76458333333333328</v>
+      </c>
+      <c r="E1149" s="2">
+        <v>0.76458333333333328</v>
+      </c>
+      <c r="F1149" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1149" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1149" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1149" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1149">
+        <v>7</v>
+      </c>
+      <c r="L1149">
+        <v>4</v>
+      </c>
+      <c r="M1149">
+        <v>6</v>
+      </c>
+      <c r="N1149">
+        <v>11</v>
+      </c>
+      <c r="O1149">
+        <v>3</v>
+      </c>
+      <c r="P1149">
+        <v>6</v>
+      </c>
+      <c r="R1149">
+        <v>97</v>
+      </c>
+      <c r="S1149">
+        <v>55</v>
+      </c>
+      <c r="T1149" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1149" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1149">
+        <v>2</v>
+      </c>
+      <c r="AC1149" s="5">
+        <f>IF(C1149=C1148, AC1148+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1149" s="5">
+        <f>IF(T1149="Loss",AD1148+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1149" s="5">
+        <f>IF(T1149="Win", AE1148+1, 0)</f>
+        <v>2</v>
+      </c>
+      <c r="AF1149" s="5">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="AG1149" s="5">
+        <v>44</v>
+      </c>
+      <c r="AH1149" s="5">
+        <v>69</v>
+      </c>
+      <c r="AI1149" s="5">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1150">
+        <v>1149</v>
+      </c>
+      <c r="B1150">
+        <v>1</v>
+      </c>
+      <c r="C1150" s="1">
+        <v>46284</v>
+      </c>
+      <c r="D1150" s="2">
+        <v>0.79097222222222219</v>
+      </c>
+      <c r="E1150" s="2">
+        <v>0.79097222222222219</v>
+      </c>
+      <c r="F1150" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1150" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1150" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1150" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q1150">
+        <v>2209</v>
+      </c>
+      <c r="R1150">
+        <v>78</v>
+      </c>
+      <c r="S1150">
+        <v>7</v>
+      </c>
+      <c r="T1150" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1150" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1150">
+        <v>2</v>
+      </c>
+      <c r="AC1150" s="5">
+        <f>IF(C1150=C1149, AC1149+1, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AD1150" s="5">
+        <f>IF(T1150="Loss",AD1149+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1150" s="5">
+        <f>IF(T1150="Win", AE1149+1, 0)</f>
+        <v>3</v>
+      </c>
+      <c r="AF1150" s="5">
+        <v>4.28</v>
+      </c>
+      <c r="AG1150" s="5">
+        <v>22</v>
+      </c>
+      <c r="AH1150" s="5">
+        <v>53</v>
+      </c>
+      <c r="AI1150" s="5">
+        <v>52</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB5410F-E6CE-400A-8DF0-939973BF5F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA11D2E7-927D-495B-A1EE-722F16344201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-2100" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7135" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7149" uniqueCount="121">
   <si>
     <t>ID</t>
   </si>
@@ -610,8 +610,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1150" totalsRowShown="0">
-  <autoFilter ref="A1:AI1150" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1152" totalsRowShown="0">
+  <autoFilter ref="A1:AI1152" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -965,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1150"/>
+  <dimension ref="A1:AI1152"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -99614,7 +99614,7 @@
         <v>1</v>
       </c>
       <c r="C1148" s="1">
-        <v>46283</v>
+        <v>46221</v>
       </c>
       <c r="D1148" s="2">
         <v>0.92083333333333328</v>
@@ -99672,7 +99672,7 @@
       </c>
       <c r="AC1148">
         <f t="shared" si="180"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD1148">
         <f t="shared" si="181"/>
@@ -99691,7 +99691,7 @@
         <v>1</v>
       </c>
       <c r="C1149" s="1">
-        <v>46284</v>
+        <v>46222</v>
       </c>
       <c r="D1149" s="2">
         <v>0.76458333333333328</v>
@@ -99744,28 +99744,28 @@
       <c r="V1149">
         <v>2</v>
       </c>
-      <c r="AC1149" s="5">
+      <c r="AC1149">
         <f>IF(C1149=C1148, AC1148+1, 1)</f>
         <v>1</v>
       </c>
-      <c r="AD1149" s="5">
+      <c r="AD1149">
         <f>IF(T1149="Loss",AD1148+1,0)</f>
         <v>0</v>
       </c>
-      <c r="AE1149" s="5">
+      <c r="AE1149">
         <f>IF(T1149="Win", AE1148+1, 0)</f>
         <v>2</v>
       </c>
-      <c r="AF1149" s="5">
+      <c r="AF1149">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AG1149" s="5">
+      <c r="AG1149">
         <v>44</v>
       </c>
-      <c r="AH1149" s="5">
+      <c r="AH1149">
         <v>69</v>
       </c>
-      <c r="AI1149" s="5">
+      <c r="AI1149">
         <v>63</v>
       </c>
     </row>
@@ -99777,7 +99777,7 @@
         <v>1</v>
       </c>
       <c r="C1150" s="1">
-        <v>46284</v>
+        <v>46222</v>
       </c>
       <c r="D1150" s="2">
         <v>0.79097222222222219</v>
@@ -99815,30 +99815,191 @@
       <c r="V1150">
         <v>2</v>
       </c>
-      <c r="AC1150" s="5">
+      <c r="AC1150">
         <f>IF(C1150=C1149, AC1149+1, 1)</f>
         <v>2</v>
       </c>
-      <c r="AD1150" s="5">
+      <c r="AD1150">
         <f>IF(T1150="Loss",AD1149+1,0)</f>
         <v>0</v>
       </c>
-      <c r="AE1150" s="5">
+      <c r="AE1150">
         <f>IF(T1150="Win", AE1149+1, 0)</f>
         <v>3</v>
       </c>
-      <c r="AF1150" s="5">
+      <c r="AF1150">
         <v>4.28</v>
       </c>
-      <c r="AG1150" s="5">
+      <c r="AG1150">
         <v>22</v>
       </c>
-      <c r="AH1150" s="5">
+      <c r="AH1150">
         <v>53</v>
       </c>
-      <c r="AI1150" s="5">
+      <c r="AI1150">
         <v>52</v>
       </c>
+    </row>
+    <row r="1151" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1151">
+        <v>1150</v>
+      </c>
+      <c r="B1151">
+        <v>2</v>
+      </c>
+      <c r="C1151" s="1">
+        <v>46230</v>
+      </c>
+      <c r="D1151" s="2">
+        <v>0.71666666666666667</v>
+      </c>
+      <c r="E1151" s="2">
+        <v>0.71666666666666667</v>
+      </c>
+      <c r="F1151" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1151" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1151" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1151" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1151" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1151">
+        <v>8</v>
+      </c>
+      <c r="L1151">
+        <v>1</v>
+      </c>
+      <c r="M1151">
+        <v>6</v>
+      </c>
+      <c r="N1151">
+        <v>8</v>
+      </c>
+      <c r="O1151">
+        <v>1</v>
+      </c>
+      <c r="P1151">
+        <v>11</v>
+      </c>
+      <c r="Q1151">
+        <v>1746</v>
+      </c>
+      <c r="R1151">
+        <v>87</v>
+      </c>
+      <c r="S1151">
+        <v>43</v>
+      </c>
+      <c r="T1151" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1151" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1151">
+        <v>2</v>
+      </c>
+      <c r="AC1151">
+        <f>IF(C1151=C1150, AC1150+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1151">
+        <f>IF(T1151="Loss",AD1150+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1151">
+        <f>IF(T1151="Win", AE1150+1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1152">
+        <v>1151</v>
+      </c>
+      <c r="B1152">
+        <v>1</v>
+      </c>
+      <c r="C1152" s="1">
+        <v>46230</v>
+      </c>
+      <c r="D1152" s="2">
+        <v>0.82916666666666672</v>
+      </c>
+      <c r="E1152" s="2">
+        <v>0.82916666666666672</v>
+      </c>
+      <c r="F1152" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1152" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1152" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1152" t="s">
+        <v>120</v>
+      </c>
+      <c r="J1152" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1152">
+        <v>4</v>
+      </c>
+      <c r="L1152">
+        <v>6</v>
+      </c>
+      <c r="M1152">
+        <v>11</v>
+      </c>
+      <c r="N1152">
+        <v>5</v>
+      </c>
+      <c r="O1152">
+        <v>2</v>
+      </c>
+      <c r="P1152">
+        <v>9</v>
+      </c>
+      <c r="Q1152">
+        <v>1467</v>
+      </c>
+      <c r="R1152">
+        <v>61</v>
+      </c>
+      <c r="T1152" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1152" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1152">
+        <v>1</v>
+      </c>
+      <c r="AC1152" s="5">
+        <f>IF(C1152=C1151, AC1151+1, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AD1152" s="5">
+        <f>IF(T1152="Loss",AD1151+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1152" s="5">
+        <f>IF(T1152="Win", AE1151+1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF1152" s="5"/>
+      <c r="AG1152" s="5"/>
+      <c r="AH1152" s="5"/>
+      <c r="AI1152" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA11D2E7-927D-495B-A1EE-722F16344201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA77D700-F0CC-4314-932B-9E33B4F35E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-2100" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7149" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7167" uniqueCount="121">
   <si>
     <t>ID</t>
   </si>
@@ -610,8 +610,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1152" totalsRowShown="0">
-  <autoFilter ref="A1:AI1152" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1155" totalsRowShown="0">
+  <autoFilter ref="A1:AI1155" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -965,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1152"/>
+  <dimension ref="A1:AI1155"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -99984,22 +99984,267 @@
       <c r="V1152">
         <v>1</v>
       </c>
-      <c r="AC1152" s="5">
+      <c r="AC1152">
         <f>IF(C1152=C1151, AC1151+1, 1)</f>
         <v>2</v>
       </c>
-      <c r="AD1152" s="5">
+      <c r="AD1152">
         <f>IF(T1152="Loss",AD1151+1,0)</f>
         <v>0</v>
       </c>
-      <c r="AE1152" s="5">
+      <c r="AE1152">
         <f>IF(T1152="Win", AE1151+1, 0)</f>
         <v>1</v>
       </c>
-      <c r="AF1152" s="5"/>
-      <c r="AG1152" s="5"/>
-      <c r="AH1152" s="5"/>
-      <c r="AI1152" s="5"/>
+    </row>
+    <row r="1153" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1153">
+        <v>1152</v>
+      </c>
+      <c r="B1153">
+        <v>1</v>
+      </c>
+      <c r="C1153" s="1">
+        <v>46231</v>
+      </c>
+      <c r="D1153" s="2">
+        <v>0.76111111111111107</v>
+      </c>
+      <c r="E1153" s="2">
+        <v>0.76111111111111107</v>
+      </c>
+      <c r="F1153" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1153" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1153" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1153" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1153" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1153">
+        <v>11</v>
+      </c>
+      <c r="L1153">
+        <v>3</v>
+      </c>
+      <c r="M1153">
+        <v>9</v>
+      </c>
+      <c r="N1153">
+        <v>7</v>
+      </c>
+      <c r="O1153">
+        <v>5</v>
+      </c>
+      <c r="P1153">
+        <v>9</v>
+      </c>
+      <c r="Q1153">
+        <v>1914</v>
+      </c>
+      <c r="R1153">
+        <v>83</v>
+      </c>
+      <c r="S1153">
+        <v>44</v>
+      </c>
+      <c r="T1153" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1153">
+        <v>16647</v>
+      </c>
+      <c r="V1153">
+        <v>1</v>
+      </c>
+      <c r="AC1153" s="5">
+        <f>IF(C1153=C1152, AC1152+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1153" s="5">
+        <f>IF(T1153="Loss",AD1152+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE1153" s="5">
+        <f>IF(T1153="Win", AE1152+1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF1153" s="5"/>
+      <c r="AG1153" s="5"/>
+      <c r="AH1153" s="5"/>
+      <c r="AI1153" s="5"/>
+    </row>
+    <row r="1154" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1154">
+        <v>1153</v>
+      </c>
+      <c r="B1154">
+        <v>2</v>
+      </c>
+      <c r="C1154" s="1">
+        <v>46231</v>
+      </c>
+      <c r="D1154" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E1154" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F1154" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1154" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1154" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1154" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1154" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1154">
+        <v>10</v>
+      </c>
+      <c r="L1154">
+        <v>4</v>
+      </c>
+      <c r="M1154">
+        <v>8</v>
+      </c>
+      <c r="N1154">
+        <v>4</v>
+      </c>
+      <c r="O1154">
+        <v>1</v>
+      </c>
+      <c r="P1154">
+        <v>7</v>
+      </c>
+      <c r="Q1154">
+        <v>1526</v>
+      </c>
+      <c r="R1154">
+        <v>66</v>
+      </c>
+      <c r="S1154">
+        <v>42</v>
+      </c>
+      <c r="T1154" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1154">
+        <v>16543</v>
+      </c>
+      <c r="V1154">
+        <v>2</v>
+      </c>
+      <c r="AC1154" s="5">
+        <f>IF(C1154=C1153, AC1153+1, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AD1154" s="5">
+        <f>IF(T1154="Loss",AD1153+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1154" s="5">
+        <f>IF(T1154="Win", AE1153+1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF1154" s="5"/>
+      <c r="AG1154" s="5"/>
+      <c r="AH1154" s="5"/>
+      <c r="AI1154" s="5"/>
+    </row>
+    <row r="1155" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1155">
+        <v>1154</v>
+      </c>
+      <c r="B1155">
+        <v>2</v>
+      </c>
+      <c r="C1155" s="1">
+        <v>46231</v>
+      </c>
+      <c r="D1155" s="2">
+        <v>0.8208333333333333</v>
+      </c>
+      <c r="E1155" s="2">
+        <v>0.8208333333333333</v>
+      </c>
+      <c r="F1155" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1155" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1155" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1155" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1155" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1155">
+        <v>5</v>
+      </c>
+      <c r="L1155">
+        <v>3</v>
+      </c>
+      <c r="M1155">
+        <v>13</v>
+      </c>
+      <c r="N1155">
+        <v>9</v>
+      </c>
+      <c r="O1155">
+        <v>6</v>
+      </c>
+      <c r="P1155">
+        <v>8</v>
+      </c>
+      <c r="R1155">
+        <v>62</v>
+      </c>
+      <c r="S1155">
+        <v>35</v>
+      </c>
+      <c r="T1155" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1155">
+        <v>16953</v>
+      </c>
+      <c r="V1155">
+        <v>2</v>
+      </c>
+      <c r="AC1155" s="5">
+        <f>IF(C1155=C1154, AC1154+1, 1)</f>
+        <v>3</v>
+      </c>
+      <c r="AD1155" s="5">
+        <f>IF(T1155="Loss",AD1154+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1155" s="5">
+        <f>IF(T1155="Win", AE1154+1, 0)</f>
+        <v>2</v>
+      </c>
+      <c r="AF1155" s="5"/>
+      <c r="AG1155" s="5"/>
+      <c r="AH1155" s="5"/>
+      <c r="AI1155" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets/xlsx/CounterStrike2.xlsx
+++ b/datasets/xlsx/CounterStrike2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\Programming SHit\HardWareWebsite\datasets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA77D700-F0CC-4314-932B-9E33B4F35E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE3824F-4383-426B-8469-FB2678D4A530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-2100" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7167" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7173" uniqueCount="121">
   <si>
     <t>ID</t>
   </si>
@@ -610,8 +610,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1155" totalsRowShown="0">
-  <autoFilter ref="A1:AI1155" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}" name="MainTable" displayName="MainTable" ref="A1:AI1156" totalsRowShown="0">
+  <autoFilter ref="A1:AI1156" xr:uid="{F76B0D88-E146-4F78-8247-B2C76B2DA893}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{F242931A-789C-4FBB-B822-B98BDC16035B}" name="ID"/>
     <tableColumn id="33" xr3:uid="{FCC59173-429E-4F7A-8FB8-03CC405E84A0}" name="PlayerID"/>
@@ -965,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1155"/>
+  <dimension ref="A1:AI1156"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -99745,15 +99745,15 @@
         <v>2</v>
       </c>
       <c r="AC1149">
-        <f>IF(C1149=C1148, AC1148+1, 1)</f>
+        <f t="shared" ref="AC1149:AC1155" si="183">IF(C1149=C1148, AC1148+1, 1)</f>
         <v>1</v>
       </c>
       <c r="AD1149">
-        <f>IF(T1149="Loss",AD1148+1,0)</f>
+        <f t="shared" ref="AD1149:AD1155" si="184">IF(T1149="Loss",AD1148+1,0)</f>
         <v>0</v>
       </c>
       <c r="AE1149">
-        <f>IF(T1149="Win", AE1148+1, 0)</f>
+        <f t="shared" ref="AE1149:AE1155" si="185">IF(T1149="Win", AE1148+1, 0)</f>
         <v>2</v>
       </c>
       <c r="AF1149">
@@ -99816,15 +99816,15 @@
         <v>2</v>
       </c>
       <c r="AC1150">
-        <f>IF(C1150=C1149, AC1149+1, 1)</f>
+        <f t="shared" si="183"/>
         <v>2</v>
       </c>
       <c r="AD1150">
-        <f>IF(T1150="Loss",AD1149+1,0)</f>
+        <f t="shared" si="184"/>
         <v>0</v>
       </c>
       <c r="AE1150">
-        <f>IF(T1150="Win", AE1149+1, 0)</f>
+        <f t="shared" si="185"/>
         <v>3</v>
       </c>
       <c r="AF1150">
@@ -99908,15 +99908,15 @@
         <v>2</v>
       </c>
       <c r="AC1151">
-        <f>IF(C1151=C1150, AC1150+1, 1)</f>
+        <f t="shared" si="183"/>
         <v>1</v>
       </c>
       <c r="AD1151">
-        <f>IF(T1151="Loss",AD1150+1,0)</f>
+        <f t="shared" si="184"/>
         <v>1</v>
       </c>
       <c r="AE1151">
-        <f>IF(T1151="Win", AE1150+1, 0)</f>
+        <f t="shared" si="185"/>
         <v>0</v>
       </c>
     </row>
@@ -99985,15 +99985,15 @@
         <v>1</v>
       </c>
       <c r="AC1152">
-        <f>IF(C1152=C1151, AC1151+1, 1)</f>
+        <f t="shared" si="183"/>
         <v>2</v>
       </c>
       <c r="AD1152">
-        <f>IF(T1152="Loss",AD1151+1,0)</f>
+        <f t="shared" si="184"/>
         <v>0</v>
       </c>
       <c r="AE1152">
-        <f>IF(T1152="Win", AE1151+1, 0)</f>
+        <f t="shared" si="185"/>
         <v>1</v>
       </c>
     </row>
@@ -100064,22 +100064,18 @@
       <c r="V1153">
         <v>1</v>
       </c>
-      <c r="AC1153" s="5">
-        <f>IF(C1153=C1152, AC1152+1, 1)</f>
-        <v>1</v>
-      </c>
-      <c r="AD1153" s="5">
-        <f>IF(T1153="Loss",AD1152+1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AE1153" s="5">
-        <f>IF(T1153="Win", AE1152+1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF1153" s="5"/>
-      <c r="AG1153" s="5"/>
-      <c r="AH1153" s="5"/>
-      <c r="AI1153" s="5"/>
+      <c r="AC1153">
+        <f t="shared" si="183"/>
+        <v>1</v>
+      </c>
+      <c r="AD1153">
+        <f t="shared" si="184"/>
+        <v>1</v>
+      </c>
+      <c r="AE1153">
+        <f t="shared" si="185"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="1154" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1154">
@@ -100148,22 +100144,18 @@
       <c r="V1154">
         <v>2</v>
       </c>
-      <c r="AC1154" s="5">
-        <f>IF(C1154=C1153, AC1153+1, 1)</f>
-        <v>2</v>
-      </c>
-      <c r="AD1154" s="5">
-        <f>IF(T1154="Loss",AD1153+1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE1154" s="5">
-        <f>IF(T1154="Win", AE1153+1, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="AF1154" s="5"/>
-      <c r="AG1154" s="5"/>
-      <c r="AH1154" s="5"/>
-      <c r="AI1154" s="5"/>
+      <c r="AC1154">
+        <f t="shared" si="183"/>
+        <v>2</v>
+      </c>
+      <c r="AD1154">
+        <f t="shared" si="184"/>
+        <v>0</v>
+      </c>
+      <c r="AE1154">
+        <f t="shared" si="185"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1155" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1155">
@@ -100229,22 +100221,102 @@
       <c r="V1155">
         <v>2</v>
       </c>
-      <c r="AC1155" s="5">
-        <f>IF(C1155=C1154, AC1154+1, 1)</f>
-        <v>3</v>
-      </c>
-      <c r="AD1155" s="5">
-        <f>IF(T1155="Loss",AD1154+1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE1155" s="5">
-        <f>IF(T1155="Win", AE1154+1, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="AF1155" s="5"/>
-      <c r="AG1155" s="5"/>
-      <c r="AH1155" s="5"/>
-      <c r="AI1155" s="5"/>
+      <c r="AC1155">
+        <f t="shared" si="183"/>
+        <v>3</v>
+      </c>
+      <c r="AD1155">
+        <f t="shared" si="184"/>
+        <v>0</v>
+      </c>
+      <c r="AE1155">
+        <f t="shared" si="185"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1156">
+        <v>1155</v>
+      </c>
+      <c r="B1156">
+        <v>1</v>
+      </c>
+      <c r="C1156" s="1">
+        <v>46249</v>
+      </c>
+      <c r="D1156" s="2">
+        <v>0.74791666666666667</v>
+      </c>
+      <c r="E1156" s="2">
+        <v>0.74791666666666667</v>
+      </c>
+      <c r="F1156" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1156" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1156" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1156" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1156" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1156">
+        <v>12</v>
+      </c>
+      <c r="L1156">
+        <v>6</v>
+      </c>
+      <c r="M1156">
+        <v>4</v>
+      </c>
+      <c r="N1156">
+        <v>2</v>
+      </c>
+      <c r="O1156">
+        <v>0</v>
+      </c>
+      <c r="P1156">
+        <v>1</v>
+      </c>
+      <c r="Q1156">
+        <v>1447</v>
+      </c>
+      <c r="R1156">
+        <v>103</v>
+      </c>
+      <c r="S1156">
+        <v>64</v>
+      </c>
+      <c r="T1156" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1156">
+        <v>17374</v>
+      </c>
+      <c r="V1156">
+        <v>1</v>
+      </c>
+      <c r="AC1156" s="5">
+        <f>IF(C1156=C1155, AC1155+1, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AD1156" s="5">
+        <f>IF(T1156="Loss",AD1155+1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE1156" s="5">
+        <f>IF(T1156="Win", AE1155+1, 0)</f>
+        <v>3</v>
+      </c>
+      <c r="AF1156" s="5"/>
+      <c r="AG1156" s="5"/>
+      <c r="AH1156" s="5"/>
+      <c r="AI1156" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
